--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -523,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-17 10:47</t>
+          <t>Dibuat: 2026-10-19 20:01</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -681,7 +681,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+245.70%</t>
+          <t>+242.70%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+9.45%</t>
+          <t>+8.99%</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -757,7 +757,7 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -772,7 +772,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-19</t>
+          <t>Prediksi untuk: 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -852,31 +852,75 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>5150</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>92.88</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>153.79</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>KUAT</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>TRUK</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
-        <v>3220</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>106.41</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>148.12</v>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="E6" s="7" t="n">
+        <v>4020</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>134.4</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>173.89</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -897,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1176,12 +1220,66 @@
         <v>9.74</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Minggu 4</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-19 s/d 2026-10-19</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-3</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="O5:O7">
+  <conditionalFormatting sqref="O5:O8">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1189,7 +1287,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P7">
+  <conditionalFormatting sqref="P5:P8">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1207,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1361,27 +1459,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4230</v>
+        <v>290</v>
       </c>
       <c r="E7" t="n">
-        <v>4020</v>
+        <v>292</v>
       </c>
       <c r="F7" t="n">
-        <v>4860</v>
+        <v>354</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>20.02</v>
       </c>
     </row>
     <row r="8">
@@ -1395,30 +1496,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>4230</v>
       </c>
       <c r="E8" t="n">
-        <v>525</v>
+        <v>4020</v>
       </c>
       <c r="F8" t="n">
-        <v>560</v>
+        <v>4860</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.6</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1432,17 +1530,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>470</v>
       </c>
       <c r="E9" t="n">
-        <v>292</v>
+        <v>525</v>
       </c>
       <c r="F9" t="n">
-        <v>354</v>
+        <v>560</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1455,7 +1553,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>20.02</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="10">
@@ -1543,21 +1641,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>332</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>342</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
+        <v>378</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1566,7 +1664,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="13">
@@ -1580,21 +1678,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SOTS</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>630</v>
+        <v>350</v>
       </c>
       <c r="E13" t="n">
-        <v>655</v>
+        <v>360</v>
       </c>
       <c r="F13" t="n">
-        <v>675</v>
+        <v>404</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1603,7 +1701,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.02</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="14">
@@ -1617,26 +1715,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PPRI</t>
+          <t>WAPO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>186</v>
+        <v>352</v>
       </c>
       <c r="E14" t="n">
-        <v>180</v>
+        <v>364</v>
       </c>
       <c r="F14" t="n">
-        <v>196</v>
+        <v>400</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -1651,17 +1749,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>332</v>
+        <v>4400</v>
       </c>
       <c r="E15" t="n">
-        <v>342</v>
+        <v>4220</v>
       </c>
       <c r="F15" t="n">
-        <v>378</v>
+        <v>4630</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1670,11 +1768,8 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.42</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1688,21 +1783,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>530</v>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>550</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
+        <v>660</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1711,7 +1806,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.18</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="17">
@@ -1725,17 +1820,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WAPO</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>352</v>
+        <v>71</v>
       </c>
       <c r="E17" t="n">
-        <v>364</v>
+        <v>71</v>
       </c>
       <c r="F17" t="n">
-        <v>400</v>
+        <v>74</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1744,8 +1839,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.18</v>
       </c>
     </row>
     <row r="18">
@@ -1759,27 +1857,30 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>SOTS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4400</v>
+        <v>630</v>
       </c>
       <c r="E18" t="n">
-        <v>4220</v>
+        <v>655</v>
       </c>
       <c r="F18" t="n">
-        <v>4630</v>
+        <v>675</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.02</v>
       </c>
     </row>
     <row r="19">
@@ -1793,21 +1894,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>530</v>
+        <v>412</v>
       </c>
       <c r="E19" t="n">
-        <v>550</v>
+        <v>434</v>
       </c>
       <c r="F19" t="n">
-        <v>660</v>
+        <v>515</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1816,7 +1917,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>18.8</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="20">
@@ -1830,30 +1931,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>PPRI</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>350</v>
+        <v>186</v>
       </c>
       <c r="E20" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="F20" t="n">
-        <v>404</v>
+        <v>196</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>11.1</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1867,21 +1965,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>412</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>434</v>
+        <v>55</v>
       </c>
       <c r="F21" t="n">
-        <v>515</v>
+        <v>59</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1890,7 +1988,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>17.48</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="22">
@@ -1904,21 +2002,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F22" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1927,7 +2025,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="23">
@@ -1975,26 +2073,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6800</v>
+        <v>655</v>
       </c>
       <c r="E24" t="n">
-        <v>6850</v>
+        <v>640</v>
       </c>
       <c r="F24" t="n">
-        <v>7150</v>
+        <v>640</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
@@ -2009,30 +2107,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IATA</t>
+          <t>PKPK</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>115</v>
+        <v>6800</v>
       </c>
       <c r="E25" t="n">
-        <v>115</v>
+        <v>6850</v>
       </c>
       <c r="F25" t="n">
-        <v>115</v>
+        <v>7150</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>-3</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2080,27 +2175,30 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>IATA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>655</v>
+        <v>115</v>
       </c>
       <c r="E27" t="n">
-        <v>640</v>
+        <v>115</v>
       </c>
       <c r="F27" t="n">
-        <v>640</v>
+        <v>115</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="28">
@@ -2114,17 +2212,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>INCI</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>71</v>
+        <v>1025</v>
       </c>
       <c r="E28" t="n">
-        <v>77</v>
+        <v>1030</v>
       </c>
       <c r="F28" t="n">
-        <v>92</v>
+        <v>1065</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2137,7 +2235,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>18.29</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="29">
@@ -2151,26 +2249,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>POLA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -2185,27 +2283,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>POLA</t>
+          <t>HELI</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>110</v>
+        <v>342</v>
       </c>
       <c r="E30" t="n">
-        <v>120</v>
+        <v>342</v>
       </c>
       <c r="F30" t="n">
-        <v>121</v>
+        <v>402</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>16.37</v>
       </c>
     </row>
     <row r="31">
@@ -2253,17 +2354,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HELI</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>342</v>
+        <v>71</v>
       </c>
       <c r="E32" t="n">
-        <v>342</v>
+        <v>77</v>
       </c>
       <c r="F32" t="n">
-        <v>402</v>
+        <v>92</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2276,7 +2377,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>16.37</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="33">
@@ -2290,30 +2391,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INCI</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1025</v>
+        <v>51</v>
       </c>
       <c r="E33" t="n">
-        <v>1030</v>
+        <v>50</v>
       </c>
       <c r="F33" t="n">
-        <v>1065</v>
+        <v>52</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2.36</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2327,27 +2425,30 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>396</v>
+        <v>905</v>
       </c>
       <c r="E34" t="n">
-        <v>402</v>
+        <v>985</v>
       </c>
       <c r="F34" t="n">
-        <v>426</v>
+        <v>1120</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>12.57</v>
       </c>
     </row>
     <row r="35">
@@ -2361,21 +2462,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>316</v>
+        <v>396</v>
       </c>
       <c r="E35" t="n">
-        <v>290</v>
+        <v>402</v>
       </c>
       <c r="F35" t="n">
-        <v>332</v>
+        <v>426</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2395,21 +2496,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>MCAS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>452</v>
+        <v>284</v>
       </c>
       <c r="E36" t="n">
-        <v>530</v>
+        <v>310</v>
       </c>
       <c r="F36" t="n">
-        <v>565</v>
+        <v>326</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2418,7 +2519,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.54</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="37">
@@ -2432,30 +2533,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MCAS</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="E37" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="F37" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>4.11</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2469,30 +2567,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>PEVE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>905</v>
+        <v>412</v>
       </c>
       <c r="E38" t="n">
-        <v>985</v>
+        <v>398</v>
       </c>
       <c r="F38" t="n">
-        <v>1120</v>
+        <v>398</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>12.57</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2506,17 +2601,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PEVE</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="E39" t="n">
-        <v>398</v>
+        <v>530</v>
       </c>
       <c r="F39" t="n">
-        <v>398</v>
+        <v>565</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2525,8 +2620,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>5.54</v>
       </c>
     </row>
     <row r="40">
@@ -2756,30 +2854,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PICO</t>
+          <t>SBMA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>142</v>
       </c>
       <c r="F46" t="n">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>3.71</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -2793,27 +2888,30 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SBMA</t>
+          <t>PICO</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="E47" t="n">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="F47" t="n">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3.71</v>
       </c>
     </row>
     <row r="48">
@@ -2827,30 +2925,30 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4160</v>
+        <v>101</v>
       </c>
       <c r="E48" t="n">
-        <v>4370</v>
+        <v>101</v>
       </c>
       <c r="F48" t="n">
-        <v>4930</v>
+        <v>101</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>11.69</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="49">
@@ -2864,21 +2962,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GRPH</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E49" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="F49" t="n">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2898,17 +2996,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>107</v>
+        <v>4160</v>
       </c>
       <c r="E50" t="n">
-        <v>105</v>
+        <v>4370</v>
       </c>
       <c r="F50" t="n">
-        <v>115</v>
+        <v>4930</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2917,8 +3015,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>11.69</v>
       </c>
     </row>
     <row r="51">
@@ -2932,17 +3033,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>GRPH</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="E51" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="F51" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2951,11 +3052,8 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -2969,26 +3067,26 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>SBMA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2580</v>
+        <v>148</v>
       </c>
       <c r="E52" t="n">
-        <v>3220</v>
+        <v>126</v>
       </c>
       <c r="F52" t="n">
-        <v>3220</v>
+        <v>131</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
@@ -3003,26 +3101,165 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SBMA</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>148</v>
+        <v>2580</v>
       </c>
       <c r="E53" t="n">
-        <v>126</v>
+        <v>3220</v>
       </c>
       <c r="F53" t="n">
-        <v>131</v>
+        <v>3220</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AKKU</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>105</v>
+      </c>
+      <c r="E54" t="n">
+        <v>98</v>
+      </c>
+      <c r="F54" t="n">
+        <v>98</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>SKIP_GAP_DOWN</t>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4020</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4020</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AIMS</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>990</v>
+      </c>
+      <c r="E56" t="n">
+        <v>925</v>
+      </c>
+      <c r="F56" t="n">
+        <v>925</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ALDO</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1955</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1820</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1820</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3268,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I53">
+  <conditionalFormatting sqref="I5:I57">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -523,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-19 20:01</t>
+          <t>Dibuat: 2026-10-20 17:17</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -681,7 +681,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+242.70%</t>
+          <t>+239.70%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+8.99%</t>
+          <t>+8.56%</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-20</t>
+          <t>Prediksi untuk: 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -852,29 +852,29 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>5150</v>
+        <v>5025</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>44.8</v>
+        <v>7.92</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>22.62</v>
+        <v>25</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>92.88</v>
+        <v>166.58</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>25.53</v>
+        <v>12.44</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>1.56</v>
+        <v>0.28</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>153.79</v>
+        <v>199.06</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -896,29 +896,29 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>4020</v>
+        <v>348</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>10.74</v>
+        <v>27.28</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>24.84</v>
+        <v>20.83</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>134.4</v>
+        <v>20</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>19.9</v>
+        <v>19.54</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.85</v>
+        <v>1.7</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>173.89</v>
+        <v>32.5</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1234,14 +1234,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-19 s/d 2026-10-19</t>
+          <t>2026-10-19 s/d 2026-10-20</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="P8" t="n">
         <v>-3</v>
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3135,17 +3135,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>105</v>
+        <v>1955</v>
       </c>
       <c r="E54" t="n">
-        <v>98</v>
+        <v>1820</v>
       </c>
       <c r="F54" t="n">
-        <v>98</v>
+        <v>1820</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3240,17 +3240,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1955</v>
+        <v>105</v>
       </c>
       <c r="E57" t="n">
-        <v>1820</v>
+        <v>98</v>
       </c>
       <c r="F57" t="n">
-        <v>1820</v>
+        <v>98</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3261,6 +3261,43 @@
         <is>
           <t>SUSPENDED</t>
         </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>4020</v>
+      </c>
+      <c r="E58" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F58" t="n">
+        <v>5025</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>-3</v>
       </c>
     </row>
   </sheetData>
@@ -3268,7 +3305,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I57">
+  <conditionalFormatting sqref="I5:I58">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -523,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-20 17:17</t>
+          <t>Dibuat: 2026-10-21 08:51</t>
         </is>
       </c>
     </row>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -523,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-21 08:51</t>
+          <t>Dibuat: 2026-10-21 15:18</t>
         </is>
       </c>
     </row>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -523,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-21 15:18</t>
+          <t>Dibuat: 2026-10-21 19:37</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.7%</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+239.70%</t>
+          <t>+241.63%</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>+8.56%</t>
+          <t>+8.05%</t>
         </is>
       </c>
     </row>
@@ -745,19 +745,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
@@ -772,7 +772,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-21</t>
+          <t>Prediksi untuk: 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -852,29 +852,29 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>5025</v>
+        <v>137</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>7.92</v>
+        <v>29.67</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>25</v>
+        <v>34.31</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>166.58</v>
+        <v>28.04</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>12.44</v>
+        <v>27.74</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>0.28</v>
+        <v>0.67</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>199.06</v>
+        <v>83.03</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -887,40 +887,84 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>KUAT</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>348</v>
+        <v>118</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>27.28</v>
+        <v>15.35</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>20.83</v>
+        <v>19.19</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>20</v>
+        <v>15.69</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>19.54</v>
+        <v>21.19</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.7</v>
+        <v>0.73</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>32.5</v>
+        <v>40.06</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>6025</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>191.06</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>210.33</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1234,20 +1278,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-19 s/d 2026-10-20</t>
+          <t>2026-10-19 s/d 2026-10-21</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -1265,13 +1309,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O8" t="n">
-        <v>-6</v>
+        <v>-4.07</v>
       </c>
       <c r="P8" t="n">
-        <v>-3</v>
+        <v>-1.02</v>
       </c>
     </row>
   </sheetData>
@@ -1305,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1459,30 +1503,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>290</v>
+        <v>4230</v>
       </c>
       <c r="E7" t="n">
-        <v>292</v>
+        <v>4020</v>
       </c>
       <c r="F7" t="n">
-        <v>354</v>
+        <v>4860</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>20.02</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1496,27 +1537,30 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4230</v>
+        <v>290</v>
       </c>
       <c r="E8" t="n">
-        <v>4020</v>
+        <v>292</v>
       </c>
       <c r="F8" t="n">
-        <v>4860</v>
+        <v>354</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>20.02</v>
       </c>
     </row>
     <row r="9">
@@ -1641,21 +1685,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>332</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>342</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>378</v>
+        <v>63</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1664,7 +1708,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>9.42</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -1678,21 +1722,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>SOTS</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>350</v>
+        <v>630</v>
       </c>
       <c r="E13" t="n">
-        <v>360</v>
+        <v>655</v>
       </c>
       <c r="F13" t="n">
-        <v>404</v>
+        <v>675</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1701,7 +1745,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>11.1</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="14">
@@ -1715,26 +1759,26 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WAPO</t>
+          <t>PPRI</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>352</v>
+        <v>186</v>
       </c>
       <c r="E14" t="n">
-        <v>364</v>
+        <v>180</v>
       </c>
       <c r="F14" t="n">
-        <v>400</v>
+        <v>196</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
@@ -1749,17 +1793,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4400</v>
+        <v>332</v>
       </c>
       <c r="E15" t="n">
-        <v>4220</v>
+        <v>342</v>
       </c>
       <c r="F15" t="n">
-        <v>4630</v>
+        <v>378</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1768,8 +1812,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9.42</v>
       </c>
     </row>
     <row r="16">
@@ -1783,21 +1830,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>530</v>
+        <v>71</v>
       </c>
       <c r="E16" t="n">
-        <v>550</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>660</v>
+        <v>74</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1806,7 +1853,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>18.8</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="17">
@@ -1820,17 +1867,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>WAPO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>352</v>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>364</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>400</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1839,11 +1886,8 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.18</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1857,30 +1901,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SOTS</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>630</v>
+        <v>4400</v>
       </c>
       <c r="E18" t="n">
-        <v>655</v>
+        <v>4220</v>
       </c>
       <c r="F18" t="n">
-        <v>675</v>
+        <v>4630</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.02</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1894,21 +1935,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>412</v>
+        <v>530</v>
       </c>
       <c r="E19" t="n">
-        <v>434</v>
+        <v>550</v>
       </c>
       <c r="F19" t="n">
-        <v>515</v>
+        <v>660</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1917,7 +1958,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>17.48</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="20">
@@ -1931,27 +1972,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PPRI</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>186</v>
+        <v>412</v>
       </c>
       <c r="E20" t="n">
-        <v>180</v>
+        <v>434</v>
       </c>
       <c r="F20" t="n">
-        <v>196</v>
+        <v>515</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>17.48</v>
       </c>
     </row>
     <row r="21">
@@ -1965,17 +2009,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>350</v>
       </c>
       <c r="E21" t="n">
-        <v>55</v>
+        <v>360</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>404</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1988,7 +2032,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="22">
@@ -2002,30 +2046,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>ASLI</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>486</v>
       </c>
       <c r="E22" t="n">
-        <v>62</v>
+        <v>496</v>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>540</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0.6</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2039,17 +2080,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ASLI</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>486</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>496</v>
+        <v>55</v>
       </c>
       <c r="F23" t="n">
-        <v>540</v>
+        <v>59</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2058,8 +2099,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="24">
@@ -2073,26 +2117,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>PKPK</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>655</v>
+        <v>6800</v>
       </c>
       <c r="E24" t="n">
-        <v>640</v>
+        <v>6850</v>
       </c>
       <c r="F24" t="n">
-        <v>640</v>
+        <v>7150</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -2107,27 +2151,30 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>IATA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6800</v>
+        <v>115</v>
       </c>
       <c r="E25" t="n">
-        <v>6850</v>
+        <v>115</v>
       </c>
       <c r="F25" t="n">
-        <v>7150</v>
+        <v>115</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="26">
@@ -2175,30 +2222,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IATA</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>115</v>
+        <v>655</v>
       </c>
       <c r="E27" t="n">
-        <v>115</v>
+        <v>640</v>
       </c>
       <c r="F27" t="n">
-        <v>115</v>
+        <v>640</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2212,17 +2256,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>INCI</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1025</v>
+        <v>71</v>
       </c>
       <c r="E28" t="n">
-        <v>1030</v>
+        <v>77</v>
       </c>
       <c r="F28" t="n">
-        <v>1065</v>
+        <v>92</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2235,7 +2279,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.36</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="29">
@@ -2249,26 +2293,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>POLA</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>110</v>
+        <v>51</v>
       </c>
       <c r="E29" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F29" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
@@ -2283,30 +2327,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HELI</t>
+          <t>POLA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>342</v>
+        <v>110</v>
       </c>
       <c r="E30" t="n">
-        <v>342</v>
+        <v>120</v>
       </c>
       <c r="F30" t="n">
-        <v>402</v>
+        <v>121</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>16.37</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2320,27 +2361,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>INCI</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1505</v>
+        <v>1025</v>
       </c>
       <c r="E31" t="n">
-        <v>1800</v>
+        <v>1030</v>
       </c>
       <c r="F31" t="n">
-        <v>1880</v>
+        <v>1065</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>2.36</v>
       </c>
     </row>
     <row r="32">
@@ -2354,17 +2398,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>HELI</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>71</v>
+        <v>342</v>
       </c>
       <c r="E32" t="n">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="F32" t="n">
-        <v>92</v>
+        <v>402</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2377,7 +2421,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>18.29</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="33">
@@ -2391,26 +2435,26 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>51</v>
+        <v>1505</v>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>1800</v>
       </c>
       <c r="F33" t="n">
-        <v>52</v>
+        <v>1880</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -2425,17 +2469,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>MCAS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>905</v>
+        <v>284</v>
       </c>
       <c r="E34" t="n">
-        <v>985</v>
+        <v>310</v>
       </c>
       <c r="F34" t="n">
-        <v>1120</v>
+        <v>326</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2448,7 +2492,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>12.57</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="35">
@@ -2462,21 +2506,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>396</v>
+        <v>316</v>
       </c>
       <c r="E35" t="n">
-        <v>402</v>
+        <v>290</v>
       </c>
       <c r="F35" t="n">
-        <v>426</v>
+        <v>332</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2496,30 +2540,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MCAS</t>
+          <t>PEVE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>284</v>
+        <v>412</v>
       </c>
       <c r="E36" t="n">
-        <v>310</v>
+        <v>398</v>
       </c>
       <c r="F36" t="n">
-        <v>326</v>
+        <v>398</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>4.11</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2533,17 +2574,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>316</v>
+        <v>452</v>
       </c>
       <c r="E37" t="n">
-        <v>290</v>
+        <v>530</v>
       </c>
       <c r="F37" t="n">
-        <v>332</v>
+        <v>565</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2552,8 +2593,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5.54</v>
       </c>
     </row>
     <row r="38">
@@ -2567,26 +2611,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PEVE</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="E38" t="n">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F38" t="n">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -2601,21 +2645,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>452</v>
+        <v>905</v>
       </c>
       <c r="E39" t="n">
-        <v>530</v>
+        <v>985</v>
       </c>
       <c r="F39" t="n">
-        <v>565</v>
+        <v>1120</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2624,7 +2668,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.54</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="40">
@@ -2675,17 +2719,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>980</v>
+        <v>83</v>
       </c>
       <c r="E41" t="n">
-        <v>1005</v>
+        <v>87</v>
       </c>
       <c r="F41" t="n">
-        <v>1115</v>
+        <v>101</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2694,8 +2738,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>14.93</v>
       </c>
     </row>
     <row r="42">
@@ -2709,17 +2756,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>83</v>
+        <v>980</v>
       </c>
       <c r="E42" t="n">
-        <v>87</v>
+        <v>1005</v>
       </c>
       <c r="F42" t="n">
-        <v>101</v>
+        <v>1115</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2728,11 +2775,8 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>14.93</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2854,27 +2898,30 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SBMA</t>
+          <t>PICO</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="E46" t="n">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="F46" t="n">
-        <v>142</v>
+        <v>220</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3.71</v>
       </c>
     </row>
     <row r="47">
@@ -2888,30 +2935,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PICO</t>
+          <t>SBMA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="E47" t="n">
-        <v>210</v>
+        <v>142</v>
       </c>
       <c r="F47" t="n">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>3.71</v>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3135,17 +3179,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1955</v>
+        <v>105</v>
       </c>
       <c r="E54" t="n">
-        <v>1820</v>
+        <v>98</v>
       </c>
       <c r="F54" t="n">
-        <v>1820</v>
+        <v>98</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3169,30 +3213,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3220</v>
+        <v>1955</v>
       </c>
       <c r="E55" t="n">
-        <v>4020</v>
+        <v>1820</v>
       </c>
       <c r="F55" t="n">
-        <v>4020</v>
+        <v>1820</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>-3</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3206,27 +3247,30 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>990</v>
+        <v>3220</v>
       </c>
       <c r="E56" t="n">
-        <v>925</v>
+        <v>4020</v>
       </c>
       <c r="F56" t="n">
-        <v>925</v>
+        <v>4020</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="57">
@@ -3240,17 +3284,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>105</v>
+        <v>990</v>
       </c>
       <c r="E57" t="n">
-        <v>98</v>
+        <v>925</v>
       </c>
       <c r="F57" t="n">
-        <v>98</v>
+        <v>925</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3298,6 +3342,80 @@
       </c>
       <c r="I58" t="n">
         <v>-3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MPXL</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>348</v>
+      </c>
+      <c r="E59" t="n">
+        <v>350</v>
+      </c>
+      <c r="F59" t="n">
+        <v>358</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>5025</v>
+      </c>
+      <c r="E60" t="n">
+        <v>5925</v>
+      </c>
+      <c r="F60" t="n">
+        <v>6025</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -3305,7 +3423,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I58">
+  <conditionalFormatting sqref="I5:I60">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -111,9 +111,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -523,7 +520,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-21 19:37</t>
+          <t>Dibuat: 2026-10-22 19:46</t>
         </is>
       </c>
     </row>
@@ -591,7 +588,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -641,7 +638,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -745,21 +742,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -772,208 +758,28 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-22</t>
+          <t>Prediksi untuk: 2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Kode</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Value (M)</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Ret1d%</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Ret5d%</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Range%</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>VolZ</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>Px&gt;sma20%</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Match</t>
+          <t>Info</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>KUAT</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n">
-        <v>137</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>34.31</v>
-      </c>
-      <c r="H5" s="7" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <v>27.74</v>
-      </c>
-      <c r="J5" s="7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="K5" s="7" t="n">
-        <v>83.03</v>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>DKHH</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>118</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>15.35</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>19.19</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>15.69</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="J6" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>40.06</v>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>TRUK</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>6025</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>191.06</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J7" s="7" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>210.33</v>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tidak ada kandidat</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2"/>
+    <mergeCell ref="A1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1108,10 +914,10 @@
           <t>Minggu 1</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>46293</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="7" t="n">
         <v>46297</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -1162,10 +968,10 @@
           <t>Minggu 2</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="7" t="n">
         <v>46300</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="7" t="n">
         <v>46304</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1216,10 +1022,10 @@
           <t>Minggu 3</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="7" t="n">
         <v>46307</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="7" t="n">
         <v>46311</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1270,19 +1076,19 @@
           <t>Minggu 4</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>46314</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="7" t="n">
         <v>46318</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-19 s/d 2026-10-21</t>
+          <t>2026-10-19 s/d 2026-10-22</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -1300,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
@@ -1349,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1425,7 +1231,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="7" t="n">
         <v>46296</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1459,7 +1265,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>46297</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1493,7 +1299,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>46297</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1527,7 +1333,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>46297</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1564,7 +1370,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="7" t="n">
         <v>46297</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1601,7 +1407,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>46300</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1638,7 +1444,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="7" t="n">
         <v>46300</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1675,7 +1481,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1712,7 +1518,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1749,7 +1555,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1783,7 +1589,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1820,7 +1626,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1857,7 +1663,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1891,7 +1697,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1925,7 +1731,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1962,7 +1768,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1999,7 +1805,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2036,7 +1842,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2070,7 +1876,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="7" t="n">
         <v>46301</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2107,7 +1913,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>46302</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2117,17 +1923,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6800</v>
+        <v>825</v>
       </c>
       <c r="E24" t="n">
-        <v>6850</v>
+        <v>910</v>
       </c>
       <c r="F24" t="n">
-        <v>7150</v>
+        <v>1030</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2141,7 +1947,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="7" t="n">
         <v>46302</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2178,7 +1984,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>46302</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2188,17 +1994,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>PKPK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>825</v>
+        <v>6800</v>
       </c>
       <c r="E26" t="n">
-        <v>910</v>
+        <v>6850</v>
       </c>
       <c r="F26" t="n">
-        <v>1030</v>
+        <v>7150</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2212,7 +2018,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="7" t="n">
         <v>46302</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2246,7 +2052,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="7" t="n">
         <v>46303</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2256,102 +2062,102 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>51</v>
+      </c>
+      <c r="E28" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" t="n">
+        <v>52</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1880</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>AKKU</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D30" t="n">
         <v>71</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E30" t="n">
         <v>77</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
         <v>92</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I30" t="n">
         <v>18.29</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>REAL</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>51</v>
-      </c>
-      <c r="E29" t="n">
-        <v>50</v>
-      </c>
-      <c r="F29" t="n">
-        <v>52</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>POLA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>110</v>
-      </c>
-      <c r="E30" t="n">
-        <v>120</v>
-      </c>
-      <c r="F30" t="n">
-        <v>121</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
     <row r="31">
-      <c r="A31" s="8" t="n">
+      <c r="A31" s="7" t="n">
         <v>46303</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2388,7 +2194,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="7" t="n">
         <v>46303</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2425,7 +2231,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="A33" s="7" t="n">
         <v>46303</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2435,17 +2241,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>POLA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1505</v>
+        <v>110</v>
       </c>
       <c r="E33" t="n">
-        <v>1800</v>
+        <v>120</v>
       </c>
       <c r="F33" t="n">
-        <v>1880</v>
+        <v>121</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2459,7 +2265,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="7" t="n">
         <v>46304</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2496,7 +2302,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="n">
+      <c r="A35" s="7" t="n">
         <v>46304</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2506,173 +2312,173 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>905</v>
+      </c>
+      <c r="E35" t="n">
+        <v>985</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>12.57</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>MPXL</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D36" t="n">
         <v>316</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E36" t="n">
         <v>290</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F36" t="n">
         <v>332</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>SUSPENDED</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="n">
+    <row r="37">
+      <c r="A37" s="7" t="n">
         <v>46304</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Jumat</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>PEVE</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>412</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>398</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>398</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="n">
+    <row r="38">
+      <c r="A38" s="7" t="n">
         <v>46304</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Jumat</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>ARII</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
         <v>452</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E38" t="n">
         <v>530</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F38" t="n">
         <v>565</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I38" t="n">
         <v>5.54</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="n">
+    <row r="39">
+      <c r="A39" s="7" t="n">
         <v>46304</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Jumat</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>PGLI</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D39" t="n">
         <v>396</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E39" t="n">
         <v>402</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F39" t="n">
         <v>426</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>SUSPENDED</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Jumat</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SAFE</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>905</v>
-      </c>
-      <c r="E39" t="n">
-        <v>985</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1120</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>12.57</v>
-      </c>
-    </row>
     <row r="40">
-      <c r="A40" s="8" t="n">
+      <c r="A40" s="7" t="n">
         <v>46307</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2682,17 +2488,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2140</v>
+        <v>980</v>
       </c>
       <c r="E40" t="n">
-        <v>2270</v>
+        <v>1005</v>
       </c>
       <c r="F40" t="n">
-        <v>2670</v>
+        <v>1115</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2701,15 +2507,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>16.44</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="n">
+      <c r="A41" s="7" t="n">
         <v>46307</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2746,7 +2549,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="7" t="n">
         <v>46307</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2756,17 +2559,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>980</v>
+        <v>2140</v>
       </c>
       <c r="E42" t="n">
-        <v>1005</v>
+        <v>2270</v>
       </c>
       <c r="F42" t="n">
-        <v>1115</v>
+        <v>2670</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2775,333 +2578,336 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>16.44</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2670</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3250</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3330</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ZONE</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>810</v>
+      </c>
+      <c r="E44" t="n">
+        <v>890</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>SUSPENDED</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Selasa</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ZONE</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>810</v>
-      </c>
-      <c r="E43" t="n">
-        <v>890</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G43" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SBMA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>144</v>
+      </c>
+      <c r="E45" t="n">
+        <v>142</v>
+      </c>
+      <c r="F45" t="n">
+        <v>142</v>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Selasa</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>BIKE</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>2670</v>
-      </c>
-      <c r="E44" t="n">
-        <v>3250</v>
-      </c>
-      <c r="F44" t="n">
+      <c r="D46" t="n">
         <v>3330</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="E46" t="n">
+        <v>3350</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4160</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>22.94</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PICO</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>194</v>
+      </c>
+      <c r="E47" t="n">
+        <v>210</v>
+      </c>
+      <c r="F47" t="n">
+        <v>220</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4160</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4370</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4930</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Rabu</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>BIKE</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>3330</v>
-      </c>
-      <c r="E45" t="n">
-        <v>3350</v>
-      </c>
-      <c r="F45" t="n">
-        <v>4160</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>22.94</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Rabu</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>PICO</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>194</v>
-      </c>
-      <c r="E46" t="n">
-        <v>210</v>
-      </c>
-      <c r="F46" t="n">
-        <v>220</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="I48" t="n">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>GRPH</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>130</v>
+      </c>
+      <c r="E49" t="n">
+        <v>127</v>
+      </c>
+      <c r="F49" t="n">
+        <v>130</v>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Rabu</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>SBMA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>144</v>
-      </c>
-      <c r="E47" t="n">
-        <v>142</v>
-      </c>
-      <c r="F47" t="n">
-        <v>142</v>
-      </c>
-      <c r="G47" t="inlineStr">
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>107</v>
+      </c>
+      <c r="E50" t="n">
+        <v>105</v>
+      </c>
+      <c r="F50" t="n">
+        <v>115</v>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="n">
+    <row r="51">
+      <c r="A51" s="7" t="n">
         <v>46310</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Kamis</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>TRON</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D51" t="n">
         <v>101</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E51" t="n">
         <v>101</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F51" t="n">
         <v>101</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I51" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>107</v>
-      </c>
-      <c r="E49" t="n">
-        <v>105</v>
-      </c>
-      <c r="F49" t="n">
-        <v>115</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>BIKE</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4160</v>
-      </c>
-      <c r="E50" t="n">
-        <v>4370</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4930</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>11.69</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>GRPH</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>130</v>
-      </c>
-      <c r="E51" t="n">
-        <v>127</v>
-      </c>
-      <c r="F51" t="n">
-        <v>130</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
-      <c r="A52" s="8" t="n">
+      <c r="A52" s="7" t="n">
         <v>46311</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3135,7 +2941,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="n">
+      <c r="A53" s="7" t="n">
         <v>46311</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3169,7 +2975,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="n">
+      <c r="A54" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3179,17 +2985,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>105</v>
+        <v>1955</v>
       </c>
       <c r="E54" t="n">
-        <v>98</v>
+        <v>1820</v>
       </c>
       <c r="F54" t="n">
-        <v>98</v>
+        <v>1820</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3203,7 +3009,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="8" t="n">
+      <c r="A55" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3213,17 +3019,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1955</v>
+        <v>990</v>
       </c>
       <c r="E55" t="n">
-        <v>1820</v>
+        <v>925</v>
       </c>
       <c r="F55" t="n">
-        <v>1820</v>
+        <v>925</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3237,7 +3043,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="8" t="n">
+      <c r="A56" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3274,7 +3080,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="n">
+      <c r="A57" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3284,17 +3090,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>990</v>
+        <v>105</v>
       </c>
       <c r="E57" t="n">
-        <v>925</v>
+        <v>98</v>
       </c>
       <c r="F57" t="n">
-        <v>925</v>
+        <v>98</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3308,7 +3114,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="n">
+      <c r="A58" s="7" t="n">
         <v>46315</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3345,7 +3151,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="8" t="n">
+      <c r="A59" s="7" t="n">
         <v>46316</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3382,7 +3188,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="8" t="n">
+      <c r="A60" s="7" t="n">
         <v>46316</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3416,6 +3222,40 @@
       </c>
       <c r="I60" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>118</v>
+      </c>
+      <c r="E61" t="n">
+        <v>113</v>
+      </c>
+      <c r="F61" t="n">
+        <v>140</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3423,7 +3263,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I60">
+  <conditionalFormatting sqref="I5:I61">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -520,7 +520,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-22 19:46</t>
+          <t>Dibuat: 2026-10-22 20:17</t>
         </is>
       </c>
     </row>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -111,6 +111,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-22 20:17</t>
+          <t>Dibuat: 2026-10-23 20:10</t>
         </is>
       </c>
     </row>
@@ -588,7 +591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -648,7 +651,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -742,10 +745,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -758,28 +772,252 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-23</t>
+          <t>Prediksi untuk: 2026-10-26</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Kode</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Value (M)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Ret1d%</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Ret5d%</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Range%</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>VolZ</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Px&gt;sma20%</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Match</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tidak ada kandidat</t>
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>TOBA</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>520</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>WMPP</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>WMUU</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>73</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>KUAT</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>380</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -914,10 +1152,10 @@
           <t>Minggu 1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>46293</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -968,10 +1206,10 @@
           <t>Minggu 2</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>46300</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1022,10 +1260,10 @@
           <t>Minggu 3</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>46307</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1076,19 +1314,19 @@
           <t>Minggu 4</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>46318</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-19 s/d 2026-10-22</t>
+          <t>2026-10-19 s/d 2026-10-23</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
         <v>4</v>
@@ -1109,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1155,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1469,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1265,7 +1503,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1299,7 +1537,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1333,7 +1571,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1370,7 +1608,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1407,7 +1645,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1444,7 +1682,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1481,7 +1719,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1518,7 +1756,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1555,7 +1793,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1589,7 +1827,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1626,7 +1864,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1663,7 +1901,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1697,7 +1935,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1731,7 +1969,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1768,7 +2006,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1805,7 +2043,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1842,7 +2080,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1876,7 +2114,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1913,7 +2151,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1923,102 +2161,102 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>PKPK</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6800</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6850</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7150</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>AIMS</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D25" t="n">
         <v>825</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E25" t="n">
         <v>910</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>1030</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>SUSPENDED</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
+    <row r="26">
+      <c r="A26" s="8" t="n">
         <v>46302</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Rabu</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>IATA</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D26" t="n">
         <v>115</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>115</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>115</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>SL</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>46302</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Rabu</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PKPK</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>6800</v>
-      </c>
-      <c r="E26" t="n">
-        <v>6850</v>
-      </c>
-      <c r="F26" t="n">
-        <v>7150</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2052,7 +2290,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2062,423 +2300,423 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>AKKU</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>71</v>
+      </c>
+      <c r="E28" t="n">
+        <v>77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>92</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>18.29</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>REAL</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D29" t="n">
         <v>51</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E29" t="n">
         <v>50</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F29" t="n">
         <v>52</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
+    <row r="30">
+      <c r="A30" s="8" t="n">
         <v>46303</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Kamis</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>BIKE</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>1505</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E30" t="n">
         <v>1800</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F30" t="n">
         <v>1880</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>SUSPENDED</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
+    <row r="31">
+      <c r="A31" s="8" t="n">
         <v>46303</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Kamis</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AKKU</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>71</v>
-      </c>
-      <c r="E30" t="n">
-        <v>77</v>
-      </c>
-      <c r="F30" t="n">
-        <v>92</v>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>POLA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>110</v>
+      </c>
+      <c r="E31" t="n">
+        <v>120</v>
+      </c>
+      <c r="F31" t="n">
+        <v>121</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INCI</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1065</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>18.29</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="I32" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
         <v>46303</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Kamis</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>INCI</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1025</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1030</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1065</v>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HELI</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>342</v>
+      </c>
+      <c r="E33" t="n">
+        <v>342</v>
+      </c>
+      <c r="F33" t="n">
+        <v>402</v>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>2.36</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>HELI</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>342</v>
-      </c>
-      <c r="E32" t="n">
-        <v>342</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="I33" t="n">
+        <v>16.37</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MPXL</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>316</v>
+      </c>
+      <c r="E34" t="n">
+        <v>290</v>
+      </c>
+      <c r="F34" t="n">
+        <v>332</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PEVE</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>412</v>
+      </c>
+      <c r="E35" t="n">
+        <v>398</v>
+      </c>
+      <c r="F35" t="n">
+        <v>398</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_DOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ARII</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>452</v>
+      </c>
+      <c r="E36" t="n">
+        <v>530</v>
+      </c>
+      <c r="F36" t="n">
+        <v>565</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>5.54</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>905</v>
+      </c>
+      <c r="E37" t="n">
+        <v>985</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>12.57</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PGLI</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>396</v>
+      </c>
+      <c r="E38" t="n">
         <v>402</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="F38" t="n">
+        <v>426</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MCAS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>284</v>
+      </c>
+      <c r="E39" t="n">
+        <v>310</v>
+      </c>
+      <c r="F39" t="n">
+        <v>326</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>16.37</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>POLA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>110</v>
-      </c>
-      <c r="E33" t="n">
-        <v>120</v>
-      </c>
-      <c r="F33" t="n">
-        <v>121</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Jumat</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>MCAS</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>284</v>
-      </c>
-      <c r="E34" t="n">
-        <v>310</v>
-      </c>
-      <c r="F34" t="n">
-        <v>326</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
+      <c r="I39" t="n">
         <v>4.11</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Jumat</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SAFE</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>905</v>
-      </c>
-      <c r="E35" t="n">
-        <v>985</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1120</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>12.57</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Jumat</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>MPXL</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>316</v>
-      </c>
-      <c r="E36" t="n">
-        <v>290</v>
-      </c>
-      <c r="F36" t="n">
-        <v>332</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Jumat</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>PEVE</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>412</v>
-      </c>
-      <c r="E37" t="n">
-        <v>398</v>
-      </c>
-      <c r="F37" t="n">
-        <v>398</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Jumat</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ARII</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>452</v>
-      </c>
-      <c r="E38" t="n">
-        <v>530</v>
-      </c>
-      <c r="F38" t="n">
-        <v>565</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>5.54</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Jumat</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>PGLI</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>396</v>
-      </c>
-      <c r="E39" t="n">
-        <v>402</v>
-      </c>
-      <c r="F39" t="n">
-        <v>426</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2512,7 +2750,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2549,7 +2787,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2586,7 +2824,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2596,213 +2834,213 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>ZONE</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>810</v>
+      </c>
+      <c r="E43" t="n">
+        <v>890</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>BIKE</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D44" t="n">
         <v>2670</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E44" t="n">
         <v>3250</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F44" t="n">
         <v>3330</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>TP</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="I44" t="n">
         <v>1.44</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Selasa</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ZONE</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>810</v>
-      </c>
-      <c r="E44" t="n">
-        <v>890</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G44" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3330</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3350</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4160</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>22.94</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PICO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>194</v>
+      </c>
+      <c r="E46" t="n">
+        <v>210</v>
+      </c>
+      <c r="F46" t="n">
+        <v>220</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SBMA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>144</v>
+      </c>
+      <c r="E47" t="n">
+        <v>142</v>
+      </c>
+      <c r="F47" t="n">
+        <v>142</v>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Rabu</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>SBMA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>144</v>
-      </c>
-      <c r="E45" t="n">
-        <v>142</v>
-      </c>
-      <c r="F45" t="n">
-        <v>142</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Rabu</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>BIKE</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>3330</v>
-      </c>
-      <c r="E46" t="n">
-        <v>3350</v>
-      </c>
-      <c r="F46" t="n">
-        <v>4160</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>22.94</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Rabu</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>PICO</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>194</v>
-      </c>
-      <c r="E47" t="n">
-        <v>210</v>
-      </c>
-      <c r="F47" t="n">
-        <v>220</v>
-      </c>
-      <c r="G47" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TRON</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>101</v>
+      </c>
+      <c r="E48" t="n">
+        <v>101</v>
+      </c>
+      <c r="F48" t="n">
+        <v>101</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>BIKE</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4160</v>
-      </c>
-      <c r="E48" t="n">
-        <v>4370</v>
-      </c>
-      <c r="F48" t="n">
-        <v>4930</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>11.69</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2836,7 +3074,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2846,68 +3084,68 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4160</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4370</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4930</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D51" t="n">
         <v>107</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E51" t="n">
         <v>105</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F51" t="n">
         <v>115</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>SKIP_GAP_DOWN</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Kamis</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>TRON</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>101</v>
-      </c>
-      <c r="E51" t="n">
-        <v>101</v>
-      </c>
-      <c r="F51" t="n">
-        <v>101</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>-3</v>
-      </c>
-    </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2941,7 +3179,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2975,7 +3213,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="8" t="n">
         <v>46314</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2985,136 +3223,136 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E54" t="n">
+        <v>4020</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4020</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AKKU</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>105</v>
+      </c>
+      <c r="E55" t="n">
+        <v>98</v>
+      </c>
+      <c r="F55" t="n">
+        <v>98</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AIMS</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>990</v>
+      </c>
+      <c r="E56" t="n">
+        <v>925</v>
+      </c>
+      <c r="F56" t="n">
+        <v>925</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>ALDO</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D57" t="n">
         <v>1955</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E57" t="n">
         <v>1820</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F57" t="n">
         <v>1820</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>SUSPENDED</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Senin</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>AIMS</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>990</v>
-      </c>
-      <c r="E55" t="n">
-        <v>925</v>
-      </c>
-      <c r="F55" t="n">
-        <v>925</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Senin</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>TRUK</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>3220</v>
-      </c>
-      <c r="E56" t="n">
-        <v>4020</v>
-      </c>
-      <c r="F56" t="n">
-        <v>4020</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Senin</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AKKU</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>105</v>
-      </c>
-      <c r="E57" t="n">
-        <v>98</v>
-      </c>
-      <c r="F57" t="n">
-        <v>98</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
-      </c>
-    </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="8" t="n">
         <v>46315</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3151,7 +3389,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="8" t="n">
         <v>46316</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3188,7 +3426,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="8" t="n">
         <v>46316</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3225,7 +3463,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="8" t="n">
         <v>46317</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3255,6 +3493,40 @@
       <c r="H61" t="inlineStr">
         <is>
           <t>SKIP_GAP_DOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>137</v>
+      </c>
+      <c r="E62" t="n">
+        <v>183</v>
+      </c>
+      <c r="F62" t="n">
+        <v>183</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3535,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I61">
+  <conditionalFormatting sqref="I5:I62">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -506,10 +506,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -523,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-23 20:10</t>
+          <t>Dibuat: 2026-10-26 20:36</t>
         </is>
       </c>
     </row>
@@ -559,172 +559,196 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TP High-1% | SL -3% (incl. fee)</t>
+          <t>TRAIL 0.5% (dari peak) | SL -3% | Max hold 30d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Gap Filter T+1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2% – 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Quality Filter</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ATR &gt;= 3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Entry (T+1)</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>RINGKASAN SINYAL</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Total Sinyal</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Tereksekusi</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>30</v>
-      </c>
+      <c r="B11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TP (high -1%)</t>
+          <t>Total Sinyal</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SL</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>4</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tereksekusi</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Close (fallback)</t>
+          <t xml:space="preserve">  TRAIL (profit)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Skip (gap down)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>12</v>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SL</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Suspended</t>
+          <t xml:space="preserve">  HOLD (max days)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Skip Gap (out of range)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B19" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>PERFORMA</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Win Rate</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>86.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Total P/L</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>+241.63%</t>
-        </is>
-      </c>
+      <c r="B21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total P/L</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>+335.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Avg P/L per Trade</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>+8.05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>+7.79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>[OK] LAYAK</t>
         </is>
@@ -745,21 +769,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -772,7 +797,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-26</t>
+          <t>Prediksi untuk: 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -833,6 +858,11 @@
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>ATR%</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
@@ -843,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -852,33 +882,36 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>TOBA</t>
+          <t>TMPO</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>520</v>
+        <v>189</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>86.79000000000001</v>
+        <v>38.93</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>25</v>
+        <v>19.62</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>53.85</v>
+        <v>11.83</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>18.85</v>
+        <v>17.99</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>20.01</v>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>AB</t>
+        <v>17.54</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
         </is>
       </c>
     </row>
@@ -887,42 +920,45 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>ELITE</t>
+          <t>KUAT</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>WMPP</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>26</v>
+        <v>430</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>10.49</v>
+        <v>41.1</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>18.18</v>
+        <v>14.97</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>30</v>
+        <v>62.88</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>26.92</v>
+        <v>20.47</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>3.14</v>
+        <v>1.72</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>10.4</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -931,42 +967,45 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ELITE</t>
+          <t>KUAT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>WMUU</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>8.26</v>
+        <v>7.92</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>33.33</v>
+        <v>11.11</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>63.64</v>
+        <v>26.76</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>25</v>
+        <v>11.11</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>22.03</v>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
+        <v>17.42</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>AC</t>
         </is>
       </c>
     </row>
@@ -975,7 +1014,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -984,40 +1023,325 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>TOBA</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>380</v>
+        <v>505</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6.12</v>
+        <v>130.61</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>25</v>
+        <v>-2.88</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>26.67</v>
+        <v>59.81</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>18.42</v>
+        <v>23.76</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>2.3</v>
+        <v>2.81</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>16.24</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>KUAT</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>BLES</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>228</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>15.77</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>WMUU</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>36.11</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>MBSS</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>4280</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>139</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>51.09</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>68.38</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>147</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>58.06</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>SEDANG</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>SBMA</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>27.12</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1029,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1039,10 +1363,10 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
@@ -1102,7 +1426,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -1112,12 +1436,12 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>Skip</t>
+          <t>Skip Gap</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -1164,16 +1488,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1182,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1194,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="O5" t="n">
-        <v>25.62</v>
+        <v>21.64</v>
       </c>
       <c r="P5" t="n">
-        <v>12.81</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="6">
@@ -1218,16 +1542,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1236,22 +1560,22 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>94.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="O6" t="n">
-        <v>151.93</v>
+        <v>177.11</v>
       </c>
       <c r="P6" t="n">
-        <v>8.94</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="7">
@@ -1272,16 +1596,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -1290,22 +1614,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>85.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>68.15000000000001</v>
+        <v>85.67</v>
       </c>
       <c r="P7" t="n">
-        <v>9.74</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="8">
@@ -1326,40 +1650,94 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.07</v>
+        <v>41.43</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.02</v>
+        <v>8.289999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Minggu 5</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-26 s/d 2026-10-26</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>60</v>
+      </c>
+      <c r="O9" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>
@@ -1367,7 +1745,7 @@
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <conditionalFormatting sqref="O5:O8">
+  <conditionalFormatting sqref="O5:O9">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1375,7 +1753,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P8">
+  <conditionalFormatting sqref="P5:P9">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1393,18 +1771,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:J207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1417,7 +1796,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>TP High-1% | SL -3% - Tanggal = entry (T+1) - Bulan October 2026</t>
+          <t>TRAIL 0.5% | SL -3% | Gap 2-20% - Bulan October 2026</t>
         </is>
       </c>
     </row>
@@ -1444,25 +1823,30 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>Gap T+1 %</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>High T+1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>P/L %</t>
         </is>
@@ -1479,706 +1863,736 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>HELI</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>478</v>
+        <v>276</v>
       </c>
       <c r="E5" t="n">
-        <v>474</v>
+        <v>0.72</v>
       </c>
       <c r="F5" t="n">
-        <v>474</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>278</v>
+      </c>
+      <c r="G5" t="n">
+        <v>278</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>705</v>
+        <v>234</v>
       </c>
       <c r="E6" t="n">
-        <v>680</v>
+        <v>0.85</v>
       </c>
       <c r="F6" t="n">
-        <v>745</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>236</v>
+      </c>
+      <c r="G6" t="n">
+        <v>292</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4230</v>
+        <v>246</v>
       </c>
       <c r="E7" t="n">
-        <v>4020</v>
+        <v>-2.44</v>
       </c>
       <c r="F7" t="n">
-        <v>4860</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>240</v>
+      </c>
+      <c r="G7" t="n">
+        <v>260</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>MTLA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>740</v>
       </c>
       <c r="E8" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>354</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>740</v>
+      </c>
+      <c r="G8" t="n">
+        <v>745</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>20.02</v>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
-        <v>46297</v>
+        <v>46296</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>470</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
-        <v>525</v>
+        <v>3.12</v>
       </c>
       <c r="F9" t="n">
-        <v>560</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>66</v>
+      </c>
+      <c r="G9" t="n">
+        <v>72</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>5.6</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>RSCH</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>266</v>
+        <v>525</v>
       </c>
       <c r="E10" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>332</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>525</v>
+      </c>
+      <c r="G10" t="n">
+        <v>555</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>9.56</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>ASGR</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3630</v>
+        <v>2520</v>
       </c>
       <c r="E11" t="n">
-        <v>3780</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4480</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>2520</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2540</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>17.33</v>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>404</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>63</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>406</v>
+      </c>
+      <c r="G12" t="n">
+        <v>486</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SOTS</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>630</v>
+        <v>478</v>
       </c>
       <c r="E13" t="n">
-        <v>655</v>
+        <v>-0.84</v>
       </c>
       <c r="F13" t="n">
-        <v>675</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>474</v>
+      </c>
+      <c r="G13" t="n">
+        <v>474</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.02</v>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PPRI</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>186</v>
+        <v>296</v>
       </c>
       <c r="E14" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>196</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>296</v>
+      </c>
+      <c r="G14" t="n">
+        <v>310</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>332</v>
+        <v>6300</v>
       </c>
       <c r="E15" t="n">
-        <v>342</v>
+        <v>-0.79</v>
       </c>
       <c r="F15" t="n">
-        <v>378</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>6250</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6250</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>9.42</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>MOLI</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>424</v>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>0.47</v>
       </c>
       <c r="F16" t="n">
-        <v>74</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>426</v>
+      </c>
+      <c r="G16" t="n">
+        <v>426</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.18</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WAPO</t>
+          <t>SOSS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>352</v>
+        <v>1180</v>
       </c>
       <c r="E17" t="n">
-        <v>364</v>
+        <v>-5.51</v>
       </c>
       <c r="F17" t="n">
-        <v>400</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>1115</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1160</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Kamis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4400</v>
+        <v>1130</v>
       </c>
       <c r="E18" t="n">
-        <v>4220</v>
+        <v>-0.44</v>
       </c>
       <c r="F18" t="n">
-        <v>4630</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>1125</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1410</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>530</v>
+        <v>4230</v>
       </c>
       <c r="E19" t="n">
-        <v>550</v>
+        <v>-4.96</v>
       </c>
       <c r="F19" t="n">
-        <v>660</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>4020</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4860</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>18.8</v>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="E20" t="n">
-        <v>434</v>
+        <v>0.9</v>
       </c>
       <c r="F20" t="n">
-        <v>515</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>448</v>
+      </c>
+      <c r="G20" t="n">
+        <v>466</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>17.48</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>350</v>
+        <v>422</v>
       </c>
       <c r="E21" t="n">
-        <v>360</v>
+        <v>1.42</v>
       </c>
       <c r="F21" t="n">
-        <v>404</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>428</v>
+      </c>
+      <c r="G21" t="n">
+        <v>480</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>11.1</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASLI</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="E22" t="n">
-        <v>496</v>
+        <v>11.7</v>
       </c>
       <c r="F22" t="n">
-        <v>540</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>525</v>
+      </c>
+      <c r="G22" t="n">
+        <v>560</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>6.13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
-        <v>46301</v>
+        <v>46297</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>SINI</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>18300</v>
       </c>
       <c r="E23" t="n">
-        <v>55</v>
+        <v>-4.37</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>17500</v>
+      </c>
+      <c r="G23" t="n">
+        <v>17875</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>6.2</v>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6800</v>
+        <v>3520</v>
       </c>
       <c r="E24" t="n">
-        <v>6850</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>7150</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>3520</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3710</v>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>SUSPENDED</t>
         </is>
@@ -2186,646 +2600,691 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>825</v>
+        <v>284</v>
       </c>
       <c r="E25" t="n">
-        <v>910</v>
+        <v>0.7</v>
       </c>
       <c r="F25" t="n">
-        <v>1030</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>286</v>
+      </c>
+      <c r="G25" t="n">
+        <v>304</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IATA</t>
+          <t>MTLA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>115</v>
+        <v>690</v>
       </c>
       <c r="E26" t="n">
-        <v>115</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>115</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>630</v>
+      </c>
+      <c r="G26" t="n">
+        <v>725</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>-3</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="n">
-        <v>46302</v>
+        <v>46297</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>655</v>
+        <v>705</v>
       </c>
       <c r="E27" t="n">
-        <v>640</v>
+        <v>-3.55</v>
       </c>
       <c r="F27" t="n">
-        <v>640</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>680</v>
+      </c>
+      <c r="G27" t="n">
+        <v>745</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>46303</v>
+        <v>46297</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>UNIQ</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="E28" t="n">
-        <v>77</v>
+        <v>-1.46</v>
       </c>
       <c r="F28" t="n">
-        <v>92</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>135</v>
+      </c>
+      <c r="G28" t="n">
+        <v>147</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>18.29</v>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
-        <v>46303</v>
+        <v>46297</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>51</v>
+        <v>1155</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>3.9</v>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>1200</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1290</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
-        </is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>6.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>46303</v>
+        <v>46297</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Jumat</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1505</v>
+        <v>290</v>
       </c>
       <c r="E30" t="n">
-        <v>1800</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1880</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>292</v>
+      </c>
+      <c r="G30" t="n">
+        <v>354</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Senin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>POLA</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>110</v>
+        <v>332</v>
       </c>
       <c r="E31" t="n">
-        <v>120</v>
+        <v>2.41</v>
       </c>
       <c r="F31" t="n">
-        <v>121</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>340</v>
+      </c>
+      <c r="G31" t="n">
+        <v>414</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>21.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Senin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INCI</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1025</v>
+        <v>710</v>
       </c>
       <c r="E32" t="n">
-        <v>1030</v>
+        <v>1.41</v>
       </c>
       <c r="F32" t="n">
-        <v>1065</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>720</v>
+      </c>
+      <c r="G32" t="n">
+        <v>885</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>2.36</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="n">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Senin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HELI</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>342</v>
+        <v>266</v>
       </c>
       <c r="E33" t="n">
-        <v>342</v>
+        <v>12.78</v>
       </c>
       <c r="F33" t="n">
-        <v>402</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>300</v>
+      </c>
+      <c r="G33" t="n">
+        <v>332</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>16.37</v>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>10.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Senin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>SAMF</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>316</v>
+        <v>360</v>
       </c>
       <c r="E34" t="n">
-        <v>290</v>
+        <v>3.33</v>
       </c>
       <c r="F34" t="n">
-        <v>332</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>372</v>
+      </c>
+      <c r="G34" t="n">
+        <v>386</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="n">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Senin</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PEVE</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>412</v>
+        <v>3760</v>
       </c>
       <c r="E35" t="n">
-        <v>398</v>
+        <v>-1.33</v>
       </c>
       <c r="F35" t="n">
-        <v>398</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>3710</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3990</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Senin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>452</v>
+        <v>302</v>
       </c>
       <c r="E36" t="n">
-        <v>530</v>
+        <v>0.66</v>
       </c>
       <c r="F36" t="n">
-        <v>565</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>304</v>
+      </c>
+      <c r="G36" t="n">
+        <v>310</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>5.54</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Senin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>905</v>
+        <v>470</v>
       </c>
       <c r="E37" t="n">
-        <v>985</v>
+        <v>2.55</v>
       </c>
       <c r="F37" t="n">
-        <v>1120</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>482</v>
+      </c>
+      <c r="G37" t="n">
+        <v>525</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>12.57</v>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46304</v>
+        <v>46300</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Senin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>ASGR</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>396</v>
+        <v>2520</v>
       </c>
       <c r="E38" t="n">
-        <v>402</v>
+        <v>0.4</v>
       </c>
       <c r="F38" t="n">
-        <v>426</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>2530</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2550</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n">
-        <v>46304</v>
+        <v>46301</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MCAS</t>
+          <t>ASLI</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>284</v>
+        <v>486</v>
       </c>
       <c r="E39" t="n">
-        <v>310</v>
+        <v>2.06</v>
       </c>
       <c r="F39" t="n">
-        <v>326</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>496</v>
+      </c>
+      <c r="G39" t="n">
+        <v>540</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>4.11</v>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46307</v>
+        <v>46301</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>BLUE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>980</v>
+        <v>3590</v>
       </c>
       <c r="E40" t="n">
-        <v>1005</v>
+        <v>1.11</v>
       </c>
       <c r="F40" t="n">
-        <v>1115</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>3630</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4100</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n">
-        <v>46307</v>
+        <v>46301</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>MPIX</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="E41" t="n">
-        <v>87</v>
+        <v>2.68</v>
       </c>
       <c r="F41" t="n">
-        <v>101</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>230</v>
+      </c>
+      <c r="G41" t="n">
+        <v>232</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>14.93</v>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46307</v>
+        <v>46301</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2140</v>
+        <v>1270</v>
       </c>
       <c r="E42" t="n">
-        <v>2270</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>2670</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>1270</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1280</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>16.44</v>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n">
-        <v>46308</v>
+        <v>46301</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2834,32 +3293,38 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ZONE</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>810</v>
+        <v>530</v>
       </c>
       <c r="E43" t="n">
-        <v>890</v>
+        <v>3.77</v>
       </c>
       <c r="F43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>550</v>
+      </c>
+      <c r="G43" t="n">
+        <v>660</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>19.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46308</v>
+        <v>46301</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2868,529 +3333,565 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2670</v>
+        <v>61</v>
       </c>
       <c r="E44" t="n">
-        <v>3250</v>
+        <v>1.64</v>
       </c>
       <c r="F44" t="n">
-        <v>3330</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="G44" t="n">
+        <v>63</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>1.44</v>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n">
-        <v>46309</v>
+        <v>46301</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3330</v>
+        <v>71</v>
       </c>
       <c r="E45" t="n">
-        <v>3350</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>4160</v>
-      </c>
-      <c r="G45" t="inlineStr">
+        <v>71</v>
+      </c>
+      <c r="G45" t="n">
+        <v>74</v>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>22.94</v>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46309</v>
+        <v>46301</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PICO</t>
+          <t>AMAN</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="E46" t="n">
-        <v>210</v>
+        <v>0.9</v>
       </c>
       <c r="F46" t="n">
-        <v>220</v>
-      </c>
-      <c r="G46" t="inlineStr">
+        <v>224</v>
+      </c>
+      <c r="G46" t="n">
+        <v>224</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>3.71</v>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n">
-        <v>46309</v>
+        <v>46301</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rabu</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SBMA</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>144</v>
+        <v>438</v>
       </c>
       <c r="E47" t="n">
-        <v>142</v>
+        <v>1.37</v>
       </c>
       <c r="F47" t="n">
-        <v>142</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>444</v>
+      </c>
+      <c r="G47" t="n">
+        <v>450</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46310</v>
+        <v>46301</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>101</v>
+        <v>332</v>
       </c>
       <c r="E48" t="n">
-        <v>101</v>
+        <v>3.01</v>
       </c>
       <c r="F48" t="n">
-        <v>101</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>342</v>
+      </c>
+      <c r="G48" t="n">
+        <v>378</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>-3</v>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n">
-        <v>46310</v>
+        <v>46301</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GRPH</t>
+          <t>DAAZ</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>130</v>
+        <v>2200</v>
       </c>
       <c r="E49" t="n">
-        <v>127</v>
+        <v>-0.45</v>
       </c>
       <c r="F49" t="n">
-        <v>130</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+        <v>2190</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46310</v>
+        <v>46301</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4160</v>
+        <v>350</v>
       </c>
       <c r="E50" t="n">
-        <v>4370</v>
+        <v>2.86</v>
       </c>
       <c r="F50" t="n">
-        <v>4930</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>360</v>
+      </c>
+      <c r="G50" t="n">
+        <v>404</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>11.69</v>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>11.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n">
-        <v>46310</v>
+        <v>46301</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>WAPO</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>107</v>
+        <v>352</v>
       </c>
       <c r="E51" t="n">
-        <v>105</v>
+        <v>3.41</v>
       </c>
       <c r="F51" t="n">
-        <v>115</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>364</v>
+      </c>
+      <c r="G51" t="n">
+        <v>400</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46311</v>
+        <v>46301</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SBMA</t>
+          <t>DEWI</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="E52" t="n">
-        <v>126</v>
+        <v>0.77</v>
       </c>
       <c r="F52" t="n">
-        <v>131</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>262</v>
+      </c>
+      <c r="G52" t="n">
+        <v>262</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n">
-        <v>46311</v>
+        <v>46301</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jumat</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2580</v>
+        <v>4400</v>
       </c>
       <c r="E53" t="n">
-        <v>3220</v>
+        <v>-4.09</v>
       </c>
       <c r="F53" t="n">
-        <v>3220</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>4220</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4630</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46314</v>
+        <v>46301</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>PPRI</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3220</v>
+        <v>186</v>
       </c>
       <c r="E54" t="n">
-        <v>4020</v>
+        <v>-3.23</v>
       </c>
       <c r="F54" t="n">
-        <v>4020</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>180</v>
+      </c>
+      <c r="G54" t="n">
+        <v>196</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>-3</v>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n">
-        <v>46314</v>
+        <v>46301</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>SOTS</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>105</v>
+        <v>630</v>
       </c>
       <c r="E55" t="n">
-        <v>98</v>
+        <v>3.97</v>
       </c>
       <c r="F55" t="n">
-        <v>98</v>
-      </c>
-      <c r="G55" t="inlineStr">
+        <v>655</v>
+      </c>
+      <c r="G55" t="n">
+        <v>675</v>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
-        </is>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2.54</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46314</v>
+        <v>46301</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Selasa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>990</v>
+        <v>412</v>
       </c>
       <c r="E56" t="n">
-        <v>925</v>
+        <v>5.34</v>
       </c>
       <c r="F56" t="n">
-        <v>925</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>434</v>
+      </c>
+      <c r="G56" t="n">
+        <v>515</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>18.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n">
-        <v>46314</v>
+        <v>46302</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Senin</t>
+          <t>Rabu</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1955</v>
+        <v>370</v>
       </c>
       <c r="E57" t="n">
-        <v>1820</v>
+        <v>0.54</v>
       </c>
       <c r="F57" t="n">
-        <v>1820</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
+        <v>372</v>
+      </c>
+      <c r="G57" t="n">
+        <v>374</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46315</v>
+        <v>46302</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Selasa</t>
+          <t>Rabu</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>IATA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4020</v>
+        <v>115</v>
       </c>
       <c r="E58" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>5025</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>115</v>
+      </c>
+      <c r="G58" t="n">
+        <v>115</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>-3</v>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n">
-        <v>46316</v>
+        <v>46302</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3399,35 +3900,35 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>348</v>
+        <v>655</v>
       </c>
       <c r="E59" t="n">
-        <v>350</v>
+        <v>-2.29</v>
       </c>
       <c r="F59" t="n">
-        <v>358</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>640</v>
+      </c>
+      <c r="G59" t="n">
+        <v>640</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>1.26</v>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46316</v>
+        <v>46302</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3436,106 +3937,5567 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>KLAS</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5025</v>
+        <v>82</v>
       </c>
       <c r="E60" t="n">
-        <v>5925</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>6025</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>82</v>
+      </c>
+      <c r="G60" t="n">
+        <v>90</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>0.67</v>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n">
-        <v>46317</v>
+        <v>46302</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kamis</t>
+          <t>Rabu</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>118</v>
+        <v>4400</v>
       </c>
       <c r="E61" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>140</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+        <v>4400</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4500</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>SKIP_GAP_DOWN</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PKPK</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>6800</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F62" t="n">
+        <v>6850</v>
+      </c>
+      <c r="G62" t="n">
+        <v>7150</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PCAR</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>70</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F63" t="n">
+        <v>72</v>
+      </c>
+      <c r="G63" t="n">
+        <v>83</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AIMS</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>825</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>910</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BDKR</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>210</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>210</v>
+      </c>
+      <c r="G65" t="n">
+        <v>230</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PGLI</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>318</v>
+      </c>
+      <c r="E66" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="F66" t="n">
+        <v>360</v>
+      </c>
+      <c r="G66" t="n">
+        <v>396</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BALI</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1530</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>WAPO</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>326</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>326</v>
+      </c>
+      <c r="G68" t="n">
+        <v>344</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SMLE</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>320</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F69" t="n">
+        <v>324</v>
+      </c>
+      <c r="G69" t="n">
+        <v>324</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BLUE</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>3660</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3740</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3910</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>6825</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="F71" t="n">
+        <v>7525</v>
+      </c>
+      <c r="G71" t="n">
+        <v>7975</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ASLI</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>500</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>500</v>
+      </c>
+      <c r="G72" t="n">
+        <v>500</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>INCI</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MPIX</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>220</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>220</v>
+      </c>
+      <c r="G74" t="n">
+        <v>224</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KKES</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>77</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>85</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>REAL</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>51</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="F76" t="n">
+        <v>50</v>
+      </c>
+      <c r="G76" t="n">
+        <v>52</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MBSS</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="F77" t="n">
+        <v>4440</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4440</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HELI</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>342</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>342</v>
+      </c>
+      <c r="G78" t="n">
+        <v>402</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PCAR</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>80</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>80</v>
+      </c>
+      <c r="G79" t="n">
+        <v>85</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>KDTN</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>605</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-2.48</v>
+      </c>
+      <c r="F80" t="n">
+        <v>590</v>
+      </c>
+      <c r="G80" t="n">
+        <v>610</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>POLA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>110</v>
+      </c>
+      <c r="E81" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="F81" t="n">
+        <v>120</v>
+      </c>
+      <c r="G81" t="n">
+        <v>121</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>354</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="F82" t="n">
+        <v>350</v>
+      </c>
+      <c r="G82" t="n">
+        <v>374</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>7550</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F83" t="n">
+        <v>7850</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8700</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>10.27</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VICI</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1230</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1255</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1320</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BLUE</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3900</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F85" t="n">
+        <v>3930</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4510</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ENAK</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>214</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>214</v>
+      </c>
+      <c r="G86" t="n">
+        <v>216</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E87" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1880</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ASLI</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>464</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="F88" t="n">
+        <v>480</v>
+      </c>
+      <c r="G88" t="n">
+        <v>496</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BDKR</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>216</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>216</v>
+      </c>
+      <c r="G89" t="n">
+        <v>218</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>8150</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>8150</v>
+      </c>
+      <c r="G90" t="n">
+        <v>8300</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ARII</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>452</v>
+      </c>
+      <c r="E91" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="F91" t="n">
+        <v>530</v>
+      </c>
+      <c r="G91" t="n">
+        <v>565</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1715</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1705</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2140</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MCAS</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>284</v>
+      </c>
+      <c r="E93" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="F93" t="n">
+        <v>310</v>
+      </c>
+      <c r="G93" t="n">
+        <v>326</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PEVE</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>412</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="F94" t="n">
+        <v>398</v>
+      </c>
+      <c r="G94" t="n">
+        <v>398</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BDKR</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>212</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>212</v>
+      </c>
+      <c r="G95" t="n">
+        <v>218</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MPXL</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>316</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-8.23</v>
+      </c>
+      <c r="F96" t="n">
+        <v>290</v>
+      </c>
+      <c r="G96" t="n">
+        <v>332</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>GTRA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>304</v>
+      </c>
+      <c r="E97" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="F97" t="n">
+        <v>318</v>
+      </c>
+      <c r="G97" t="n">
+        <v>318</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>905</v>
+      </c>
+      <c r="E98" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="F98" t="n">
+        <v>985</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1120</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>13.14</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PKPK</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>6800</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G99" t="n">
+        <v>7225</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>INCI</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1070</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TEBE</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2690</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-10.78</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2840</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>HELI</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>342</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F102" t="n">
+        <v>348</v>
+      </c>
+      <c r="G102" t="n">
+        <v>352</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VICI</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1295</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1325</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>POLA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>105</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F104" t="n">
+        <v>107</v>
+      </c>
+      <c r="G104" t="n">
+        <v>127</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PGLI</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>396</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F105" t="n">
+        <v>402</v>
+      </c>
+      <c r="G105" t="n">
+        <v>426</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1075</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PEVE</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>384</v>
+      </c>
+      <c r="E107" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="F107" t="n">
+        <v>374</v>
+      </c>
+      <c r="G107" t="n">
+        <v>384</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PCAR</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>90</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>90</v>
+      </c>
+      <c r="G108" t="n">
+        <v>100</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ARII</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>420</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F109" t="n">
+        <v>428</v>
+      </c>
+      <c r="G109" t="n">
+        <v>478</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>2140</v>
+      </c>
+      <c r="E110" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2270</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2670</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>17.03</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>POLA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>108</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F111" t="n">
+        <v>110</v>
+      </c>
+      <c r="G111" t="n">
+        <v>121</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PGLI</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>388</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>388</v>
+      </c>
+      <c r="G112" t="n">
+        <v>434</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MPXL</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>290</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F113" t="n">
+        <v>292</v>
+      </c>
+      <c r="G113" t="n">
+        <v>294</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SMMT</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3990</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G114" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TEBE</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2840</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3100</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>VICI</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E116" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1310</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1445</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TCPI</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E117" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1860</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1865</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>83</v>
+      </c>
+      <c r="E118" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="F118" t="n">
+        <v>87</v>
+      </c>
+      <c r="G118" t="n">
+        <v>101</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>15.51</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MBSS</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>4600</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="n">
+        <v>4600</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4660</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ASPI</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>980</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1005</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1115</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SOSS</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1260</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>DAAZ</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2420</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2940</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DAAZ</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2730</v>
+      </c>
+      <c r="E123" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2720</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2720</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>TEBE</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2850</v>
+      </c>
+      <c r="G124" t="n">
+        <v>3020</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PKPK</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>7650</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>7650</v>
+      </c>
+      <c r="G125" t="n">
+        <v>7675</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SMMT</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>3710</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F126" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G126" t="n">
+        <v>3830</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TCPI</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1780</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2670</v>
+      </c>
+      <c r="E128" t="n">
+        <v>21.72</v>
+      </c>
+      <c r="F128" t="n">
+        <v>3250</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3330</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PGLI</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>376</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>376</v>
+      </c>
+      <c r="G129" t="n">
+        <v>390</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>92</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="F130" t="n">
+        <v>89</v>
+      </c>
+      <c r="G130" t="n">
+        <v>92</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ASPI</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1095</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1120</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>89</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>89</v>
+      </c>
+      <c r="G132" t="n">
+        <v>102</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ARII</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>408</v>
+      </c>
+      <c r="E133" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="F133" t="n">
+        <v>402</v>
+      </c>
+      <c r="G133" t="n">
+        <v>484</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>PCAR</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>98</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F134" t="n">
+        <v>100</v>
+      </c>
+      <c r="G134" t="n">
+        <v>103</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>MINE</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>320</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="F135" t="n">
+        <v>318</v>
+      </c>
+      <c r="G135" t="n">
+        <v>324</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ALDO</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1440</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1750</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>20.92</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>90</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="F137" t="n">
+        <v>86</v>
+      </c>
+      <c r="G137" t="n">
+        <v>115</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SBMA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>144</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="F138" t="n">
+        <v>142</v>
+      </c>
+      <c r="G138" t="n">
+        <v>142</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>TCPI</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2010</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2080</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G140" t="n">
+        <v>7975</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>ARII</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>458</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F141" t="n">
+        <v>464</v>
+      </c>
+      <c r="G141" t="n">
+        <v>494</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SOSS</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1240</v>
+      </c>
+      <c r="E142" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1235</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ASPI</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1015</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1140</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>97</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>97</v>
+      </c>
+      <c r="G144" t="n">
+        <v>102</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PCAR</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>92</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>92</v>
+      </c>
+      <c r="G145" t="n">
+        <v>96</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>PICO</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>194</v>
+      </c>
+      <c r="E146" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="F146" t="n">
+        <v>210</v>
+      </c>
+      <c r="G146" t="n">
+        <v>220</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>3330</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F147" t="n">
+        <v>3350</v>
+      </c>
+      <c r="G147" t="n">
+        <v>4160</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BELI</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>314</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="n">
+        <v>314</v>
+      </c>
+      <c r="G148" t="n">
+        <v>336</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SONA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>3450</v>
+      </c>
+      <c r="E149" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="F149" t="n">
+        <v>3710</v>
+      </c>
+      <c r="G149" t="n">
+        <v>3970</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>6.47</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>107</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="F150" t="n">
+        <v>105</v>
+      </c>
+      <c r="G150" t="n">
+        <v>115</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>102</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="n">
+        <v>102</v>
+      </c>
+      <c r="G151" t="n">
+        <v>127</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TCPI</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1915</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1910</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1910</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>TRON</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>101</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="n">
+        <v>101</v>
+      </c>
+      <c r="G153" t="n">
+        <v>101</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>4160</v>
+      </c>
+      <c r="E154" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="F154" t="n">
+        <v>4370</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4930</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SAFE</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>950</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F155" t="n">
+        <v>965</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1020</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>BAIK</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>282</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="n">
+        <v>282</v>
+      </c>
+      <c r="G156" t="n">
+        <v>318</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>GRPH</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>130</v>
+      </c>
+      <c r="E157" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="F157" t="n">
+        <v>127</v>
+      </c>
+      <c r="G157" t="n">
+        <v>130</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>HATM</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>670</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F158" t="n">
+        <v>675</v>
+      </c>
+      <c r="G158" t="n">
+        <v>680</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="8" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ALDO</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1565</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1565</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1955</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MPXL</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>310</v>
+      </c>
+      <c r="E160" t="n">
+        <v>-14.84</v>
+      </c>
+      <c r="F160" t="n">
+        <v>264</v>
+      </c>
+      <c r="G160" t="n">
+        <v>294</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SBMA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>148</v>
+      </c>
+      <c r="E161" t="n">
+        <v>-14.86</v>
+      </c>
+      <c r="F161" t="n">
+        <v>126</v>
+      </c>
+      <c r="G161" t="n">
+        <v>131</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>2580</v>
+      </c>
+      <c r="E162" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="F162" t="n">
+        <v>3220</v>
+      </c>
+      <c r="G162" t="n">
+        <v>3220</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>4370</v>
+      </c>
+      <c r="E163" t="n">
+        <v>-14.19</v>
+      </c>
+      <c r="F163" t="n">
+        <v>3750</v>
+      </c>
+      <c r="G163" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PCAR</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>89</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-14.61</v>
+      </c>
+      <c r="F164" t="n">
+        <v>76</v>
+      </c>
+      <c r="G164" t="n">
+        <v>89</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ARII</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>470</v>
+      </c>
+      <c r="E165" t="n">
+        <v>-12.77</v>
+      </c>
+      <c r="F165" t="n">
+        <v>410</v>
+      </c>
+      <c r="G165" t="n">
+        <v>438</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>HATM</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>665</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-14.29</v>
+      </c>
+      <c r="F166" t="n">
+        <v>570</v>
+      </c>
+      <c r="G166" t="n">
+        <v>605</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>108</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-14.81</v>
+      </c>
+      <c r="F167" t="n">
+        <v>92</v>
+      </c>
+      <c r="G167" t="n">
+        <v>105</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>116</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-14.66</v>
+      </c>
+      <c r="F168" t="n">
+        <v>99</v>
+      </c>
+      <c r="G168" t="n">
+        <v>99</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>BIKE</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E169" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="F169" t="n">
+        <v>4180</v>
+      </c>
+      <c r="G169" t="n">
+        <v>5225</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AIMS</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>990</v>
+      </c>
+      <c r="E170" t="n">
+        <v>-6.57</v>
+      </c>
+      <c r="F170" t="n">
+        <v>925</v>
+      </c>
+      <c r="G170" t="n">
+        <v>925</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>3220</v>
+      </c>
+      <c r="E171" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="F171" t="n">
+        <v>4020</v>
+      </c>
+      <c r="G171" t="n">
+        <v>4020</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ALDO</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1955</v>
+      </c>
+      <c r="E172" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1820</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1820</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AIMS</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>925</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-6.49</v>
+      </c>
+      <c r="F173" t="n">
+        <v>865</v>
+      </c>
+      <c r="G173" t="n">
+        <v>865</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>4020</v>
+      </c>
+      <c r="E174" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="F174" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G174" t="n">
+        <v>5025</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>TMPO</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>169</v>
+      </c>
+      <c r="E175" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="F175" t="n">
+        <v>178</v>
+      </c>
+      <c r="G175" t="n">
+        <v>194</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AKKU</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>98</v>
+      </c>
+      <c r="E176" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="F176" t="n">
+        <v>92</v>
+      </c>
+      <c r="G176" t="n">
+        <v>92</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>TIFA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>360</v>
+      </c>
+      <c r="E177" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="F177" t="n">
+        <v>390</v>
+      </c>
+      <c r="G177" t="n">
+        <v>398</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="8" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ALDO</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-6.87</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1695</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1695</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ARII</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>510</v>
+      </c>
+      <c r="E179" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="F179" t="n">
+        <v>530</v>
+      </c>
+      <c r="G179" t="n">
+        <v>535</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>102</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F180" t="n">
+        <v>105</v>
+      </c>
+      <c r="G180" t="n">
+        <v>137</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>29.82</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>TRUK</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>5025</v>
+      </c>
+      <c r="E181" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="F181" t="n">
+        <v>5925</v>
+      </c>
+      <c r="G181" t="n">
+        <v>6025</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AKKU</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>92</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="n">
+        <v>92</v>
+      </c>
+      <c r="G182" t="n">
+        <v>114</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>MPXL</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>348</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F183" t="n">
+        <v>350</v>
+      </c>
+      <c r="G183" t="n">
+        <v>358</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>MPXL</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>332</v>
+      </c>
+      <c r="E184" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F184" t="n">
+        <v>328</v>
+      </c>
+      <c r="G184" t="n">
+        <v>334</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>DMAS</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>208</v>
+      </c>
+      <c r="E185" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="F185" t="n">
+        <v>204</v>
+      </c>
+      <c r="G185" t="n">
+        <v>220</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BAPA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>116</v>
+      </c>
+      <c r="E186" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="F186" t="n">
+        <v>114</v>
+      </c>
+      <c r="G186" t="n">
+        <v>114</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ARII</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>500</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>500</v>
+      </c>
+      <c r="G187" t="n">
+        <v>515</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>PRDA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E188" t="n">
+        <v>-2.86</v>
+      </c>
+      <c r="F188" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G188" t="n">
+        <v>3680</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Kamis</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>118</v>
+      </c>
+      <c r="E189" t="n">
+        <v>-4.24</v>
+      </c>
+      <c r="F189" t="n">
+        <v>113</v>
+      </c>
+      <c r="G189" t="n">
+        <v>140</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="8" t="n">
         <v>46318</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B190" t="inlineStr">
         <is>
           <t>Jumat</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>STRK</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D190" t="n">
         <v>137</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E190" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="F190" t="n">
         <v>183</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G190" t="n">
         <v>183</v>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>SUSPENDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>PRDA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>3590</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F191" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G191" t="n">
+        <v>3750</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>134</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F192" t="n">
+        <v>135</v>
+      </c>
+      <c r="G192" t="n">
+        <v>146</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Jumat</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>DMAS</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>218</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F193" t="n">
+        <v>220</v>
+      </c>
+      <c r="G193" t="n">
+        <v>220</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AALI</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>9625</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>9625</v>
+      </c>
+      <c r="G194" t="n">
+        <v>9800</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>TCPI</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1735</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1760</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H195" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>SUSPENDED</t>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>130</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F196" t="n">
+        <v>131</v>
+      </c>
+      <c r="G196" t="n">
+        <v>145</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>PTSN</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>390</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F197" t="n">
+        <v>392</v>
+      </c>
+      <c r="G197" t="n">
+        <v>428</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>PRDA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>3670</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="F198" t="n">
+        <v>3650</v>
+      </c>
+      <c r="G198" t="n">
+        <v>3760</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>WMPP</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>26</v>
+      </c>
+      <c r="E199" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="F199" t="n">
+        <v>25</v>
+      </c>
+      <c r="G199" t="n">
+        <v>31</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>IRSX</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>272</v>
+      </c>
+      <c r="E200" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="F200" t="n">
+        <v>268</v>
+      </c>
+      <c r="G200" t="n">
+        <v>290</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>380</v>
+      </c>
+      <c r="E201" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="F201" t="n">
+        <v>430</v>
+      </c>
+      <c r="G201" t="n">
+        <v>436</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ENZO</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>57</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F202" t="n">
+        <v>58</v>
+      </c>
+      <c r="G202" t="n">
+        <v>59</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>135</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F203" t="n">
+        <v>139</v>
+      </c>
+      <c r="G203" t="n">
+        <v>151</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AYLS</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>218</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F204" t="n">
+        <v>226</v>
+      </c>
+      <c r="G204" t="n">
+        <v>226</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ASPI</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>995</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1020</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1025</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>TOBA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>520</v>
+      </c>
+      <c r="E206" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="F206" t="n">
+        <v>580</v>
+      </c>
+      <c r="G206" t="n">
+        <v>620</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Senin</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>WMUU</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>36</v>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="n">
+        <v>36</v>
+      </c>
+      <c r="G207" t="n">
+        <v>47</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I62">
+  <conditionalFormatting sqref="J5:J207">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -523,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-26 20:36</t>
+          <t>Dibuat: 2026-10-27 18:45</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
@@ -705,7 +705,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+335.18%</t>
+          <t>+335.38%</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>+7.79%</t>
+          <t>+7.62%</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -781,7 +781,7 @@
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
@@ -797,7 +797,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-27</t>
+          <t>Prediksi untuk: 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -886,32 +886,32 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>38.93</v>
+        <v>113.54</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>19.62</v>
+        <v>20.63</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>11.83</v>
+        <v>44.3</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>17.99</v>
+        <v>24.12</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>2.4</v>
+        <v>3.64</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>17.54</v>
+        <v>39.28</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>10.32</v>
+        <v>10.09</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
     </row>
@@ -920,45 +920,45 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>KUAT</t>
+          <t>ELITE</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>TGUK</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>430</v>
+        <v>100</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>41.1</v>
+        <v>22.85</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>14.97</v>
+        <v>23.46</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>62.88</v>
+        <v>26.58</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>20.47</v>
+        <v>28</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>1.72</v>
+        <v>4.21</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>10.4</v>
+        <v>2.46</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>14.02</v>
+        <v>17.71</v>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
@@ -976,36 +976,36 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>OKAS</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>7.92</v>
+        <v>6.79</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>11.11</v>
+        <v>19.32</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>26.76</v>
+        <v>25</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>-0.15</v>
+        <v>4.18</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>17.42</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>15</v>
+        <v>7.14</v>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1014,327 +1014,45 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>KUAT</t>
+          <t>SEDANG</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>TOBA</t>
+          <t>WMUU</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>505</v>
+        <v>34</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>130.61</v>
+        <v>7.69</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-2.88</v>
+        <v>-5.56</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>59.81</v>
+        <v>30.77</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>23.76</v>
+        <v>17.65</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>2.81</v>
+        <v>0.16</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>16.24</v>
+        <v>17.24</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>8.77</v>
+        <v>13.03</v>
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
           <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>KUAT</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>BLES</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>228</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>13.16</v>
-      </c>
-      <c r="J9" s="7" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>15.77</v>
-      </c>
-      <c r="L9" s="7" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>WMUU</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>21.27</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>71.43000000000001</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>36.11</v>
-      </c>
-      <c r="J10" s="7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="K10" s="7" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="L10" s="7" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="M10" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>MBSS</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>4280</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>51.04</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>42.67</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>11.21</v>
-      </c>
-      <c r="J11" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="L11" s="7" t="n">
-        <v>11.52</v>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>STRK</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>139</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>51.09</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>68.38</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>DKHH</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>147</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>17.69</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>58.06</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>55.72</v>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>10.74</v>
-      </c>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>51</v>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>SEDANG</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>SBMA</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>7.72</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>27.12</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="K14" s="7" t="n">
-        <v>24.28</v>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>A</t>
         </is>
       </c>
     </row>
@@ -1700,20 +1418,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-26 s/d 2026-10-26</t>
+          <t>2026-10-26 s/d 2026-10-27</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -1722,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1731,13 +1449,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="O9" t="n">
-        <v>9.34</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>
@@ -1771,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J207"/>
+  <dimension ref="A1:J217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1863,20 +1581,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HELI</t>
+          <t>RSCH</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>276</v>
+        <v>525</v>
       </c>
       <c r="E5" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>278</v>
+        <v>525</v>
       </c>
       <c r="G5" t="n">
-        <v>278</v>
+        <v>555</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1900,20 +1618,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>MOLI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>234</v>
+        <v>424</v>
       </c>
       <c r="E6" t="n">
-        <v>0.85</v>
+        <v>0.47</v>
       </c>
       <c r="F6" t="n">
-        <v>236</v>
+        <v>426</v>
       </c>
       <c r="G6" t="n">
-        <v>292</v>
+        <v>426</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2051,24 +1769,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RSCH</t>
+          <t>ASGR</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>525</v>
+        <v>2520</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>525</v>
+        <v>2520</v>
       </c>
       <c r="G10" t="n">
-        <v>555</v>
+        <v>2540</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2088,24 +1806,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ASGR</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2520</v>
+        <v>404</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F11" t="n">
-        <v>2520</v>
+        <v>406</v>
       </c>
       <c r="G11" t="n">
-        <v>2540</v>
+        <v>486</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2125,20 +1843,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SAPX</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>404</v>
+        <v>6300</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>-0.79</v>
       </c>
       <c r="F12" t="n">
-        <v>406</v>
+        <v>6250</v>
       </c>
       <c r="G12" t="n">
-        <v>486</v>
+        <v>6250</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2162,24 +1880,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>478</v>
+        <v>296</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.84</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>474</v>
+        <v>296</v>
       </c>
       <c r="G13" t="n">
-        <v>474</v>
+        <v>310</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2199,24 +1917,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SMLE</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
       <c r="F14" t="n">
-        <v>296</v>
+        <v>474</v>
       </c>
       <c r="G14" t="n">
-        <v>310</v>
+        <v>474</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2236,20 +1954,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>HELI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6300</v>
+        <v>276</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.79</v>
+        <v>0.72</v>
       </c>
       <c r="F15" t="n">
-        <v>6250</v>
+        <v>278</v>
       </c>
       <c r="G15" t="n">
-        <v>6250</v>
+        <v>278</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2273,20 +1991,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MOLI</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>424</v>
+        <v>1130</v>
       </c>
       <c r="E16" t="n">
-        <v>0.47</v>
+        <v>-0.44</v>
       </c>
       <c r="F16" t="n">
-        <v>426</v>
+        <v>1125</v>
       </c>
       <c r="G16" t="n">
-        <v>426</v>
+        <v>1410</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2310,20 +2028,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOSS</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1180</v>
+        <v>234</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.51</v>
+        <v>0.85</v>
       </c>
       <c r="F17" t="n">
-        <v>1115</v>
+        <v>236</v>
       </c>
       <c r="G17" t="n">
-        <v>1160</v>
+        <v>292</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2347,20 +2065,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>SOSS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1130</v>
+        <v>1180</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.44</v>
+        <v>-5.51</v>
       </c>
       <c r="F18" t="n">
-        <v>1125</v>
+        <v>1115</v>
       </c>
       <c r="G18" t="n">
-        <v>1410</v>
+        <v>1160</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2384,20 +2102,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4230</v>
+        <v>705</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.96</v>
+        <v>-3.55</v>
       </c>
       <c r="F19" t="n">
-        <v>4020</v>
+        <v>680</v>
       </c>
       <c r="G19" t="n">
-        <v>4860</v>
+        <v>745</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2406,7 +2124,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -2421,30 +2139,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SAPX</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="F20" t="n">
-        <v>448</v>
+        <v>525</v>
       </c>
       <c r="G20" t="n">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>6.13</v>
       </c>
     </row>
     <row r="21">
@@ -2458,20 +2179,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>MTLA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>422</v>
+        <v>690</v>
       </c>
       <c r="E21" t="n">
-        <v>1.42</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>428</v>
+        <v>630</v>
       </c>
       <c r="G21" t="n">
-        <v>480</v>
+        <v>725</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2495,24 +2216,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>470</v>
+        <v>1155</v>
       </c>
       <c r="E22" t="n">
-        <v>11.7</v>
+        <v>3.9</v>
       </c>
       <c r="F22" t="n">
-        <v>525</v>
+        <v>1200</v>
       </c>
       <c r="G22" t="n">
-        <v>560</v>
+        <v>1290</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2521,7 +2242,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6.13</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="23">
@@ -2535,29 +2256,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SINI</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18300</v>
+        <v>444</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.37</v>
+        <v>0.9</v>
       </c>
       <c r="F23" t="n">
-        <v>17500</v>
+        <v>448</v>
       </c>
       <c r="G23" t="n">
-        <v>17875</v>
+        <v>466</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -2609,24 +2330,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SMLE</t>
+          <t>UNIQ</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>284</v>
+        <v>137</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7</v>
+        <v>-1.46</v>
       </c>
       <c r="F25" t="n">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="G25" t="n">
-        <v>304</v>
+        <v>147</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2646,20 +2367,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MTLA</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>690</v>
+        <v>422</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.699999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="F26" t="n">
-        <v>630</v>
+        <v>428</v>
       </c>
       <c r="G26" t="n">
-        <v>725</v>
+        <v>480</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2683,24 +2404,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>705</v>
+        <v>284</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.55</v>
+        <v>0.7</v>
       </c>
       <c r="F27" t="n">
-        <v>680</v>
+        <v>286</v>
       </c>
       <c r="G27" t="n">
-        <v>745</v>
+        <v>304</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2720,20 +2441,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UNIQ</t>
+          <t>SINI</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>137</v>
+        <v>18300</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.46</v>
+        <v>-4.37</v>
       </c>
       <c r="F28" t="n">
-        <v>135</v>
+        <v>17500</v>
       </c>
       <c r="G28" t="n">
-        <v>147</v>
+        <v>17875</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2742,7 +2463,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -2757,33 +2478,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1155</v>
+        <v>4230</v>
       </c>
       <c r="E29" t="n">
-        <v>3.9</v>
+        <v>-4.96</v>
       </c>
       <c r="F29" t="n">
-        <v>1200</v>
+        <v>4020</v>
       </c>
       <c r="G29" t="n">
-        <v>1290</v>
+        <v>4860</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>6.96</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2834,33 +2552,30 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>332</v>
+        <v>302</v>
       </c>
       <c r="E31" t="n">
-        <v>2.41</v>
+        <v>0.66</v>
       </c>
       <c r="F31" t="n">
-        <v>340</v>
+        <v>304</v>
       </c>
       <c r="G31" t="n">
-        <v>414</v>
+        <v>310</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>21.16</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2911,33 +2626,30 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>ASGR</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>266</v>
+        <v>2520</v>
       </c>
       <c r="E33" t="n">
-        <v>12.78</v>
+        <v>0.4</v>
       </c>
       <c r="F33" t="n">
-        <v>300</v>
+        <v>2530</v>
       </c>
       <c r="G33" t="n">
-        <v>332</v>
+        <v>2550</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>10.11</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2951,24 +2663,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SAMF</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>360</v>
+        <v>470</v>
       </c>
       <c r="E34" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="F34" t="n">
-        <v>372</v>
+        <v>482</v>
       </c>
       <c r="G34" t="n">
-        <v>386</v>
+        <v>525</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2977,7 +2689,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>3.24</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2991,30 +2703,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3760</v>
+        <v>266</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.33</v>
+        <v>12.78</v>
       </c>
       <c r="F35" t="n">
-        <v>3710</v>
+        <v>300</v>
       </c>
       <c r="G35" t="n">
-        <v>3990</v>
+        <v>332</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>10.11</v>
       </c>
     </row>
     <row r="36">
@@ -3028,30 +2743,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SMLE</t>
+          <t>SAMF</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>302</v>
+        <v>360</v>
       </c>
       <c r="E36" t="n">
-        <v>0.66</v>
+        <v>3.33</v>
       </c>
       <c r="F36" t="n">
-        <v>304</v>
+        <v>372</v>
       </c>
       <c r="G36" t="n">
-        <v>310</v>
+        <v>386</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="37">
@@ -3065,33 +2783,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>470</v>
+        <v>3760</v>
       </c>
       <c r="E37" t="n">
-        <v>2.55</v>
+        <v>-1.33</v>
       </c>
       <c r="F37" t="n">
-        <v>482</v>
+        <v>3710</v>
       </c>
       <c r="G37" t="n">
-        <v>525</v>
+        <v>3990</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>8.380000000000001</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3105,30 +2820,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ASGR</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2520</v>
+        <v>332</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4</v>
+        <v>2.41</v>
       </c>
       <c r="F38" t="n">
-        <v>2530</v>
+        <v>340</v>
       </c>
       <c r="G38" t="n">
-        <v>2550</v>
+        <v>414</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>21.16</v>
       </c>
     </row>
     <row r="39">
@@ -3142,20 +2860,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ASLI</t>
+          <t>DAAZ</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>486</v>
+        <v>2200</v>
       </c>
       <c r="E39" t="n">
-        <v>2.06</v>
+        <v>-0.45</v>
       </c>
       <c r="F39" t="n">
-        <v>496</v>
+        <v>2190</v>
       </c>
       <c r="G39" t="n">
-        <v>540</v>
+        <v>2190</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3164,7 +2882,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -3179,30 +2897,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BLUE</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3590</v>
+        <v>412</v>
       </c>
       <c r="E40" t="n">
-        <v>1.11</v>
+        <v>5.34</v>
       </c>
       <c r="F40" t="n">
-        <v>3630</v>
+        <v>434</v>
       </c>
       <c r="G40" t="n">
-        <v>4100</v>
+        <v>515</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>18.07</v>
       </c>
     </row>
     <row r="41">
@@ -3216,33 +2937,30 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MPIX</t>
+          <t>DEWI</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E41" t="n">
-        <v>2.68</v>
+        <v>0.77</v>
       </c>
       <c r="F41" t="n">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="G41" t="n">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>0.37</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3256,30 +2974,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>MPIX</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1270</v>
+        <v>224</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="F42" t="n">
-        <v>1270</v>
+        <v>230</v>
       </c>
       <c r="G42" t="n">
-        <v>1280</v>
+        <v>232</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="43">
@@ -3293,20 +3014,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>530</v>
+        <v>350</v>
       </c>
       <c r="E43" t="n">
-        <v>3.77</v>
+        <v>2.86</v>
       </c>
       <c r="F43" t="n">
-        <v>550</v>
+        <v>360</v>
       </c>
       <c r="G43" t="n">
-        <v>660</v>
+        <v>404</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3319,7 +3040,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>19.4</v>
+        <v>11.66</v>
       </c>
     </row>
     <row r="44">
@@ -3333,24 +3054,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E44" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G44" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3370,30 +3091,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>71</v>
+        <v>332</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
-        <v>71</v>
+        <v>342</v>
       </c>
       <c r="G45" t="n">
-        <v>74</v>
+        <v>378</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -3407,24 +3131,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AMAN</t>
+          <t>PPRI</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>222</v>
+        <v>186</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9</v>
+        <v>-3.23</v>
       </c>
       <c r="F46" t="n">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="G46" t="n">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3444,24 +3168,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SAPX</t>
+          <t>BLUE</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>438</v>
+        <v>3590</v>
       </c>
       <c r="E47" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="F47" t="n">
-        <v>444</v>
+        <v>3630</v>
       </c>
       <c r="G47" t="n">
-        <v>450</v>
+        <v>4100</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3481,33 +3205,30 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>332</v>
+        <v>438</v>
       </c>
       <c r="E48" t="n">
-        <v>3.01</v>
+        <v>1.37</v>
       </c>
       <c r="F48" t="n">
-        <v>342</v>
+        <v>444</v>
       </c>
       <c r="G48" t="n">
-        <v>378</v>
+        <v>450</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>9.970000000000001</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3521,30 +3242,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DAAZ</t>
+          <t>SOTS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2200</v>
+        <v>630</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.45</v>
+        <v>3.97</v>
       </c>
       <c r="F49" t="n">
-        <v>2190</v>
+        <v>655</v>
       </c>
       <c r="G49" t="n">
-        <v>2190</v>
+        <v>675</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>2.54</v>
       </c>
     </row>
     <row r="50">
@@ -3558,33 +3282,30 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>350</v>
+        <v>61</v>
       </c>
       <c r="E50" t="n">
-        <v>2.86</v>
+        <v>1.64</v>
       </c>
       <c r="F50" t="n">
-        <v>360</v>
+        <v>62</v>
       </c>
       <c r="G50" t="n">
-        <v>404</v>
+        <v>63</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>11.66</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3598,20 +3319,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WAPO</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>352</v>
+        <v>530</v>
       </c>
       <c r="E51" t="n">
-        <v>3.41</v>
+        <v>3.77</v>
       </c>
       <c r="F51" t="n">
-        <v>364</v>
+        <v>550</v>
       </c>
       <c r="G51" t="n">
-        <v>400</v>
+        <v>660</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3620,8 +3341,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>19.4</v>
       </c>
     </row>
     <row r="52">
@@ -3635,29 +3359,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DEWI</t>
+          <t>WAPO</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>260</v>
+        <v>352</v>
       </c>
       <c r="E52" t="n">
-        <v>0.77</v>
+        <v>3.41</v>
       </c>
       <c r="F52" t="n">
-        <v>262</v>
+        <v>364</v>
       </c>
       <c r="G52" t="n">
-        <v>262</v>
+        <v>400</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -3709,24 +3433,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PPRI</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>186</v>
+        <v>1270</v>
       </c>
       <c r="E54" t="n">
-        <v>-3.23</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>180</v>
+        <v>1270</v>
       </c>
       <c r="G54" t="n">
-        <v>196</v>
+        <v>1280</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3746,33 +3470,30 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SOTS</t>
+          <t>ASLI</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>630</v>
+        <v>486</v>
       </c>
       <c r="E55" t="n">
-        <v>3.97</v>
+        <v>2.06</v>
       </c>
       <c r="F55" t="n">
-        <v>655</v>
+        <v>496</v>
       </c>
       <c r="G55" t="n">
-        <v>675</v>
+        <v>540</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>2.54</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3786,33 +3507,30 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>AMAN</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>412</v>
+        <v>222</v>
       </c>
       <c r="E56" t="n">
-        <v>5.34</v>
+        <v>0.9</v>
       </c>
       <c r="F56" t="n">
-        <v>434</v>
+        <v>224</v>
       </c>
       <c r="G56" t="n">
-        <v>515</v>
+        <v>224</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>18.07</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3826,20 +3544,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>370</v>
+        <v>318</v>
       </c>
       <c r="E57" t="n">
-        <v>0.54</v>
+        <v>13.21</v>
       </c>
       <c r="F57" t="n">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="G57" t="n">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3848,8 +3566,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -3863,30 +3584,33 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IATA</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="F58" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="G58" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>14.7</v>
       </c>
     </row>
     <row r="59">
@@ -3900,20 +3624,20 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>PKPK</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>655</v>
+        <v>6800</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.29</v>
+        <v>0.74</v>
       </c>
       <c r="F59" t="n">
-        <v>640</v>
+        <v>6850</v>
       </c>
       <c r="G59" t="n">
-        <v>640</v>
+        <v>7150</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -3922,7 +3646,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -3937,24 +3661,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KLAS</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="F60" t="n">
-        <v>82</v>
+        <v>372</v>
       </c>
       <c r="G60" t="n">
-        <v>90</v>
+        <v>374</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3974,20 +3698,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>BALI</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4400</v>
+        <v>1560</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>-1.92</v>
       </c>
       <c r="F61" t="n">
-        <v>4400</v>
+        <v>1530</v>
       </c>
       <c r="G61" t="n">
-        <v>4500</v>
+        <v>1530</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4011,29 +3735,29 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>WAPO</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6800</v>
+        <v>326</v>
       </c>
       <c r="E62" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>6850</v>
+        <v>326</v>
       </c>
       <c r="G62" t="n">
-        <v>7150</v>
+        <v>344</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -4048,33 +3772,30 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>BDKR</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="E63" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>72</v>
+        <v>210</v>
       </c>
       <c r="G63" t="n">
-        <v>83</v>
+        <v>230</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>14.7</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -4088,29 +3809,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>IATA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>825</v>
+        <v>115</v>
       </c>
       <c r="E64" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>910</v>
+        <v>115</v>
       </c>
       <c r="G64" t="n">
-        <v>1030</v>
+        <v>115</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -4125,24 +3846,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BDKR</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>210</v>
+        <v>4400</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>210</v>
+        <v>4400</v>
       </c>
       <c r="G65" t="n">
-        <v>230</v>
+        <v>4500</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4162,33 +3883,30 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>KLAS</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="E66" t="n">
-        <v>13.21</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="G66" t="n">
-        <v>396</v>
+        <v>90</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>9.449999999999999</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4202,20 +3920,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BALI</t>
+          <t>BLUE</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1560</v>
+        <v>3660</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.92</v>
+        <v>2.19</v>
       </c>
       <c r="F67" t="n">
-        <v>1530</v>
+        <v>3740</v>
       </c>
       <c r="G67" t="n">
-        <v>1530</v>
+        <v>3910</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4224,8 +3942,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>4.02</v>
       </c>
     </row>
     <row r="68">
@@ -4239,24 +3960,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WAPO</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>326</v>
+        <v>655</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>-2.29</v>
       </c>
       <c r="F68" t="n">
-        <v>326</v>
+        <v>640</v>
       </c>
       <c r="G68" t="n">
-        <v>344</v>
+        <v>640</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4276,20 +3997,20 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SMLE</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>320</v>
+        <v>6825</v>
       </c>
       <c r="E69" t="n">
-        <v>1.25</v>
+        <v>10.26</v>
       </c>
       <c r="F69" t="n">
-        <v>324</v>
+        <v>7525</v>
       </c>
       <c r="G69" t="n">
-        <v>324</v>
+        <v>7975</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4298,8 +4019,11 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>5.45</v>
       </c>
     </row>
     <row r="70">
@@ -4313,20 +4037,20 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BLUE</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>3660</v>
+        <v>320</v>
       </c>
       <c r="E70" t="n">
-        <v>2.19</v>
+        <v>1.25</v>
       </c>
       <c r="F70" t="n">
-        <v>3740</v>
+        <v>324</v>
       </c>
       <c r="G70" t="n">
-        <v>3910</v>
+        <v>324</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4335,11 +4059,8 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>4.02</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4353,33 +4074,30 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6825</v>
+        <v>825</v>
       </c>
       <c r="E71" t="n">
-        <v>10.26</v>
+        <v>10.3</v>
       </c>
       <c r="F71" t="n">
-        <v>7525</v>
+        <v>910</v>
       </c>
       <c r="G71" t="n">
-        <v>7975</v>
+        <v>1030</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>5.45</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4467,24 +4185,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MPIX</t>
+          <t>HELI</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="G74" t="n">
-        <v>224</v>
+        <v>402</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4504,24 +4222,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KKES</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="F75" t="n">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="G75" t="n">
-        <v>85</v>
+        <v>374</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4541,24 +4259,24 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>REAL</t>
+          <t>MPIX</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>51</v>
+        <v>220</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.96</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="G76" t="n">
-        <v>52</v>
+        <v>224</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4578,20 +4296,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>ASLI</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4500</v>
+        <v>464</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.33</v>
+        <v>3.45</v>
       </c>
       <c r="F77" t="n">
-        <v>4440</v>
+        <v>480</v>
       </c>
       <c r="G77" t="n">
-        <v>4440</v>
+        <v>496</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -4600,8 +4318,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>2.82</v>
       </c>
     </row>
     <row r="78">
@@ -4615,20 +4336,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HELI</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>342</v>
+        <v>1230</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="F78" t="n">
-        <v>342</v>
+        <v>1255</v>
       </c>
       <c r="G78" t="n">
-        <v>402</v>
+        <v>1320</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4637,8 +4358,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>4.65</v>
       </c>
     </row>
     <row r="79">
@@ -4652,24 +4376,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>ENAK</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>80</v>
+        <v>214</v>
       </c>
       <c r="G79" t="n">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4689,20 +4413,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>605</v>
+        <v>4500</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.48</v>
+        <v>-1.33</v>
       </c>
       <c r="F80" t="n">
-        <v>590</v>
+        <v>4440</v>
       </c>
       <c r="G80" t="n">
-        <v>610</v>
+        <v>4440</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -4726,20 +4450,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>POLA</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E81" t="n">
-        <v>9.09</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G81" t="n">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -4748,7 +4472,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -4763,20 +4487,20 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>354</v>
+        <v>605</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.13</v>
+        <v>-2.48</v>
       </c>
       <c r="F82" t="n">
-        <v>350</v>
+        <v>590</v>
       </c>
       <c r="G82" t="n">
-        <v>374</v>
+        <v>610</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -4840,33 +4564,30 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>BLUE</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1230</v>
+        <v>3900</v>
       </c>
       <c r="E84" t="n">
-        <v>2.03</v>
+        <v>0.77</v>
       </c>
       <c r="F84" t="n">
-        <v>1255</v>
+        <v>3930</v>
       </c>
       <c r="G84" t="n">
-        <v>1320</v>
+        <v>4510</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>4.65</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -4880,29 +4601,29 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BLUE</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3900</v>
+        <v>1505</v>
       </c>
       <c r="E85" t="n">
-        <v>0.77</v>
+        <v>19.6</v>
       </c>
       <c r="F85" t="n">
-        <v>3930</v>
+        <v>1800</v>
       </c>
       <c r="G85" t="n">
-        <v>4510</v>
+        <v>1880</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -4917,24 +4638,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ENAK</t>
+          <t>BDKR</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G86" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4954,29 +4675,29 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>REAL</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1505</v>
+        <v>51</v>
       </c>
       <c r="E87" t="n">
-        <v>19.6</v>
+        <v>-1.96</v>
       </c>
       <c r="F87" t="n">
-        <v>1800</v>
+        <v>50</v>
       </c>
       <c r="G87" t="n">
-        <v>1880</v>
+        <v>52</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -4991,33 +4712,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ASLI</t>
+          <t>KKES</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>464</v>
+        <v>77</v>
       </c>
       <c r="E88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>480</v>
+        <v>77</v>
       </c>
       <c r="G88" t="n">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>2.82</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5031,29 +4749,29 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BDKR</t>
+          <t>POLA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="F89" t="n">
-        <v>216</v>
+        <v>120</v>
       </c>
       <c r="G89" t="n">
-        <v>218</v>
+        <v>121</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -5068,30 +4786,33 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>8150</v>
+        <v>905</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>8.84</v>
       </c>
       <c r="F90" t="n">
-        <v>8150</v>
+        <v>985</v>
       </c>
       <c r="G90" t="n">
-        <v>8300</v>
+        <v>1120</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>13.14</v>
       </c>
     </row>
     <row r="91">
@@ -5105,20 +4826,20 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>PEVE</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>452</v>
+        <v>412</v>
       </c>
       <c r="E91" t="n">
-        <v>17.26</v>
+        <v>-3.4</v>
       </c>
       <c r="F91" t="n">
-        <v>530</v>
+        <v>398</v>
       </c>
       <c r="G91" t="n">
-        <v>565</v>
+        <v>398</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5127,11 +4848,8 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>6.07</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -5145,20 +4863,20 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1715</v>
+        <v>452</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.58</v>
+        <v>17.26</v>
       </c>
       <c r="F92" t="n">
-        <v>1705</v>
+        <v>530</v>
       </c>
       <c r="G92" t="n">
-        <v>2140</v>
+        <v>565</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5167,8 +4885,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>6.07</v>
       </c>
     </row>
     <row r="93">
@@ -5182,33 +4903,30 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MCAS</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>284</v>
+        <v>8150</v>
       </c>
       <c r="E93" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>310</v>
+        <v>8150</v>
       </c>
       <c r="G93" t="n">
-        <v>326</v>
+        <v>8300</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>4.64</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -5222,24 +4940,24 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PEVE</t>
+          <t>PKPK</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>412</v>
+        <v>6800</v>
       </c>
       <c r="E94" t="n">
-        <v>-3.4</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>398</v>
+        <v>6800</v>
       </c>
       <c r="G94" t="n">
-        <v>398</v>
+        <v>7225</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5259,29 +4977,29 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BDKR</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>212</v>
+        <v>316</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>-8.23</v>
       </c>
       <c r="F95" t="n">
-        <v>212</v>
+        <v>290</v>
       </c>
       <c r="G95" t="n">
-        <v>218</v>
+        <v>332</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -5296,24 +5014,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>316</v>
+        <v>396</v>
       </c>
       <c r="E96" t="n">
-        <v>-8.23</v>
+        <v>1.52</v>
       </c>
       <c r="F96" t="n">
-        <v>290</v>
+        <v>402</v>
       </c>
       <c r="G96" t="n">
-        <v>332</v>
+        <v>426</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5333,20 +5051,20 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GTRA</t>
+          <t>POLA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>304</v>
+        <v>105</v>
       </c>
       <c r="E97" t="n">
-        <v>4.61</v>
+        <v>1.9</v>
       </c>
       <c r="F97" t="n">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="G97" t="n">
-        <v>318</v>
+        <v>127</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -5355,11 +5073,8 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -5373,20 +5088,20 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>MCAS</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>905</v>
+        <v>284</v>
       </c>
       <c r="E98" t="n">
-        <v>8.84</v>
+        <v>9.15</v>
       </c>
       <c r="F98" t="n">
-        <v>985</v>
+        <v>310</v>
       </c>
       <c r="G98" t="n">
-        <v>1120</v>
+        <v>326</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -5399,7 +5114,7 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>13.14</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="99">
@@ -5413,29 +5128,29 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>TEBE</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6800</v>
+        <v>2690</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>-10.78</v>
       </c>
       <c r="F99" t="n">
-        <v>6800</v>
+        <v>2400</v>
       </c>
       <c r="G99" t="n">
-        <v>7225</v>
+        <v>2840</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -5487,29 +5202,29 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TEBE</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2690</v>
+        <v>1295</v>
       </c>
       <c r="E101" t="n">
-        <v>-10.78</v>
+        <v>1.93</v>
       </c>
       <c r="F101" t="n">
-        <v>2400</v>
+        <v>1320</v>
       </c>
       <c r="G101" t="n">
-        <v>2840</v>
+        <v>1325</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -5561,20 +5276,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>BDKR</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1295</v>
+        <v>212</v>
       </c>
       <c r="E103" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>1320</v>
+        <v>212</v>
       </c>
       <c r="G103" t="n">
-        <v>1325</v>
+        <v>218</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -5598,24 +5313,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>POLA</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>105</v>
+        <v>1715</v>
       </c>
       <c r="E104" t="n">
-        <v>1.9</v>
+        <v>-0.58</v>
       </c>
       <c r="F104" t="n">
-        <v>107</v>
+        <v>1705</v>
       </c>
       <c r="G104" t="n">
-        <v>127</v>
+        <v>2140</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5635,30 +5350,33 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>GTRA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>396</v>
+        <v>304</v>
       </c>
       <c r="E105" t="n">
-        <v>1.52</v>
+        <v>4.61</v>
       </c>
       <c r="F105" t="n">
-        <v>402</v>
+        <v>318</v>
       </c>
       <c r="G105" t="n">
-        <v>426</v>
+        <v>318</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="106">
@@ -5709,24 +5427,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PEVE</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>384</v>
+        <v>90</v>
       </c>
       <c r="E107" t="n">
-        <v>-2.6</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>374</v>
+        <v>90</v>
       </c>
       <c r="G107" t="n">
-        <v>384</v>
+        <v>100</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5746,30 +5464,33 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>90</v>
+        <v>1250</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="F108" t="n">
-        <v>90</v>
+        <v>1310</v>
       </c>
       <c r="G108" t="n">
-        <v>100</v>
+        <v>1445</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>9.75</v>
       </c>
     </row>
     <row r="109">
@@ -5783,20 +5504,20 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>PEVE</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>420</v>
+        <v>384</v>
       </c>
       <c r="E109" t="n">
-        <v>1.9</v>
+        <v>-2.6</v>
       </c>
       <c r="F109" t="n">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="G109" t="n">
-        <v>478</v>
+        <v>384</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -5820,20 +5541,20 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>SOSS</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2140</v>
+        <v>1200</v>
       </c>
       <c r="E110" t="n">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>2270</v>
+        <v>1200</v>
       </c>
       <c r="G110" t="n">
-        <v>2670</v>
+        <v>1260</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -5842,11 +5563,8 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>17.03</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -5860,30 +5578,33 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>POLA</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>108</v>
+        <v>2140</v>
       </c>
       <c r="E111" t="n">
-        <v>1.85</v>
+        <v>6.07</v>
       </c>
       <c r="F111" t="n">
-        <v>110</v>
+        <v>2270</v>
       </c>
       <c r="G111" t="n">
-        <v>121</v>
+        <v>2670</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>17.03</v>
       </c>
     </row>
     <row r="112">
@@ -5897,30 +5618,33 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="F112" t="n">
-        <v>388</v>
+        <v>87</v>
       </c>
       <c r="G112" t="n">
-        <v>434</v>
+        <v>101</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>15.51</v>
       </c>
     </row>
     <row r="113">
@@ -5934,20 +5658,20 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>290</v>
+        <v>388</v>
       </c>
       <c r="E113" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>292</v>
+        <v>388</v>
       </c>
       <c r="G113" t="n">
-        <v>294</v>
+        <v>434</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -5971,24 +5695,24 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3990</v>
+        <v>290</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F114" t="n">
-        <v>3990</v>
+        <v>292</v>
       </c>
       <c r="G114" t="n">
-        <v>4000</v>
+        <v>294</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6008,29 +5732,29 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TEBE</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2800</v>
+        <v>980</v>
       </c>
       <c r="E115" t="n">
-        <v>1.43</v>
+        <v>2.55</v>
       </c>
       <c r="F115" t="n">
-        <v>2840</v>
+        <v>1005</v>
       </c>
       <c r="G115" t="n">
-        <v>3100</v>
+        <v>1115</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -6045,33 +5769,30 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>DAAZ</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1250</v>
+        <v>2420</v>
       </c>
       <c r="E116" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>1310</v>
+        <v>2420</v>
       </c>
       <c r="G116" t="n">
-        <v>1445</v>
+        <v>2940</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>9.75</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -6085,33 +5806,30 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TCPI</t>
+          <t>POLA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1625</v>
+        <v>108</v>
       </c>
       <c r="E117" t="n">
-        <v>14.46</v>
+        <v>1.85</v>
       </c>
       <c r="F117" t="n">
-        <v>1860</v>
+        <v>110</v>
       </c>
       <c r="G117" t="n">
-        <v>1865</v>
+        <v>121</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -6125,33 +5843,30 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>TEBE</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>83</v>
+        <v>2800</v>
       </c>
       <c r="E118" t="n">
-        <v>4.82</v>
+        <v>1.43</v>
       </c>
       <c r="F118" t="n">
-        <v>87</v>
+        <v>2840</v>
       </c>
       <c r="G118" t="n">
-        <v>101</v>
+        <v>3100</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>15.51</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -6165,30 +5880,33 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>TCPI</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>4600</v>
+        <v>1625</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>14.46</v>
       </c>
       <c r="F119" t="n">
-        <v>4600</v>
+        <v>1860</v>
       </c>
       <c r="G119" t="n">
-        <v>4660</v>
+        <v>1865</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="120">
@@ -6202,29 +5920,29 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>980</v>
+        <v>420</v>
       </c>
       <c r="E120" t="n">
-        <v>2.55</v>
+        <v>1.9</v>
       </c>
       <c r="F120" t="n">
-        <v>1005</v>
+        <v>428</v>
       </c>
       <c r="G120" t="n">
-        <v>1115</v>
+        <v>478</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -6239,24 +5957,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SOSS</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="G121" t="n">
-        <v>1260</v>
+        <v>4660</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6276,20 +5994,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DAAZ</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2420</v>
+        <v>3990</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>2420</v>
+        <v>3990</v>
       </c>
       <c r="G122" t="n">
-        <v>2940</v>
+        <v>4000</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -6313,24 +6031,24 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DAAZ</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>2730</v>
+        <v>376</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>2720</v>
+        <v>376</v>
       </c>
       <c r="G123" t="n">
-        <v>2720</v>
+        <v>390</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6350,20 +6068,20 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TEBE</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>2850</v>
+        <v>89</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>2850</v>
+        <v>89</v>
       </c>
       <c r="G124" t="n">
-        <v>3020</v>
+        <v>102</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -6387,24 +6105,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>DAAZ</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>7650</v>
+        <v>2730</v>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="F125" t="n">
-        <v>7650</v>
+        <v>2720</v>
       </c>
       <c r="G125" t="n">
-        <v>7675</v>
+        <v>2720</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6424,20 +6142,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>3710</v>
+        <v>408</v>
       </c>
       <c r="E126" t="n">
-        <v>1.08</v>
+        <v>-1.47</v>
       </c>
       <c r="F126" t="n">
-        <v>3750</v>
+        <v>402</v>
       </c>
       <c r="G126" t="n">
-        <v>3830</v>
+        <v>484</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -6461,24 +6179,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TCPI</t>
+          <t>PKPK</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1800</v>
+        <v>7650</v>
       </c>
       <c r="E127" t="n">
-        <v>-1.11</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>1780</v>
+        <v>7650</v>
       </c>
       <c r="G127" t="n">
-        <v>2150</v>
+        <v>7675</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6498,30 +6216,33 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>2670</v>
+        <v>98</v>
       </c>
       <c r="E128" t="n">
-        <v>21.72</v>
+        <v>2.04</v>
       </c>
       <c r="F128" t="n">
-        <v>3250</v>
+        <v>100</v>
       </c>
       <c r="G128" t="n">
-        <v>3330</v>
+        <v>103</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>SKIP_GAP_HIGH</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="129">
@@ -6535,29 +6256,29 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>376</v>
+        <v>2670</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>21.72</v>
       </c>
       <c r="F129" t="n">
-        <v>376</v>
+        <v>3250</v>
       </c>
       <c r="G129" t="n">
-        <v>390</v>
+        <v>3330</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SKIP_GAP_HIGH</t>
         </is>
       </c>
     </row>
@@ -6572,20 +6293,20 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>TCPI</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>92</v>
+        <v>1800</v>
       </c>
       <c r="E130" t="n">
-        <v>-3.26</v>
+        <v>-1.11</v>
       </c>
       <c r="F130" t="n">
-        <v>89</v>
+        <v>1780</v>
       </c>
       <c r="G130" t="n">
-        <v>92</v>
+        <v>2150</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -6609,24 +6330,24 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>MINE</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1090</v>
+        <v>320</v>
       </c>
       <c r="E131" t="n">
-        <v>0.46</v>
+        <v>-0.62</v>
       </c>
       <c r="F131" t="n">
-        <v>1095</v>
+        <v>318</v>
       </c>
       <c r="G131" t="n">
-        <v>1120</v>
+        <v>324</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6646,24 +6367,24 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>-3.26</v>
       </c>
       <c r="F132" t="n">
         <v>89</v>
       </c>
       <c r="G132" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6683,24 +6404,24 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>408</v>
+        <v>1090</v>
       </c>
       <c r="E133" t="n">
-        <v>-1.47</v>
+        <v>0.46</v>
       </c>
       <c r="F133" t="n">
-        <v>402</v>
+        <v>1095</v>
       </c>
       <c r="G133" t="n">
-        <v>484</v>
+        <v>1120</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6720,20 +6441,20 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>TEBE</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>98</v>
+        <v>2850</v>
       </c>
       <c r="E134" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>100</v>
+        <v>2850</v>
       </c>
       <c r="G134" t="n">
-        <v>103</v>
+        <v>3020</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -6742,11 +6463,8 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J134" t="n">
-        <v>2.49</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -6760,24 +6478,24 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MINE</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>320</v>
+        <v>3710</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.62</v>
+        <v>1.08</v>
       </c>
       <c r="F135" t="n">
-        <v>318</v>
+        <v>3750</v>
       </c>
       <c r="G135" t="n">
-        <v>324</v>
+        <v>3830</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6797,20 +6515,20 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1400</v>
+        <v>92</v>
       </c>
       <c r="E136" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>1440</v>
+        <v>92</v>
       </c>
       <c r="G136" t="n">
-        <v>1750</v>
+        <v>96</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6819,11 +6537,8 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J136" t="n">
-        <v>20.92</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -6837,24 +6552,24 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>TCPI</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>90</v>
+        <v>2010</v>
       </c>
       <c r="E137" t="n">
-        <v>-4.44</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>86</v>
+        <v>2010</v>
       </c>
       <c r="G137" t="n">
-        <v>115</v>
+        <v>2080</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6874,24 +6589,24 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SBMA</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>144</v>
+        <v>1015</v>
       </c>
       <c r="E138" t="n">
-        <v>-1.39</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>142</v>
+        <v>1015</v>
       </c>
       <c r="G138" t="n">
-        <v>142</v>
+        <v>1140</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6911,24 +6626,24 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TCPI</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>2010</v>
+        <v>7800</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>2010</v>
+        <v>7800</v>
       </c>
       <c r="G139" t="n">
-        <v>2080</v>
+        <v>7975</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6948,20 +6663,20 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>7800</v>
+        <v>458</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="F140" t="n">
-        <v>7800</v>
+        <v>464</v>
       </c>
       <c r="G140" t="n">
-        <v>7975</v>
+        <v>494</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -6985,24 +6700,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>458</v>
+        <v>97</v>
       </c>
       <c r="E141" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>464</v>
+        <v>97</v>
       </c>
       <c r="G141" t="n">
-        <v>494</v>
+        <v>102</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7022,20 +6737,20 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SOSS</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1240</v>
+        <v>3330</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F142" t="n">
-        <v>1235</v>
+        <v>3350</v>
       </c>
       <c r="G142" t="n">
-        <v>1235</v>
+        <v>4160</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -7059,30 +6774,33 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>PICO</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1015</v>
+        <v>194</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="F143" t="n">
-        <v>1015</v>
+        <v>210</v>
       </c>
       <c r="G143" t="n">
-        <v>1140</v>
+        <v>220</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="144">
@@ -7096,20 +6814,20 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>-4.44</v>
       </c>
       <c r="F144" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G144" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -7133,24 +6851,24 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>SOSS</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>92</v>
+        <v>1240</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F145" t="n">
-        <v>92</v>
+        <v>1235</v>
       </c>
       <c r="G145" t="n">
-        <v>96</v>
+        <v>1235</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7170,24 +6888,24 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PICO</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>194</v>
+        <v>1400</v>
       </c>
       <c r="E146" t="n">
-        <v>8.25</v>
+        <v>2.86</v>
       </c>
       <c r="F146" t="n">
-        <v>210</v>
+        <v>1440</v>
       </c>
       <c r="G146" t="n">
-        <v>220</v>
+        <v>1750</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7196,7 +6914,7 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>4.24</v>
+        <v>20.92</v>
       </c>
     </row>
     <row r="147">
@@ -7210,24 +6928,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>SBMA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3330</v>
+        <v>144</v>
       </c>
       <c r="E147" t="n">
-        <v>0.6</v>
+        <v>-1.39</v>
       </c>
       <c r="F147" t="n">
-        <v>3350</v>
+        <v>142</v>
       </c>
       <c r="G147" t="n">
-        <v>4160</v>
+        <v>142</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7284,24 +7002,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3450</v>
+        <v>4160</v>
       </c>
       <c r="E149" t="n">
-        <v>7.54</v>
+        <v>5.05</v>
       </c>
       <c r="F149" t="n">
-        <v>3710</v>
+        <v>4370</v>
       </c>
       <c r="G149" t="n">
-        <v>3970</v>
+        <v>4930</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7310,7 +7028,7 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>6.47</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="150">
@@ -7324,20 +7042,20 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>107</v>
+        <v>1565</v>
       </c>
       <c r="E150" t="n">
-        <v>-1.87</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>105</v>
+        <v>1565</v>
       </c>
       <c r="G150" t="n">
-        <v>115</v>
+        <v>1955</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -7361,24 +7079,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>102</v>
+        <v>950</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="F151" t="n">
-        <v>102</v>
+        <v>965</v>
       </c>
       <c r="G151" t="n">
-        <v>127</v>
+        <v>1020</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7398,20 +7116,20 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>TCPI</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1915</v>
+        <v>3450</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.26</v>
+        <v>7.54</v>
       </c>
       <c r="F152" t="n">
-        <v>1910</v>
+        <v>3710</v>
       </c>
       <c r="G152" t="n">
-        <v>1910</v>
+        <v>3970</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -7420,8 +7138,11 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>6.47</v>
       </c>
     </row>
     <row r="153">
@@ -7435,20 +7156,20 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="F153" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G153" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -7472,33 +7193,30 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>TCPI</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>4160</v>
+        <v>1915</v>
       </c>
       <c r="E154" t="n">
-        <v>5.05</v>
+        <v>-0.26</v>
       </c>
       <c r="F154" t="n">
-        <v>4370</v>
+        <v>1910</v>
       </c>
       <c r="G154" t="n">
-        <v>4930</v>
+        <v>1910</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J154" t="n">
-        <v>12.25</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -7512,24 +7230,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>950</v>
+        <v>101</v>
       </c>
       <c r="E155" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>965</v>
+        <v>101</v>
       </c>
       <c r="G155" t="n">
-        <v>1020</v>
+        <v>101</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7586,24 +7304,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>GRPH</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="E157" t="n">
-        <v>-2.31</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
+        <v>102</v>
+      </c>
+      <c r="G157" t="n">
         <v>127</v>
       </c>
-      <c r="G157" t="n">
-        <v>130</v>
-      </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7623,24 +7341,24 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>HATM</t>
+          <t>GRPH</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>670</v>
+        <v>130</v>
       </c>
       <c r="E158" t="n">
-        <v>0.75</v>
+        <v>-2.31</v>
       </c>
       <c r="F158" t="n">
-        <v>675</v>
+        <v>127</v>
       </c>
       <c r="G158" t="n">
-        <v>680</v>
+        <v>130</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7660,24 +7378,24 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>HATM</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1565</v>
+        <v>670</v>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F159" t="n">
-        <v>1565</v>
+        <v>675</v>
       </c>
       <c r="G159" t="n">
-        <v>1955</v>
+        <v>680</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7697,20 +7415,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>HATM</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>310</v>
+        <v>665</v>
       </c>
       <c r="E160" t="n">
-        <v>-14.84</v>
+        <v>-14.29</v>
       </c>
       <c r="F160" t="n">
-        <v>264</v>
+        <v>570</v>
       </c>
       <c r="G160" t="n">
-        <v>294</v>
+        <v>605</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7771,29 +7489,29 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2580</v>
+        <v>116</v>
       </c>
       <c r="E162" t="n">
-        <v>24.81</v>
+        <v>-14.66</v>
       </c>
       <c r="F162" t="n">
-        <v>3220</v>
+        <v>99</v>
       </c>
       <c r="G162" t="n">
-        <v>3220</v>
+        <v>99</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -7808,20 +7526,20 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>4370</v>
+        <v>108</v>
       </c>
       <c r="E163" t="n">
-        <v>-14.19</v>
+        <v>-14.81</v>
       </c>
       <c r="F163" t="n">
-        <v>3750</v>
+        <v>92</v>
       </c>
       <c r="G163" t="n">
-        <v>4800</v>
+        <v>105</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -7882,20 +7600,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>470</v>
+        <v>310</v>
       </c>
       <c r="E165" t="n">
-        <v>-12.77</v>
+        <v>-14.84</v>
       </c>
       <c r="F165" t="n">
-        <v>410</v>
+        <v>264</v>
       </c>
       <c r="G165" t="n">
-        <v>438</v>
+        <v>294</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7919,20 +7637,20 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HATM</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>665</v>
+        <v>470</v>
       </c>
       <c r="E166" t="n">
-        <v>-14.29</v>
+        <v>-12.77</v>
       </c>
       <c r="F166" t="n">
-        <v>570</v>
+        <v>410</v>
       </c>
       <c r="G166" t="n">
-        <v>605</v>
+        <v>438</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -7956,20 +7674,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>108</v>
+        <v>4370</v>
       </c>
       <c r="E167" t="n">
-        <v>-14.81</v>
+        <v>-14.19</v>
       </c>
       <c r="F167" t="n">
-        <v>92</v>
+        <v>3750</v>
       </c>
       <c r="G167" t="n">
-        <v>105</v>
+        <v>4800</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -7993,29 +7711,29 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>116</v>
+        <v>2580</v>
       </c>
       <c r="E168" t="n">
-        <v>-14.66</v>
+        <v>24.81</v>
       </c>
       <c r="F168" t="n">
-        <v>99</v>
+        <v>3220</v>
       </c>
       <c r="G168" t="n">
-        <v>99</v>
+        <v>3220</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -8030,29 +7748,29 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>4200</v>
+        <v>3220</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.48</v>
+        <v>24.84</v>
       </c>
       <c r="F169" t="n">
-        <v>4180</v>
+        <v>4020</v>
       </c>
       <c r="G169" t="n">
-        <v>5225</v>
+        <v>4020</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SKIP_GAP_HIGH</t>
         </is>
       </c>
     </row>
@@ -8067,20 +7785,20 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>990</v>
+        <v>1955</v>
       </c>
       <c r="E170" t="n">
-        <v>-6.57</v>
+        <v>-6.91</v>
       </c>
       <c r="F170" t="n">
-        <v>925</v>
+        <v>1820</v>
       </c>
       <c r="G170" t="n">
-        <v>925</v>
+        <v>1820</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -8104,29 +7822,29 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>3220</v>
+        <v>990</v>
       </c>
       <c r="E171" t="n">
-        <v>24.84</v>
+        <v>-6.57</v>
       </c>
       <c r="F171" t="n">
-        <v>4020</v>
+        <v>925</v>
       </c>
       <c r="G171" t="n">
-        <v>4020</v>
+        <v>925</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>SKIP_GAP_HIGH</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -8141,29 +7859,29 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1955</v>
+        <v>4200</v>
       </c>
       <c r="E172" t="n">
-        <v>-6.91</v>
+        <v>-0.48</v>
       </c>
       <c r="F172" t="n">
-        <v>1820</v>
+        <v>4180</v>
       </c>
       <c r="G172" t="n">
-        <v>1820</v>
+        <v>5225</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -8178,29 +7896,29 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>925</v>
+        <v>4020</v>
       </c>
       <c r="E173" t="n">
-        <v>-6.49</v>
+        <v>24.38</v>
       </c>
       <c r="F173" t="n">
-        <v>865</v>
+        <v>5000</v>
       </c>
       <c r="G173" t="n">
-        <v>865</v>
+        <v>5025</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SKIP_GAP_HIGH</t>
         </is>
       </c>
     </row>
@@ -8215,29 +7933,29 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>4020</v>
+        <v>925</v>
       </c>
       <c r="E174" t="n">
-        <v>24.38</v>
+        <v>-6.49</v>
       </c>
       <c r="F174" t="n">
-        <v>5000</v>
+        <v>865</v>
       </c>
       <c r="G174" t="n">
-        <v>5025</v>
+        <v>865</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>SKIP_GAP_HIGH</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -8252,33 +7970,30 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TMPO</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="E175" t="n">
-        <v>5.33</v>
+        <v>-6.12</v>
       </c>
       <c r="F175" t="n">
-        <v>178</v>
+        <v>92</v>
       </c>
       <c r="G175" t="n">
-        <v>194</v>
+        <v>92</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J175" t="n">
-        <v>8.44</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -8292,20 +8007,20 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>98</v>
+        <v>1820</v>
       </c>
       <c r="E176" t="n">
-        <v>-6.12</v>
+        <v>-6.87</v>
       </c>
       <c r="F176" t="n">
-        <v>92</v>
+        <v>1695</v>
       </c>
       <c r="G176" t="n">
-        <v>92</v>
+        <v>1695</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -8369,30 +8084,33 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>TMPO</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1820</v>
+        <v>169</v>
       </c>
       <c r="E178" t="n">
-        <v>-6.87</v>
+        <v>5.33</v>
       </c>
       <c r="F178" t="n">
-        <v>1695</v>
+        <v>178</v>
       </c>
       <c r="G178" t="n">
-        <v>1695</v>
+        <v>194</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>8.44</v>
       </c>
     </row>
     <row r="179">
@@ -8406,33 +8124,30 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>510</v>
+        <v>92</v>
       </c>
       <c r="E179" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>530</v>
+        <v>92</v>
       </c>
       <c r="G179" t="n">
-        <v>535</v>
+        <v>114</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J179" t="n">
-        <v>0.44</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -8446,24 +8161,24 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>102</v>
+        <v>5025</v>
       </c>
       <c r="E180" t="n">
-        <v>2.94</v>
+        <v>17.91</v>
       </c>
       <c r="F180" t="n">
-        <v>105</v>
+        <v>5925</v>
       </c>
       <c r="G180" t="n">
-        <v>137</v>
+        <v>6025</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8472,7 +8187,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>29.82</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="181">
@@ -8486,24 +8201,24 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>5025</v>
+        <v>510</v>
       </c>
       <c r="E181" t="n">
-        <v>17.91</v>
+        <v>3.92</v>
       </c>
       <c r="F181" t="n">
-        <v>5925</v>
+        <v>530</v>
       </c>
       <c r="G181" t="n">
-        <v>6025</v>
+        <v>535</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8512,7 +8227,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>1.18</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="182">
@@ -8526,24 +8241,24 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>92</v>
+        <v>348</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="F182" t="n">
-        <v>92</v>
+        <v>350</v>
       </c>
       <c r="G182" t="n">
-        <v>114</v>
+        <v>358</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8563,30 +8278,33 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>348</v>
+        <v>102</v>
       </c>
       <c r="E183" t="n">
-        <v>0.57</v>
+        <v>2.94</v>
       </c>
       <c r="F183" t="n">
-        <v>350</v>
+        <v>105</v>
       </c>
       <c r="G183" t="n">
-        <v>358</v>
+        <v>137</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>29.82</v>
       </c>
     </row>
     <row r="184">
@@ -8600,20 +8318,20 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>332</v>
+        <v>500</v>
       </c>
       <c r="E184" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>328</v>
+        <v>500</v>
       </c>
       <c r="G184" t="n">
-        <v>334</v>
+        <v>515</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -8674,24 +8392,24 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BAPA</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="E186" t="n">
-        <v>-1.72</v>
+        <v>-1.2</v>
       </c>
       <c r="F186" t="n">
-        <v>114</v>
+        <v>328</v>
       </c>
       <c r="G186" t="n">
-        <v>114</v>
+        <v>334</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -8711,24 +8429,24 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>BAPA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>500</v>
+        <v>116</v>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="F187" t="n">
-        <v>500</v>
+        <v>114</v>
       </c>
       <c r="G187" t="n">
-        <v>515</v>
+        <v>114</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -8748,24 +8466,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>PRDA</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>3500</v>
+        <v>118</v>
       </c>
       <c r="E188" t="n">
-        <v>-2.86</v>
+        <v>-4.24</v>
       </c>
       <c r="F188" t="n">
-        <v>3400</v>
+        <v>113</v>
       </c>
       <c r="G188" t="n">
-        <v>3680</v>
+        <v>140</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8785,24 +8503,24 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>PRDA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>118</v>
+        <v>3500</v>
       </c>
       <c r="E189" t="n">
-        <v>-4.24</v>
+        <v>-2.86</v>
       </c>
       <c r="F189" t="n">
-        <v>113</v>
+        <v>3400</v>
       </c>
       <c r="G189" t="n">
-        <v>140</v>
+        <v>3680</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -8822,29 +8540,29 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E190" t="n">
-        <v>33.58</v>
+        <v>0.75</v>
       </c>
       <c r="F190" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="G190" t="n">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -8859,20 +8577,20 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PRDA</t>
+          <t>DMAS</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>3590</v>
+        <v>218</v>
       </c>
       <c r="E191" t="n">
-        <v>0.28</v>
+        <v>0.92</v>
       </c>
       <c r="F191" t="n">
-        <v>3600</v>
+        <v>220</v>
       </c>
       <c r="G191" t="n">
-        <v>3750</v>
+        <v>220</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -8896,29 +8614,29 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E192" t="n">
-        <v>0.75</v>
+        <v>33.58</v>
       </c>
       <c r="F192" t="n">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="G192" t="n">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -8933,20 +8651,20 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DMAS</t>
+          <t>PRDA</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>218</v>
+        <v>3590</v>
       </c>
       <c r="E193" t="n">
-        <v>0.92</v>
+        <v>0.28</v>
       </c>
       <c r="F193" t="n">
-        <v>220</v>
+        <v>3600</v>
       </c>
       <c r="G193" t="n">
-        <v>220</v>
+        <v>3750</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -8970,24 +8688,24 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>AALI</t>
+          <t>WMPP</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>9625</v>
+        <v>26</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
       <c r="F194" t="n">
-        <v>9625</v>
+        <v>25</v>
       </c>
       <c r="G194" t="n">
-        <v>9800</v>
+        <v>31</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9007,30 +8725,33 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TCPI</t>
+          <t>TOBA</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1735</v>
+        <v>520</v>
       </c>
       <c r="E195" t="n">
-        <v>1.44</v>
+        <v>11.54</v>
       </c>
       <c r="F195" t="n">
-        <v>1760</v>
+        <v>580</v>
       </c>
       <c r="G195" t="n">
-        <v>1770</v>
+        <v>620</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>6.36</v>
       </c>
     </row>
     <row r="196">
@@ -9044,20 +8765,20 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>AALI</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>130</v>
+        <v>9625</v>
       </c>
       <c r="E196" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>131</v>
+        <v>9625</v>
       </c>
       <c r="G196" t="n">
-        <v>145</v>
+        <v>9800</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -9081,24 +8802,24 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PTSN</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="E197" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
       <c r="F197" t="n">
-        <v>392</v>
+        <v>131</v>
       </c>
       <c r="G197" t="n">
-        <v>428</v>
+        <v>145</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9118,20 +8839,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>PRDA</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3670</v>
+        <v>995</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.54</v>
+        <v>2.51</v>
       </c>
       <c r="F198" t="n">
-        <v>3650</v>
+        <v>1020</v>
       </c>
       <c r="G198" t="n">
-        <v>3760</v>
+        <v>1025</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -9140,8 +8861,11 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="199">
@@ -9155,30 +8879,33 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>WMPP</t>
+          <t>AYLS</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="E199" t="n">
-        <v>-3.85</v>
+        <v>3.67</v>
       </c>
       <c r="F199" t="n">
-        <v>25</v>
+        <v>226</v>
       </c>
       <c r="G199" t="n">
-        <v>31</v>
+        <v>226</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="200">
@@ -9192,24 +8919,24 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>IRSX</t>
+          <t>PTSN</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>272</v>
+        <v>390</v>
       </c>
       <c r="E200" t="n">
-        <v>-1.47</v>
+        <v>0.51</v>
       </c>
       <c r="F200" t="n">
-        <v>268</v>
+        <v>392</v>
       </c>
       <c r="G200" t="n">
-        <v>290</v>
+        <v>428</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9229,24 +8956,24 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>380</v>
+        <v>135</v>
       </c>
       <c r="E201" t="n">
-        <v>13.16</v>
+        <v>2.96</v>
       </c>
       <c r="F201" t="n">
-        <v>430</v>
+        <v>139</v>
       </c>
       <c r="G201" t="n">
-        <v>436</v>
+        <v>151</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9255,7 +8982,7 @@
         </is>
       </c>
       <c r="J201" t="n">
-        <v>0.89</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="202">
@@ -9269,24 +8996,24 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ENZO</t>
+          <t>PRDA</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>57</v>
+        <v>3670</v>
       </c>
       <c r="E202" t="n">
-        <v>1.75</v>
+        <v>-0.54</v>
       </c>
       <c r="F202" t="n">
-        <v>58</v>
+        <v>3650</v>
       </c>
       <c r="G202" t="n">
-        <v>59</v>
+        <v>3760</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9306,33 +9033,30 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>WMUU</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E203" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="G203" t="n">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J203" t="n">
-        <v>8.09</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -9346,33 +9070,30 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>AYLS</t>
+          <t>TCPI</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>218</v>
+        <v>1735</v>
       </c>
       <c r="E204" t="n">
-        <v>3.67</v>
+        <v>1.44</v>
       </c>
       <c r="F204" t="n">
-        <v>226</v>
+        <v>1760</v>
       </c>
       <c r="G204" t="n">
-        <v>226</v>
+        <v>1770</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="J204" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -9386,33 +9107,30 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>IRSX</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>995</v>
+        <v>272</v>
       </c>
       <c r="E205" t="n">
-        <v>2.51</v>
+        <v>-1.47</v>
       </c>
       <c r="F205" t="n">
-        <v>1020</v>
+        <v>268</v>
       </c>
       <c r="G205" t="n">
-        <v>1025</v>
+        <v>290</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="J205" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -9426,24 +9144,24 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>TOBA</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>520</v>
+        <v>380</v>
       </c>
       <c r="E206" t="n">
-        <v>11.54</v>
+        <v>13.16</v>
       </c>
       <c r="F206" t="n">
-        <v>580</v>
+        <v>430</v>
       </c>
       <c r="G206" t="n">
-        <v>620</v>
+        <v>436</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9452,7 +9170,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>6.36</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="207">
@@ -9466,27 +9184,400 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
+          <t>ENZO</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>57</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F207" t="n">
+        <v>58</v>
+      </c>
+      <c r="G207" t="n">
+        <v>59</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>STRK</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>139</v>
+      </c>
+      <c r="E208" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F208" t="n">
+        <v>143</v>
+      </c>
+      <c r="G208" t="n">
+        <v>144</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>BLES</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>228</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>228</v>
+      </c>
+      <c r="G209" t="n">
+        <v>230</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>DKHH</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>147</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>147</v>
+      </c>
+      <c r="G210" t="n">
+        <v>155</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>MBSS</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>4280</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F211" t="n">
+        <v>4360</v>
+      </c>
+      <c r="G211" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>TOBA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>505</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>505</v>
+      </c>
+      <c r="G212" t="n">
+        <v>520</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>TMPO</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>189</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="F213" t="n">
+        <v>185</v>
+      </c>
+      <c r="G213" t="n">
+        <v>236</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SBMA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>150</v>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="n">
+        <v>150</v>
+      </c>
+      <c r="G214" t="n">
+        <v>173</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SEMA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>430</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F215" t="n">
+        <v>432</v>
+      </c>
+      <c r="G215" t="n">
+        <v>460</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>PCAR</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>90</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="n">
+        <v>90</v>
+      </c>
+      <c r="G216" t="n">
+        <v>95</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Selasa</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
           <t>WMUU</t>
         </is>
       </c>
-      <c r="D207" t="n">
+      <c r="D217" t="n">
         <v>36</v>
       </c>
-      <c r="E207" t="n">
+      <c r="E217" t="n">
         <v>0</v>
       </c>
-      <c r="F207" t="n">
+      <c r="F217" t="n">
         <v>36</v>
       </c>
-      <c r="G207" t="n">
-        <v>47</v>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
+      <c r="G217" t="n">
+        <v>40</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
         <is>
           <t>SKIP_GAP_LOW</t>
         </is>
@@ -9497,7 +9588,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J207">
+  <conditionalFormatting sqref="J5:J217">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -523,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-27 18:45</t>
+          <t>Dibuat: 2026-10-28 17:26</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18">
@@ -797,7 +797,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-28</t>
+          <t>Prediksi untuk: 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -882,32 +882,32 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>TMPO</t>
+          <t>UNIQ</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>228</v>
+        <v>144</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>113.54</v>
+        <v>11.14</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>20.63</v>
+        <v>11.63</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>44.3</v>
+        <v>26.32</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>24.12</v>
+        <v>17.36</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>3.64</v>
+        <v>2.39</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>39.28</v>
+        <v>16.84</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>10.09</v>
+        <v>7.99</v>
       </c>
       <c r="M5" s="7" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -929,32 +929,32 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>TGUK</t>
+          <t>KOKA</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>22.85</v>
+        <v>18.54</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>23.46</v>
+        <v>22.12</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>26.58</v>
+        <v>33.98</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>28</v>
+        <v>26.09</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>2.46</v>
+        <v>5.83</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>17.71</v>
+        <v>11.18</v>
       </c>
       <c r="M6" s="7" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
@@ -976,36 +976,36 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>OKAS</t>
+          <t>PBID</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>105</v>
+        <v>595</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>6.79</v>
+        <v>9.91</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>19.32</v>
+        <v>13.33</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>25</v>
+        <v>15.53</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>14.29</v>
+        <v>20.17</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>4.18</v>
+        <v>3.97</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>9.890000000000001</v>
+        <v>14.09</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>7.14</v>
+        <v>4.33</v>
       </c>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -1023,32 +1023,32 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>WMUU</t>
+          <t>TMPO</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>34</v>
+        <v>214</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>7.69</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-5.56</v>
+        <v>-6.14</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>30.77</v>
+        <v>45.58</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>17.65</v>
+        <v>15.89</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.16</v>
+        <v>1.67</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>17.24</v>
+        <v>29.42</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>13.03</v>
+        <v>11.58</v>
       </c>
       <c r="M8" s="7" t="inlineStr">
         <is>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-26 s/d 2026-10-27</t>
+          <t>2026-10-26 s/d 2026-10-28</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J217"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1581,20 +1581,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RSCH</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>525</v>
+        <v>246</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-2.44</v>
       </c>
       <c r="F5" t="n">
-        <v>525</v>
+        <v>240</v>
       </c>
       <c r="G5" t="n">
-        <v>555</v>
+        <v>260</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1618,20 +1618,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MOLI</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>424</v>
+        <v>234</v>
       </c>
       <c r="E6" t="n">
-        <v>0.47</v>
+        <v>0.85</v>
       </c>
       <c r="F6" t="n">
-        <v>426</v>
+        <v>236</v>
       </c>
       <c r="G6" t="n">
-        <v>426</v>
+        <v>292</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1655,20 +1655,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>HELI</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.44</v>
+        <v>0.72</v>
       </c>
       <c r="F7" t="n">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c r="G7" t="n">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1692,24 +1692,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MTLA</t>
+          <t>MOLI</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>740</v>
+        <v>424</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="F8" t="n">
-        <v>740</v>
+        <v>426</v>
       </c>
       <c r="G8" t="n">
-        <v>745</v>
+        <v>426</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1729,33 +1729,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>MTLA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>740</v>
       </c>
       <c r="E9" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>740</v>
       </c>
       <c r="G9" t="n">
-        <v>72</v>
+        <v>745</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>8.550000000000001</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1769,30 +1766,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASGR</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2520</v>
+        <v>64</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="F10" t="n">
-        <v>2520</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>2540</v>
+        <v>72</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1806,24 +1806,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAPX</t>
+          <t>ASGR</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>404</v>
+        <v>2520</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>406</v>
+        <v>2520</v>
       </c>
       <c r="G11" t="n">
-        <v>486</v>
+        <v>2540</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1843,20 +1843,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6300</v>
+        <v>404</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.79</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>6250</v>
+        <v>406</v>
       </c>
       <c r="G12" t="n">
-        <v>6250</v>
+        <v>486</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1880,24 +1880,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SMLE</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.84</v>
       </c>
       <c r="F13" t="n">
-        <v>296</v>
+        <v>474</v>
       </c>
       <c r="G13" t="n">
-        <v>310</v>
+        <v>474</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1917,24 +1917,24 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>478</v>
+        <v>6300</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.84</v>
+        <v>-0.79</v>
       </c>
       <c r="F14" t="n">
-        <v>474</v>
+        <v>6250</v>
       </c>
       <c r="G14" t="n">
-        <v>474</v>
+        <v>6250</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HELI</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="E15" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="G15" t="n">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1991,20 +1991,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>RSCH</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1130</v>
+        <v>525</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.44</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1125</v>
+        <v>525</v>
       </c>
       <c r="G16" t="n">
-        <v>1410</v>
+        <v>555</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2028,20 +2028,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>SOSS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>234</v>
+        <v>1180</v>
       </c>
       <c r="E17" t="n">
-        <v>0.85</v>
+        <v>-5.51</v>
       </c>
       <c r="F17" t="n">
-        <v>236</v>
+        <v>1115</v>
       </c>
       <c r="G17" t="n">
-        <v>292</v>
+        <v>1160</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2065,20 +2065,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SOSS</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1180</v>
+        <v>1130</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.51</v>
+        <v>-0.44</v>
       </c>
       <c r="F18" t="n">
-        <v>1115</v>
+        <v>1125</v>
       </c>
       <c r="G18" t="n">
-        <v>1160</v>
+        <v>1410</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>705</v>
+        <v>284</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.55</v>
+        <v>0.7</v>
       </c>
       <c r="F19" t="n">
-        <v>680</v>
+        <v>286</v>
       </c>
       <c r="G19" t="n">
-        <v>745</v>
+        <v>304</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2139,33 +2139,30 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CCSI</t>
+          <t>MTLA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>470</v>
+        <v>690</v>
       </c>
       <c r="E20" t="n">
-        <v>11.7</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="G20" t="n">
-        <v>560</v>
+        <v>725</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>6.13</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2179,24 +2176,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MTLA</t>
+          <t>UNIQ</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>690</v>
+        <v>137</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.699999999999999</v>
+        <v>-1.46</v>
       </c>
       <c r="F21" t="n">
-        <v>630</v>
+        <v>135</v>
       </c>
       <c r="G21" t="n">
-        <v>725</v>
+        <v>147</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2216,24 +2213,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>CCSI</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1155</v>
+        <v>470</v>
       </c>
       <c r="E22" t="n">
-        <v>3.9</v>
+        <v>11.7</v>
       </c>
       <c r="F22" t="n">
-        <v>1200</v>
+        <v>525</v>
       </c>
       <c r="G22" t="n">
-        <v>1290</v>
+        <v>560</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2242,7 +2239,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6.96</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="23">
@@ -2256,29 +2253,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SAPX</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>444</v>
+        <v>4230</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9</v>
+        <v>-4.96</v>
       </c>
       <c r="F23" t="n">
-        <v>448</v>
+        <v>4020</v>
       </c>
       <c r="G23" t="n">
-        <v>466</v>
+        <v>4860</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -2293,20 +2290,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3520</v>
+        <v>444</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="F24" t="n">
-        <v>3520</v>
+        <v>448</v>
       </c>
       <c r="G24" t="n">
-        <v>3710</v>
+        <v>466</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2315,7 +2312,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -2330,24 +2327,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNIQ</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>137</v>
+        <v>422</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.46</v>
+        <v>1.42</v>
       </c>
       <c r="F25" t="n">
-        <v>135</v>
+        <v>428</v>
       </c>
       <c r="G25" t="n">
-        <v>147</v>
+        <v>480</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2367,24 +2364,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>422</v>
+        <v>705</v>
       </c>
       <c r="E26" t="n">
-        <v>1.42</v>
+        <v>-3.55</v>
       </c>
       <c r="F26" t="n">
-        <v>428</v>
+        <v>680</v>
       </c>
       <c r="G26" t="n">
-        <v>480</v>
+        <v>745</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2404,20 +2401,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SMLE</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>284</v>
+        <v>1155</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="F27" t="n">
-        <v>286</v>
+        <v>1200</v>
       </c>
       <c r="G27" t="n">
-        <v>304</v>
+        <v>1290</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2426,8 +2423,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>6.96</v>
       </c>
     </row>
     <row r="28">
@@ -2478,24 +2478,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4230</v>
+        <v>3520</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.96</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>4020</v>
+        <v>3520</v>
       </c>
       <c r="G29" t="n">
-        <v>4860</v>
+        <v>3710</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2552,30 +2552,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SMLE</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="E31" t="n">
-        <v>0.66</v>
+        <v>2.41</v>
       </c>
       <c r="F31" t="n">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="G31" t="n">
-        <v>310</v>
+        <v>414</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>21.16</v>
       </c>
     </row>
     <row r="32">
@@ -2626,20 +2629,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ASGR</t>
+          <t>SMLE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2520</v>
+        <v>302</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4</v>
+        <v>0.66</v>
       </c>
       <c r="F33" t="n">
-        <v>2530</v>
+        <v>304</v>
       </c>
       <c r="G33" t="n">
-        <v>2550</v>
+        <v>310</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2663,33 +2666,30 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>ASGR</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>470</v>
+        <v>2520</v>
       </c>
       <c r="E34" t="n">
-        <v>2.55</v>
+        <v>0.4</v>
       </c>
       <c r="F34" t="n">
-        <v>482</v>
+        <v>2530</v>
       </c>
       <c r="G34" t="n">
-        <v>525</v>
+        <v>2550</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>8.380000000000001</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2743,24 +2743,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SAMF</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>360</v>
+        <v>470</v>
       </c>
       <c r="E36" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="F36" t="n">
-        <v>372</v>
+        <v>482</v>
       </c>
       <c r="G36" t="n">
-        <v>386</v>
+        <v>525</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>3.24</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2783,30 +2783,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>SAMF</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3760</v>
+        <v>360</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.33</v>
+        <v>3.33</v>
       </c>
       <c r="F37" t="n">
-        <v>3710</v>
+        <v>372</v>
       </c>
       <c r="G37" t="n">
-        <v>3990</v>
+        <v>386</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="38">
@@ -2820,33 +2823,30 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>332</v>
+        <v>3760</v>
       </c>
       <c r="E38" t="n">
-        <v>2.41</v>
+        <v>-1.33</v>
       </c>
       <c r="F38" t="n">
-        <v>340</v>
+        <v>3710</v>
       </c>
       <c r="G38" t="n">
-        <v>414</v>
+        <v>3990</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>21.16</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2860,24 +2860,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DAAZ</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2200</v>
+        <v>71</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>2190</v>
+        <v>71</v>
       </c>
       <c r="G39" t="n">
-        <v>2190</v>
+        <v>74</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2897,33 +2897,30 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CSMI</t>
+          <t>SAPX</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="E40" t="n">
-        <v>5.34</v>
+        <v>1.37</v>
       </c>
       <c r="F40" t="n">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="G40" t="n">
-        <v>515</v>
+        <v>450</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>18.07</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2937,30 +2934,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DEWI</t>
+          <t>CSMI</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>260</v>
+        <v>412</v>
       </c>
       <c r="E41" t="n">
-        <v>0.77</v>
+        <v>5.34</v>
       </c>
       <c r="F41" t="n">
-        <v>262</v>
+        <v>434</v>
       </c>
       <c r="G41" t="n">
-        <v>262</v>
+        <v>515</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>18.07</v>
       </c>
     </row>
     <row r="42">
@@ -2974,33 +2974,30 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MPIX</t>
+          <t>DAAZ</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>224</v>
+        <v>2200</v>
       </c>
       <c r="E42" t="n">
-        <v>2.68</v>
+        <v>-0.45</v>
       </c>
       <c r="F42" t="n">
-        <v>230</v>
+        <v>2190</v>
       </c>
       <c r="G42" t="n">
-        <v>232</v>
+        <v>2190</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>0.37</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3014,33 +3011,30 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>DEWI</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="E43" t="n">
-        <v>2.86</v>
+        <v>0.77</v>
       </c>
       <c r="F43" t="n">
-        <v>360</v>
+        <v>262</v>
       </c>
       <c r="G43" t="n">
-        <v>404</v>
+        <v>262</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>11.66</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3054,24 +3048,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>PPRI</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-3.23</v>
       </c>
       <c r="F44" t="n">
-        <v>71</v>
+        <v>180</v>
       </c>
       <c r="G44" t="n">
-        <v>74</v>
+        <v>196</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3131,30 +3125,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PPRI</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>186</v>
+        <v>530</v>
       </c>
       <c r="E46" t="n">
-        <v>-3.23</v>
+        <v>3.77</v>
       </c>
       <c r="F46" t="n">
-        <v>180</v>
+        <v>550</v>
       </c>
       <c r="G46" t="n">
-        <v>196</v>
+        <v>660</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>19.4</v>
       </c>
     </row>
     <row r="47">
@@ -3168,30 +3165,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BLUE</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3590</v>
+        <v>350</v>
       </c>
       <c r="E47" t="n">
-        <v>1.11</v>
+        <v>2.86</v>
       </c>
       <c r="F47" t="n">
-        <v>3630</v>
+        <v>360</v>
       </c>
       <c r="G47" t="n">
-        <v>4100</v>
+        <v>404</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>11.66</v>
       </c>
     </row>
     <row r="48">
@@ -3205,24 +3205,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SAPX</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>438</v>
+        <v>61</v>
       </c>
       <c r="E48" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="F48" t="n">
-        <v>444</v>
+        <v>62</v>
       </c>
       <c r="G48" t="n">
-        <v>450</v>
+        <v>63</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3242,24 +3242,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SOTS</t>
+          <t>MPIX</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>630</v>
+        <v>224</v>
       </c>
       <c r="E49" t="n">
-        <v>3.97</v>
+        <v>2.68</v>
       </c>
       <c r="F49" t="n">
-        <v>655</v>
+        <v>230</v>
       </c>
       <c r="G49" t="n">
-        <v>675</v>
+        <v>232</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>2.54</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="50">
@@ -3282,30 +3282,33 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>SOTS</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>61</v>
+        <v>630</v>
       </c>
       <c r="E50" t="n">
-        <v>1.64</v>
+        <v>3.97</v>
       </c>
       <c r="F50" t="n">
-        <v>62</v>
+        <v>655</v>
       </c>
       <c r="G50" t="n">
-        <v>63</v>
+        <v>675</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>2.54</v>
       </c>
     </row>
     <row r="51">
@@ -3319,20 +3322,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>WAPO</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>530</v>
+        <v>352</v>
       </c>
       <c r="E51" t="n">
-        <v>3.77</v>
+        <v>3.41</v>
       </c>
       <c r="F51" t="n">
-        <v>550</v>
+        <v>364</v>
       </c>
       <c r="G51" t="n">
-        <v>660</v>
+        <v>400</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3341,11 +3344,8 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>19.4</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3359,29 +3359,29 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>WAPO</t>
+          <t>BLUE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>352</v>
+        <v>3590</v>
       </c>
       <c r="E52" t="n">
-        <v>3.41</v>
+        <v>1.11</v>
       </c>
       <c r="F52" t="n">
-        <v>364</v>
+        <v>3630</v>
       </c>
       <c r="G52" t="n">
-        <v>400</v>
+        <v>4100</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -3433,29 +3433,29 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>ASLI</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1270</v>
+        <v>486</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="F54" t="n">
-        <v>1270</v>
+        <v>496</v>
       </c>
       <c r="G54" t="n">
-        <v>1280</v>
+        <v>540</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -3470,29 +3470,29 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ASLI</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>486</v>
+        <v>1270</v>
       </c>
       <c r="E55" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>496</v>
+        <v>1270</v>
       </c>
       <c r="G55" t="n">
-        <v>540</v>
+        <v>1280</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -3544,20 +3544,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>BALI</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>318</v>
+        <v>1560</v>
       </c>
       <c r="E57" t="n">
-        <v>13.21</v>
+        <v>-1.92</v>
       </c>
       <c r="F57" t="n">
-        <v>360</v>
+        <v>1530</v>
       </c>
       <c r="G57" t="n">
-        <v>396</v>
+        <v>1530</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3566,11 +3566,8 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>9.449999999999999</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3584,20 +3581,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>ASLI</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="E58" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>72</v>
+        <v>500</v>
       </c>
       <c r="G58" t="n">
-        <v>83</v>
+        <v>500</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3606,11 +3603,8 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>14.7</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -3698,24 +3692,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BALI</t>
+          <t>IATA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1560</v>
+        <v>115</v>
       </c>
       <c r="E61" t="n">
-        <v>-1.92</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>1530</v>
+        <v>115</v>
       </c>
       <c r="G61" t="n">
-        <v>1530</v>
+        <v>115</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3735,20 +3729,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WAPO</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>326</v>
+        <v>70</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="F62" t="n">
-        <v>326</v>
+        <v>72</v>
       </c>
       <c r="G62" t="n">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3757,8 +3751,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>14.7</v>
       </c>
     </row>
     <row r="63">
@@ -3772,30 +3769,33 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BDKR</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>210</v>
+        <v>318</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>13.21</v>
       </c>
       <c r="F63" t="n">
-        <v>210</v>
+        <v>360</v>
       </c>
       <c r="G63" t="n">
-        <v>230</v>
+        <v>396</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -3809,24 +3809,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IATA</t>
+          <t>BDKR</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>115</v>
+        <v>210</v>
       </c>
       <c r="G64" t="n">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3846,24 +3846,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>KLAS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4400</v>
+        <v>82</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>4400</v>
+        <v>82</v>
       </c>
       <c r="G65" t="n">
-        <v>4500</v>
+        <v>90</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KLAS</t>
+          <t>KDTN</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>82</v>
+        <v>655</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>-2.29</v>
       </c>
       <c r="F66" t="n">
-        <v>82</v>
+        <v>640</v>
       </c>
       <c r="G66" t="n">
-        <v>90</v>
+        <v>640</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3960,29 +3960,29 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KDTN</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>655</v>
+        <v>825</v>
       </c>
       <c r="E68" t="n">
-        <v>-2.29</v>
+        <v>10.3</v>
       </c>
       <c r="F68" t="n">
-        <v>640</v>
+        <v>910</v>
       </c>
       <c r="G68" t="n">
-        <v>640</v>
+        <v>1030</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -4074,29 +4074,29 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>825</v>
+        <v>4400</v>
       </c>
       <c r="E71" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>910</v>
+        <v>4400</v>
       </c>
       <c r="G71" t="n">
-        <v>1030</v>
+        <v>4500</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -4111,20 +4111,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ASLI</t>
+          <t>WAPO</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>500</v>
+        <v>326</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>500</v>
+        <v>326</v>
       </c>
       <c r="G72" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4148,24 +4148,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>INCI</t>
+          <t>ENAK</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1025</v>
+        <v>214</v>
       </c>
       <c r="E73" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>1030</v>
+        <v>214</v>
       </c>
       <c r="G73" t="n">
-        <v>1065</v>
+        <v>216</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4185,20 +4185,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HELI</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>342</v>
+        <v>1230</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="F74" t="n">
-        <v>342</v>
+        <v>1255</v>
       </c>
       <c r="G74" t="n">
-        <v>402</v>
+        <v>1320</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -4207,8 +4207,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>4.65</v>
       </c>
     </row>
     <row r="75">
@@ -4222,20 +4225,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MITI</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>354</v>
+        <v>4500</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.13</v>
+        <v>-1.33</v>
       </c>
       <c r="F75" t="n">
-        <v>350</v>
+        <v>4440</v>
       </c>
       <c r="G75" t="n">
-        <v>374</v>
+        <v>4440</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -4259,20 +4262,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MPIX</t>
+          <t>MITI</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>220</v>
+        <v>354</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="F76" t="n">
-        <v>220</v>
+        <v>350</v>
       </c>
       <c r="G76" t="n">
-        <v>224</v>
+        <v>374</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -4296,33 +4299,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ASLI</t>
+          <t>HELI</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>464</v>
+        <v>342</v>
       </c>
       <c r="E77" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>480</v>
+        <v>342</v>
       </c>
       <c r="G77" t="n">
-        <v>496</v>
+        <v>402</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>2.82</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -4336,20 +4336,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>INCI</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1230</v>
+        <v>1025</v>
       </c>
       <c r="E78" t="n">
-        <v>2.03</v>
+        <v>0.49</v>
       </c>
       <c r="F78" t="n">
-        <v>1255</v>
+        <v>1030</v>
       </c>
       <c r="G78" t="n">
-        <v>1320</v>
+        <v>1065</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4358,11 +4358,8 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>4.65</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4376,30 +4373,33 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ENAK</t>
+          <t>ASLI</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>214</v>
+        <v>464</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="F79" t="n">
-        <v>214</v>
+        <v>480</v>
       </c>
       <c r="G79" t="n">
-        <v>216</v>
+        <v>496</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>2.82</v>
       </c>
     </row>
     <row r="80">
@@ -4413,20 +4413,20 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>MPIX</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4500</v>
+        <v>220</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.33</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>4440</v>
+        <v>220</v>
       </c>
       <c r="G80" t="n">
-        <v>4440</v>
+        <v>224</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -4524,33 +4524,30 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>BLUE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>7550</v>
+        <v>3900</v>
       </c>
       <c r="E83" t="n">
-        <v>3.97</v>
+        <v>0.77</v>
       </c>
       <c r="F83" t="n">
-        <v>7850</v>
+        <v>3930</v>
       </c>
       <c r="G83" t="n">
-        <v>8700</v>
+        <v>4510</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>10.27</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -4564,30 +4561,33 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BLUE</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3900</v>
+        <v>7550</v>
       </c>
       <c r="E84" t="n">
-        <v>0.77</v>
+        <v>3.97</v>
       </c>
       <c r="F84" t="n">
-        <v>3930</v>
+        <v>7850</v>
       </c>
       <c r="G84" t="n">
-        <v>4510</v>
+        <v>8700</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>10.27</v>
       </c>
     </row>
     <row r="85">
@@ -4940,29 +4940,29 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>6800</v>
+        <v>316</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>-8.23</v>
       </c>
       <c r="F94" t="n">
-        <v>6800</v>
+        <v>290</v>
       </c>
       <c r="G94" t="n">
-        <v>7225</v>
+        <v>332</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -4977,29 +4977,29 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>PKPK</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>316</v>
+        <v>6800</v>
       </c>
       <c r="E95" t="n">
-        <v>-8.23</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>290</v>
+        <v>6800</v>
       </c>
       <c r="G95" t="n">
-        <v>332</v>
+        <v>7225</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -5165,20 +5165,20 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>INCI</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1050</v>
+        <v>1295</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="F100" t="n">
-        <v>1050</v>
+        <v>1320</v>
       </c>
       <c r="G100" t="n">
-        <v>1070</v>
+        <v>1325</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -5202,20 +5202,20 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>INCI</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1295</v>
+        <v>1050</v>
       </c>
       <c r="E101" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>1320</v>
+        <v>1050</v>
       </c>
       <c r="G101" t="n">
-        <v>1325</v>
+        <v>1070</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -5239,24 +5239,24 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HELI</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>342</v>
+        <v>1715</v>
       </c>
       <c r="E102" t="n">
-        <v>1.75</v>
+        <v>-0.58</v>
       </c>
       <c r="F102" t="n">
-        <v>348</v>
+        <v>1705</v>
       </c>
       <c r="G102" t="n">
-        <v>352</v>
+        <v>2140</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5276,20 +5276,20 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BDKR</t>
+          <t>HELI</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>212</v>
+        <v>342</v>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="F103" t="n">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="G103" t="n">
-        <v>218</v>
+        <v>352</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -5313,24 +5313,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>BDKR</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1715</v>
+        <v>212</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.58</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>1705</v>
+        <v>212</v>
       </c>
       <c r="G104" t="n">
-        <v>2140</v>
+        <v>218</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5390,20 +5390,20 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1020</v>
+        <v>90</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>1020</v>
+        <v>90</v>
       </c>
       <c r="G106" t="n">
-        <v>1075</v>
+        <v>100</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -5427,20 +5427,20 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="F107" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G107" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -5449,8 +5449,11 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>15.51</v>
       </c>
     </row>
     <row r="108">
@@ -5464,20 +5467,20 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1250</v>
+        <v>388</v>
       </c>
       <c r="E108" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>1310</v>
+        <v>388</v>
       </c>
       <c r="G108" t="n">
-        <v>1445</v>
+        <v>434</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -5486,11 +5489,8 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>9.75</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -5541,24 +5541,24 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SOSS</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1200</v>
+        <v>290</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>1200</v>
+        <v>292</v>
       </c>
       <c r="G110" t="n">
-        <v>1260</v>
+        <v>294</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5578,20 +5578,20 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2140</v>
+        <v>3990</v>
       </c>
       <c r="E111" t="n">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>2270</v>
+        <v>3990</v>
       </c>
       <c r="G111" t="n">
-        <v>2670</v>
+        <v>4000</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -5600,11 +5600,8 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>17.03</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -5618,20 +5615,20 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>83</v>
+        <v>980</v>
       </c>
       <c r="E112" t="n">
-        <v>4.82</v>
+        <v>2.55</v>
       </c>
       <c r="F112" t="n">
-        <v>87</v>
+        <v>1005</v>
       </c>
       <c r="G112" t="n">
-        <v>101</v>
+        <v>1115</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -5640,11 +5637,8 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>15.51</v>
+          <t>SUSPENDED</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -5658,30 +5652,33 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>388</v>
+        <v>2140</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="F113" t="n">
-        <v>388</v>
+        <v>2270</v>
       </c>
       <c r="G113" t="n">
-        <v>434</v>
+        <v>2670</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>17.03</v>
       </c>
     </row>
     <row r="114">
@@ -5695,20 +5692,20 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>POLA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="E114" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.85</v>
       </c>
       <c r="F114" t="n">
-        <v>292</v>
+        <v>110</v>
       </c>
       <c r="G114" t="n">
-        <v>294</v>
+        <v>121</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -5732,29 +5729,29 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>TEBE</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>980</v>
+        <v>2800</v>
       </c>
       <c r="E115" t="n">
-        <v>2.55</v>
+        <v>1.43</v>
       </c>
       <c r="F115" t="n">
-        <v>1005</v>
+        <v>2840</v>
       </c>
       <c r="G115" t="n">
-        <v>1115</v>
+        <v>3100</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -5769,30 +5766,33 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>DAAZ</t>
+          <t>TCPI</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2420</v>
+        <v>1625</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>14.46</v>
       </c>
       <c r="F116" t="n">
-        <v>2420</v>
+        <v>1860</v>
       </c>
       <c r="G116" t="n">
-        <v>2940</v>
+        <v>1865</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="117">
@@ -5806,24 +5806,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>POLA</t>
+          <t>DAAZ</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>108</v>
+        <v>2420</v>
       </c>
       <c r="E117" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>110</v>
+        <v>2420</v>
       </c>
       <c r="G117" t="n">
-        <v>121</v>
+        <v>2940</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5843,20 +5843,20 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TEBE</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2800</v>
+        <v>420</v>
       </c>
       <c r="E118" t="n">
-        <v>1.43</v>
+        <v>1.9</v>
       </c>
       <c r="F118" t="n">
-        <v>2840</v>
+        <v>428</v>
       </c>
       <c r="G118" t="n">
-        <v>3100</v>
+        <v>478</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -5880,33 +5880,30 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TCPI</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1625</v>
+        <v>4600</v>
       </c>
       <c r="E119" t="n">
-        <v>14.46</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>1860</v>
+        <v>4600</v>
       </c>
       <c r="G119" t="n">
-        <v>1865</v>
+        <v>4660</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -5920,24 +5917,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>420</v>
+        <v>1020</v>
       </c>
       <c r="E120" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>428</v>
+        <v>1020</v>
       </c>
       <c r="G120" t="n">
-        <v>478</v>
+        <v>1075</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5957,30 +5954,33 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>4600</v>
+        <v>1250</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="F121" t="n">
-        <v>4600</v>
+        <v>1310</v>
       </c>
       <c r="G121" t="n">
-        <v>4660</v>
+        <v>1445</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>9.75</v>
       </c>
     </row>
     <row r="122">
@@ -5994,20 +5994,20 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>SOSS</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3990</v>
+        <v>1200</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>3990</v>
+        <v>1200</v>
       </c>
       <c r="G122" t="n">
-        <v>4000</v>
+        <v>1260</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -6031,20 +6031,20 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PGLI</t>
+          <t>PKPK</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>376</v>
+        <v>7650</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>376</v>
+        <v>7650</v>
       </c>
       <c r="G123" t="n">
-        <v>390</v>
+        <v>7675</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -6105,24 +6105,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DAAZ</t>
+          <t>PGLI</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>2730</v>
+        <v>376</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>2720</v>
+        <v>376</v>
       </c>
       <c r="G125" t="n">
-        <v>2720</v>
+        <v>390</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6142,20 +6142,20 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>408</v>
+        <v>98</v>
       </c>
       <c r="E126" t="n">
-        <v>-1.47</v>
+        <v>2.04</v>
       </c>
       <c r="F126" t="n">
-        <v>402</v>
+        <v>100</v>
       </c>
       <c r="G126" t="n">
-        <v>484</v>
+        <v>103</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -6164,8 +6164,11 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>2.49</v>
       </c>
     </row>
     <row r="127">
@@ -6179,24 +6182,24 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PKPK</t>
+          <t>DAAZ</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7650</v>
+        <v>2730</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="F127" t="n">
-        <v>7650</v>
+        <v>2720</v>
       </c>
       <c r="G127" t="n">
-        <v>7675</v>
+        <v>2720</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6216,33 +6219,30 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>98</v>
+        <v>2670</v>
       </c>
       <c r="E128" t="n">
-        <v>2.04</v>
+        <v>21.72</v>
       </c>
       <c r="F128" t="n">
-        <v>100</v>
+        <v>3250</v>
       </c>
       <c r="G128" t="n">
-        <v>103</v>
+        <v>3330</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J128" t="n">
-        <v>2.49</v>
+          <t>SKIP_GAP_HIGH</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -6256,29 +6256,29 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>SMMT</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2670</v>
+        <v>3710</v>
       </c>
       <c r="E129" t="n">
-        <v>21.72</v>
+        <v>1.08</v>
       </c>
       <c r="F129" t="n">
-        <v>3250</v>
+        <v>3750</v>
       </c>
       <c r="G129" t="n">
-        <v>3330</v>
+        <v>3830</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>SKIP_GAP_HIGH</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -6367,20 +6367,20 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>92</v>
+        <v>1090</v>
       </c>
       <c r="E132" t="n">
-        <v>-3.26</v>
+        <v>0.46</v>
       </c>
       <c r="F132" t="n">
-        <v>89</v>
+        <v>1095</v>
       </c>
       <c r="G132" t="n">
-        <v>92</v>
+        <v>1120</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -6404,20 +6404,20 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1090</v>
+        <v>92</v>
       </c>
       <c r="E133" t="n">
-        <v>0.46</v>
+        <v>-3.26</v>
       </c>
       <c r="F133" t="n">
-        <v>1095</v>
+        <v>89</v>
       </c>
       <c r="G133" t="n">
-        <v>1120</v>
+        <v>92</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -6478,20 +6478,20 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SMMT</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>3710</v>
+        <v>408</v>
       </c>
       <c r="E135" t="n">
-        <v>1.08</v>
+        <v>-1.47</v>
       </c>
       <c r="F135" t="n">
-        <v>3750</v>
+        <v>402</v>
       </c>
       <c r="G135" t="n">
-        <v>3830</v>
+        <v>484</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -6626,20 +6626,20 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>7800</v>
+        <v>458</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="F139" t="n">
-        <v>7800</v>
+        <v>464</v>
       </c>
       <c r="G139" t="n">
-        <v>7975</v>
+        <v>494</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -6663,24 +6663,24 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>458</v>
+        <v>97</v>
       </c>
       <c r="E140" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>464</v>
+        <v>97</v>
       </c>
       <c r="G140" t="n">
-        <v>494</v>
+        <v>102</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6700,24 +6700,24 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>SBMA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>-1.39</v>
       </c>
       <c r="F141" t="n">
-        <v>97</v>
+        <v>142</v>
       </c>
       <c r="G141" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6737,30 +6737,33 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>PICO</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>3330</v>
+        <v>194</v>
       </c>
       <c r="E142" t="n">
-        <v>0.6</v>
+        <v>8.25</v>
       </c>
       <c r="F142" t="n">
-        <v>3350</v>
+        <v>210</v>
       </c>
       <c r="G142" t="n">
-        <v>4160</v>
+        <v>220</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>4.24</v>
       </c>
     </row>
     <row r="143">
@@ -6774,33 +6777,30 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PICO</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>194</v>
+        <v>90</v>
       </c>
       <c r="E143" t="n">
-        <v>8.25</v>
+        <v>-4.44</v>
       </c>
       <c r="F143" t="n">
-        <v>210</v>
+        <v>86</v>
       </c>
       <c r="G143" t="n">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J143" t="n">
-        <v>4.24</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -6814,24 +6814,24 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>SOSS</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>90</v>
+        <v>1240</v>
       </c>
       <c r="E144" t="n">
-        <v>-4.44</v>
+        <v>-0.4</v>
       </c>
       <c r="F144" t="n">
-        <v>86</v>
+        <v>1235</v>
       </c>
       <c r="G144" t="n">
-        <v>115</v>
+        <v>1235</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -6851,30 +6851,33 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SOSS</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1240</v>
+        <v>1400</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.4</v>
+        <v>2.86</v>
       </c>
       <c r="F145" t="n">
-        <v>1235</v>
+        <v>1440</v>
       </c>
       <c r="G145" t="n">
-        <v>1235</v>
+        <v>1750</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>20.92</v>
       </c>
     </row>
     <row r="146">
@@ -6888,33 +6891,30 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1400</v>
+        <v>7800</v>
       </c>
       <c r="E146" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>1440</v>
+        <v>7800</v>
       </c>
       <c r="G146" t="n">
-        <v>1750</v>
+        <v>7975</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J146" t="n">
-        <v>20.92</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -6928,24 +6928,24 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SBMA</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>144</v>
+        <v>3330</v>
       </c>
       <c r="E147" t="n">
-        <v>-1.39</v>
+        <v>0.6</v>
       </c>
       <c r="F147" t="n">
-        <v>142</v>
+        <v>3350</v>
       </c>
       <c r="G147" t="n">
-        <v>142</v>
+        <v>4160</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6965,24 +6965,24 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BELI</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>314</v>
+        <v>107</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>-1.87</v>
       </c>
       <c r="F148" t="n">
-        <v>314</v>
+        <v>105</v>
       </c>
       <c r="G148" t="n">
-        <v>336</v>
+        <v>115</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7002,33 +7002,30 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>BELI</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4160</v>
+        <v>314</v>
       </c>
       <c r="E149" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>4370</v>
+        <v>314</v>
       </c>
       <c r="G149" t="n">
-        <v>4930</v>
+        <v>336</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J149" t="n">
-        <v>12.25</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -7042,20 +7039,20 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1565</v>
+        <v>4160</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="F150" t="n">
-        <v>1565</v>
+        <v>4370</v>
       </c>
       <c r="G150" t="n">
-        <v>1955</v>
+        <v>4930</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -7064,8 +7061,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>12.25</v>
       </c>
     </row>
     <row r="151">
@@ -7079,24 +7079,24 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SAFE</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>950</v>
+        <v>1565</v>
       </c>
       <c r="E151" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>965</v>
+        <v>1565</v>
       </c>
       <c r="G151" t="n">
-        <v>1020</v>
+        <v>1955</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7156,24 +7156,24 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>SAFE</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>107</v>
+        <v>950</v>
       </c>
       <c r="E153" t="n">
-        <v>-1.87</v>
+        <v>1.58</v>
       </c>
       <c r="F153" t="n">
-        <v>105</v>
+        <v>965</v>
       </c>
       <c r="G153" t="n">
-        <v>115</v>
+        <v>1020</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7230,24 +7230,24 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TRON</t>
+          <t>HATM</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>101</v>
+        <v>670</v>
       </c>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F155" t="n">
-        <v>101</v>
+        <v>675</v>
       </c>
       <c r="G155" t="n">
-        <v>101</v>
+        <v>680</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7267,24 +7267,24 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BAIK</t>
+          <t>TRON</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>282</v>
+        <v>101</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>282</v>
+        <v>101</v>
       </c>
       <c r="G156" t="n">
-        <v>318</v>
+        <v>101</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7378,20 +7378,20 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>HATM</t>
+          <t>BAIK</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>670</v>
+        <v>282</v>
       </c>
       <c r="E159" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>675</v>
+        <v>282</v>
       </c>
       <c r="G159" t="n">
-        <v>680</v>
+        <v>318</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -7415,20 +7415,20 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HATM</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>665</v>
+        <v>108</v>
       </c>
       <c r="E160" t="n">
-        <v>-14.29</v>
+        <v>-14.81</v>
       </c>
       <c r="F160" t="n">
-        <v>570</v>
+        <v>92</v>
       </c>
       <c r="G160" t="n">
-        <v>605</v>
+        <v>105</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7452,24 +7452,24 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SBMA</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>148</v>
+        <v>310</v>
       </c>
       <c r="E161" t="n">
-        <v>-14.86</v>
+        <v>-14.84</v>
       </c>
       <c r="F161" t="n">
-        <v>126</v>
+        <v>264</v>
       </c>
       <c r="G161" t="n">
-        <v>131</v>
+        <v>294</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7489,24 +7489,24 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>HATM</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>116</v>
+        <v>665</v>
       </c>
       <c r="E162" t="n">
-        <v>-14.66</v>
+        <v>-14.29</v>
       </c>
       <c r="F162" t="n">
-        <v>99</v>
+        <v>570</v>
       </c>
       <c r="G162" t="n">
-        <v>99</v>
+        <v>605</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7526,24 +7526,24 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="E163" t="n">
-        <v>-14.81</v>
+        <v>-14.61</v>
       </c>
       <c r="F163" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G163" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7563,29 +7563,29 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>89</v>
+        <v>2580</v>
       </c>
       <c r="E164" t="n">
-        <v>-14.61</v>
+        <v>24.81</v>
       </c>
       <c r="F164" t="n">
-        <v>76</v>
+        <v>3220</v>
       </c>
       <c r="G164" t="n">
-        <v>89</v>
+        <v>3220</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -7600,20 +7600,20 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>310</v>
+        <v>4370</v>
       </c>
       <c r="E165" t="n">
-        <v>-14.84</v>
+        <v>-14.19</v>
       </c>
       <c r="F165" t="n">
-        <v>264</v>
+        <v>3750</v>
       </c>
       <c r="G165" t="n">
-        <v>294</v>
+        <v>4800</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -7637,24 +7637,24 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>470</v>
+        <v>116</v>
       </c>
       <c r="E166" t="n">
-        <v>-12.77</v>
+        <v>-14.66</v>
       </c>
       <c r="F166" t="n">
-        <v>410</v>
+        <v>99</v>
       </c>
       <c r="G166" t="n">
-        <v>438</v>
+        <v>99</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -7674,20 +7674,20 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4370</v>
+        <v>470</v>
       </c>
       <c r="E167" t="n">
-        <v>-14.19</v>
+        <v>-12.77</v>
       </c>
       <c r="F167" t="n">
-        <v>3750</v>
+        <v>410</v>
       </c>
       <c r="G167" t="n">
-        <v>4800</v>
+        <v>438</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -7711,29 +7711,29 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>SBMA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>2580</v>
+        <v>148</v>
       </c>
       <c r="E168" t="n">
-        <v>24.81</v>
+        <v>-14.86</v>
       </c>
       <c r="F168" t="n">
-        <v>3220</v>
+        <v>126</v>
       </c>
       <c r="G168" t="n">
-        <v>3220</v>
+        <v>131</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -7748,29 +7748,29 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3220</v>
+        <v>1955</v>
       </c>
       <c r="E169" t="n">
-        <v>24.84</v>
+        <v>-6.91</v>
       </c>
       <c r="F169" t="n">
-        <v>4020</v>
+        <v>1820</v>
       </c>
       <c r="G169" t="n">
-        <v>4020</v>
+        <v>1820</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>SKIP_GAP_HIGH</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -7785,29 +7785,29 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>BIKE</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1955</v>
+        <v>4200</v>
       </c>
       <c r="E170" t="n">
-        <v>-6.91</v>
+        <v>-0.48</v>
       </c>
       <c r="F170" t="n">
-        <v>1820</v>
+        <v>4180</v>
       </c>
       <c r="G170" t="n">
-        <v>1820</v>
+        <v>5225</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -7859,29 +7859,29 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BIKE</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>4200</v>
+        <v>3220</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.48</v>
+        <v>24.84</v>
       </c>
       <c r="F172" t="n">
-        <v>4180</v>
+        <v>4020</v>
       </c>
       <c r="G172" t="n">
-        <v>5225</v>
+        <v>4020</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SKIP_GAP_HIGH</t>
         </is>
       </c>
     </row>
@@ -7896,30 +7896,33 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>TIFA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4020</v>
+        <v>360</v>
       </c>
       <c r="E173" t="n">
-        <v>24.38</v>
+        <v>8.33</v>
       </c>
       <c r="F173" t="n">
-        <v>5000</v>
+        <v>390</v>
       </c>
       <c r="G173" t="n">
-        <v>5025</v>
+        <v>398</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>SKIP_GAP_HIGH</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="174">
@@ -7933,20 +7936,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AIMS</t>
+          <t>ALDO</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>925</v>
+        <v>1820</v>
       </c>
       <c r="E174" t="n">
-        <v>-6.49</v>
+        <v>-6.87</v>
       </c>
       <c r="F174" t="n">
-        <v>865</v>
+        <v>1695</v>
       </c>
       <c r="G174" t="n">
-        <v>865</v>
+        <v>1695</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -7970,29 +7973,29 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>98</v>
+        <v>4020</v>
       </c>
       <c r="E175" t="n">
-        <v>-6.12</v>
+        <v>24.38</v>
       </c>
       <c r="F175" t="n">
-        <v>92</v>
+        <v>5000</v>
       </c>
       <c r="G175" t="n">
-        <v>92</v>
+        <v>5025</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SKIP_GAP_HIGH</t>
         </is>
       </c>
     </row>
@@ -8007,30 +8010,33 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>ALDO</t>
+          <t>TMPO</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1820</v>
+        <v>169</v>
       </c>
       <c r="E176" t="n">
-        <v>-6.87</v>
+        <v>5.33</v>
       </c>
       <c r="F176" t="n">
-        <v>1695</v>
+        <v>178</v>
       </c>
       <c r="G176" t="n">
-        <v>1695</v>
+        <v>194</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>8.44</v>
       </c>
     </row>
     <row r="177">
@@ -8044,33 +8050,30 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>TIFA</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>360</v>
+        <v>98</v>
       </c>
       <c r="E177" t="n">
-        <v>8.33</v>
+        <v>-6.12</v>
       </c>
       <c r="F177" t="n">
-        <v>390</v>
+        <v>92</v>
       </c>
       <c r="G177" t="n">
-        <v>398</v>
+        <v>92</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J177" t="n">
-        <v>1.54</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -8084,33 +8087,30 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TMPO</t>
+          <t>AIMS</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>169</v>
+        <v>925</v>
       </c>
       <c r="E178" t="n">
-        <v>5.33</v>
+        <v>-6.49</v>
       </c>
       <c r="F178" t="n">
-        <v>178</v>
+        <v>865</v>
       </c>
       <c r="G178" t="n">
-        <v>194</v>
+        <v>865</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J178" t="n">
-        <v>8.44</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -8124,30 +8124,33 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AKKU</t>
+          <t>TRUK</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>92</v>
+        <v>5025</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>17.91</v>
       </c>
       <c r="F179" t="n">
-        <v>92</v>
+        <v>5925</v>
       </c>
       <c r="G179" t="n">
-        <v>114</v>
+        <v>6025</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>1.18</v>
       </c>
     </row>
     <row r="180">
@@ -8161,33 +8164,30 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TRUK</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5025</v>
+        <v>348</v>
       </c>
       <c r="E180" t="n">
-        <v>17.91</v>
+        <v>0.57</v>
       </c>
       <c r="F180" t="n">
-        <v>5925</v>
+        <v>350</v>
       </c>
       <c r="G180" t="n">
-        <v>6025</v>
+        <v>358</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J180" t="n">
-        <v>1.18</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -8201,33 +8201,30 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>AKKU</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>510</v>
+        <v>92</v>
       </c>
       <c r="E181" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>530</v>
+        <v>92</v>
       </c>
       <c r="G181" t="n">
-        <v>535</v>
+        <v>114</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J181" t="n">
-        <v>0.44</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -8241,30 +8238,33 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>348</v>
+        <v>102</v>
       </c>
       <c r="E182" t="n">
-        <v>0.57</v>
+        <v>2.94</v>
       </c>
       <c r="F182" t="n">
-        <v>350</v>
+        <v>105</v>
       </c>
       <c r="G182" t="n">
-        <v>358</v>
+        <v>137</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>29.82</v>
       </c>
     </row>
     <row r="183">
@@ -8278,20 +8278,20 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>102</v>
+        <v>510</v>
       </c>
       <c r="E183" t="n">
-        <v>2.94</v>
+        <v>3.92</v>
       </c>
       <c r="F183" t="n">
-        <v>105</v>
+        <v>530</v>
       </c>
       <c r="G183" t="n">
-        <v>137</v>
+        <v>535</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>29.82</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="184">
@@ -8318,24 +8318,24 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ARII</t>
+          <t>DMAS</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>500</v>
+        <v>208</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>-1.92</v>
       </c>
       <c r="F184" t="n">
-        <v>500</v>
+        <v>204</v>
       </c>
       <c r="G184" t="n">
-        <v>515</v>
+        <v>220</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8355,24 +8355,24 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>DMAS</t>
+          <t>MPXL</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>208</v>
+        <v>332</v>
       </c>
       <c r="E185" t="n">
-        <v>-1.92</v>
+        <v>-1.2</v>
       </c>
       <c r="F185" t="n">
-        <v>204</v>
+        <v>328</v>
       </c>
       <c r="G185" t="n">
-        <v>220</v>
+        <v>334</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -8392,20 +8392,20 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MPXL</t>
+          <t>PRDA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>332</v>
+        <v>3500</v>
       </c>
       <c r="E186" t="n">
-        <v>-1.2</v>
+        <v>-2.86</v>
       </c>
       <c r="F186" t="n">
-        <v>328</v>
+        <v>3400</v>
       </c>
       <c r="G186" t="n">
-        <v>334</v>
+        <v>3680</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -8429,24 +8429,24 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BAPA</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E187" t="n">
-        <v>-1.72</v>
+        <v>-4.24</v>
       </c>
       <c r="F187" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G187" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -8466,24 +8466,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>BAPA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E188" t="n">
-        <v>-4.24</v>
+        <v>-1.72</v>
       </c>
       <c r="F188" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G188" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8503,20 +8503,20 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PRDA</t>
+          <t>ARII</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>3500</v>
+        <v>500</v>
       </c>
       <c r="E189" t="n">
-        <v>-2.86</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>3400</v>
+        <v>500</v>
       </c>
       <c r="G189" t="n">
-        <v>3680</v>
+        <v>515</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -8540,24 +8540,24 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>PRDA</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>134</v>
+        <v>3590</v>
       </c>
       <c r="E190" t="n">
-        <v>0.75</v>
+        <v>0.28</v>
       </c>
       <c r="F190" t="n">
-        <v>135</v>
+        <v>3600</v>
       </c>
       <c r="G190" t="n">
-        <v>146</v>
+        <v>3750</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8614,29 +8614,29 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E192" t="n">
-        <v>33.58</v>
+        <v>0.75</v>
       </c>
       <c r="F192" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="G192" t="n">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SUSPENDED</t>
+          <t>SKIP_GAP_LOW</t>
         </is>
       </c>
     </row>
@@ -8651,29 +8651,29 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>PRDA</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>3590</v>
+        <v>137</v>
       </c>
       <c r="E193" t="n">
-        <v>0.28</v>
+        <v>33.58</v>
       </c>
       <c r="F193" t="n">
-        <v>3600</v>
+        <v>183</v>
       </c>
       <c r="G193" t="n">
-        <v>3750</v>
+        <v>183</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
+          <t>SUSPENDED</t>
         </is>
       </c>
     </row>
@@ -8688,24 +8688,24 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>WMPP</t>
+          <t>WMUU</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E194" t="n">
-        <v>-3.85</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G194" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8725,33 +8725,30 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TOBA</t>
+          <t>WMPP</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>520</v>
+        <v>26</v>
       </c>
       <c r="E195" t="n">
-        <v>11.54</v>
+        <v>-3.85</v>
       </c>
       <c r="F195" t="n">
-        <v>580</v>
+        <v>25</v>
       </c>
       <c r="G195" t="n">
-        <v>620</v>
+        <v>31</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J195" t="n">
-        <v>6.36</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -8765,30 +8762,33 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>AALI</t>
+          <t>TOBA</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>9625</v>
+        <v>520</v>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
+        <v>11.54</v>
       </c>
       <c r="F196" t="n">
-        <v>9625</v>
+        <v>580</v>
       </c>
       <c r="G196" t="n">
-        <v>9800</v>
+        <v>620</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>6.36</v>
       </c>
     </row>
     <row r="197">
@@ -8802,20 +8802,20 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>AALI</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>130</v>
+        <v>9625</v>
       </c>
       <c r="E197" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>131</v>
+        <v>9625</v>
       </c>
       <c r="G197" t="n">
-        <v>145</v>
+        <v>9800</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -8839,20 +8839,20 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ASPI</t>
+          <t>PRDA</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>995</v>
+        <v>3670</v>
       </c>
       <c r="E198" t="n">
-        <v>2.51</v>
+        <v>-0.54</v>
       </c>
       <c r="F198" t="n">
-        <v>1020</v>
+        <v>3650</v>
       </c>
       <c r="G198" t="n">
-        <v>1025</v>
+        <v>3760</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -8861,11 +8861,8 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="J198" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -8879,20 +8876,20 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>AYLS</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>218</v>
+        <v>130</v>
       </c>
       <c r="E199" t="n">
-        <v>3.67</v>
+        <v>0.77</v>
       </c>
       <c r="F199" t="n">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="G199" t="n">
-        <v>226</v>
+        <v>145</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -8901,11 +8898,8 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="J199" t="n">
-        <v>-3</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -8919,30 +8913,33 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>PTSN</t>
+          <t>ASPI</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>390</v>
+        <v>995</v>
       </c>
       <c r="E200" t="n">
-        <v>0.51</v>
+        <v>2.51</v>
       </c>
       <c r="F200" t="n">
-        <v>392</v>
+        <v>1020</v>
       </c>
       <c r="G200" t="n">
-        <v>428</v>
+        <v>1025</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="201">
@@ -8956,33 +8953,30 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>ENZO</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="E201" t="n">
-        <v>2.96</v>
+        <v>1.75</v>
       </c>
       <c r="F201" t="n">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="G201" t="n">
-        <v>151</v>
+        <v>59</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J201" t="n">
-        <v>8.09</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -8996,30 +8990,33 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>PRDA</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>3670</v>
+        <v>380</v>
       </c>
       <c r="E202" t="n">
-        <v>-0.54</v>
+        <v>13.16</v>
       </c>
       <c r="F202" t="n">
-        <v>3650</v>
+        <v>430</v>
       </c>
       <c r="G202" t="n">
-        <v>3760</v>
+        <v>436</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="203">
@@ -9033,30 +9030,33 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>WMUU</t>
+          <t>AYLS</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="F203" t="n">
-        <v>36</v>
+        <v>226</v>
       </c>
       <c r="G203" t="n">
-        <v>47</v>
+        <v>226</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="204">
@@ -9070,24 +9070,24 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>TCPI</t>
+          <t>PTSN</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1735</v>
+        <v>390</v>
       </c>
       <c r="E204" t="n">
-        <v>1.44</v>
+        <v>0.51</v>
       </c>
       <c r="F204" t="n">
-        <v>1760</v>
+        <v>392</v>
       </c>
       <c r="G204" t="n">
-        <v>1770</v>
+        <v>428</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -9144,24 +9144,24 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>380</v>
+        <v>135</v>
       </c>
       <c r="E206" t="n">
-        <v>13.16</v>
+        <v>2.96</v>
       </c>
       <c r="F206" t="n">
-        <v>430</v>
+        <v>139</v>
       </c>
       <c r="G206" t="n">
-        <v>436</v>
+        <v>151</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="J206" t="n">
-        <v>0.89</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="207">
@@ -9184,24 +9184,24 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ENZO</t>
+          <t>TCPI</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>57</v>
+        <v>1735</v>
       </c>
       <c r="E207" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="F207" t="n">
-        <v>58</v>
+        <v>1760</v>
       </c>
       <c r="G207" t="n">
-        <v>59</v>
+        <v>1770</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -9221,20 +9221,20 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>DKHH</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E208" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G208" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -9243,11 +9243,8 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>TRAIL</t>
-        </is>
-      </c>
-      <c r="J208" t="n">
-        <v>0.2</v>
+          <t>SKIP_GAP_LOW</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -9261,20 +9258,20 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>BLES</t>
+          <t>MBSS</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>228</v>
+        <v>4280</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="F209" t="n">
-        <v>228</v>
+        <v>4360</v>
       </c>
       <c r="G209" t="n">
-        <v>230</v>
+        <v>4500</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -9298,20 +9295,20 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DKHH</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="F210" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G210" t="n">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -9320,8 +9317,11 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>SKIP_GAP_LOW</t>
-        </is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="211">
@@ -9335,24 +9335,24 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>MBSS</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>4280</v>
+        <v>90</v>
       </c>
       <c r="E211" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>4360</v>
+        <v>90</v>
       </c>
       <c r="G211" t="n">
-        <v>4500</v>
+        <v>95</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -9520,24 +9520,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>WMUU</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="G216" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9557,20 +9557,20 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>WMUU</t>
+          <t>BLES</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>36</v>
+        <v>228</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>36</v>
+        <v>228</v>
       </c>
       <c r="G217" t="n">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -9578,6 +9578,154 @@
         </is>
       </c>
       <c r="I217" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>OKAS</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>105</v>
+      </c>
+      <c r="E218" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="F218" t="n">
+        <v>103</v>
+      </c>
+      <c r="G218" t="n">
+        <v>103</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>TGUK</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>100</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="n">
+        <v>100</v>
+      </c>
+      <c r="G219" t="n">
+        <v>101</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>TMPO</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>228</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>228</v>
+      </c>
+      <c r="G220" t="n">
+        <v>248</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>SKIP_GAP_LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Rabu</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>WMUU</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>34</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>34</v>
+      </c>
+      <c r="G221" t="n">
+        <v>35</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
         <is>
           <t>SKIP_GAP_LOW</t>
         </is>
@@ -9588,7 +9736,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J5:J217">
+  <conditionalFormatting sqref="J5:J221">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/quant/output/Rekap_Trading_2026-10.xlsx
+++ b/quant/output/Rekap_Trading_2026-10.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -111,6 +111,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -520,7 +523,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Dibuat: 2026-10-30 00:45</t>
+          <t>Dibuat: 2026-10-30 21:20</t>
         </is>
       </c>
     </row>
@@ -766,10 +769,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -782,28 +797,222 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Prediksi untuk: 2026-10-30</t>
+          <t>Prediksi untuk: 2026-11-02</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Kode</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Value (M)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Ret1d%</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Ret5d%</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Range%</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>VolZ</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Px&gt;sma20%</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>ATR%</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Match</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tidak ada kandidat</t>
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>77</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>5525</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>KUAT</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>NPGF</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>LEMAH</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>CBUT</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1065</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>17.48</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2"/>
-    <mergeCell ref="A1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -938,10 +1147,10 @@
           <t>Minggu 1</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="8" t="n">
         <v>46293</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -992,10 +1201,10 @@
           <t>Minggu 2</t>
         </is>
       </c>
-      <c r="B6" s="7" t="n">
+      <c r="B6" s="8" t="n">
         <v>46300</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1046,10 +1255,10 @@
           <t>Minggu 3</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="8" t="n">
         <v>46307</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1100,10 +1309,10 @@
           <t>Minggu 4</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
+      <c r="B8" s="8" t="n">
         <v>46314</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>46318</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -1154,10 +1363,10 @@
           <t>Minggu 5</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="8" t="n">
         <v>46321</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>46325</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -1315,7 +1524,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1352,7 +1561,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1389,7 +1598,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1426,7 +1635,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1463,7 +1672,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1500,7 +1709,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,7 +1746,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1574,7 +1783,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1614,7 +1823,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1651,7 +1860,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1688,7 +1897,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1725,7 +1934,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1762,7 +1971,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,7 +2008,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="8" t="n">
         <v>46296</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1836,7 +2045,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1876,7 +2085,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1913,7 +2122,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1950,7 +2159,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1990,7 +2199,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2027,7 +2236,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2064,7 +2273,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2101,7 +2310,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2138,7 +2347,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2175,7 +2384,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2212,7 +2421,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="8" t="n">
         <v>46297</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2249,7 +2458,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2289,7 +2498,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2326,7 +2535,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2366,7 +2575,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2406,7 +2615,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2446,7 +2655,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2483,7 +2692,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="8" t="n">
         <v>46300</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2520,7 +2729,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2560,7 +2769,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n">
+      <c r="A38" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2597,7 +2806,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n">
+      <c r="A39" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2637,7 +2846,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2674,7 +2883,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2714,7 +2923,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2751,7 +2960,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="n">
+      <c r="A43" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2788,7 +2997,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2828,7 +3037,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="n">
+      <c r="A45" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2865,7 +3074,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="n">
+      <c r="A46" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2905,7 +3114,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="n">
+      <c r="A47" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2942,7 +3151,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n">
+      <c r="A48" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2982,7 +3191,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3019,7 +3228,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="n">
+      <c r="A50" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3056,7 +3265,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="n">
+      <c r="A51" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3093,7 +3302,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="n">
+      <c r="A52" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3130,7 +3339,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="n">
+      <c r="A53" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3167,7 +3376,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="n">
+      <c r="A54" s="8" t="n">
         <v>46301</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3204,7 +3413,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="n">
+      <c r="A55" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3241,7 +3450,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="7" t="n">
+      <c r="A56" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3278,7 +3487,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="n">
+      <c r="A57" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3315,7 +3524,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="n">
+      <c r="A58" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3355,7 +3564,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="n">
+      <c r="A59" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3392,7 +3601,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="7" t="n">
+      <c r="A60" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3429,7 +3638,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="n">
+      <c r="A61" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3466,7 +3675,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="n">
+      <c r="A62" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3506,7 +3715,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="n">
+      <c r="A63" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3543,7 +3752,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="n">
+      <c r="A64" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3580,7 +3789,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="n">
+      <c r="A65" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3620,7 +3829,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="7" t="n">
+      <c r="A66" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3657,7 +3866,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="n">
+      <c r="A67" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3694,7 +3903,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="7" t="n">
+      <c r="A68" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -3731,7 +3940,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="n">
+      <c r="A69" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -3768,7 +3977,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="7" t="n">
+      <c r="A70" s="8" t="n">
         <v>46302</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -3808,7 +4017,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="n">
+      <c r="A71" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -3845,7 +4054,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="n">
+      <c r="A72" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -3882,7 +4091,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="n">
+      <c r="A73" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -3919,7 +4128,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="n">
+      <c r="A74" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -3956,7 +4165,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="n">
+      <c r="A75" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -3993,7 +4202,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="7" t="n">
+      <c r="A76" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4030,7 +4239,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="n">
+      <c r="A77" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4067,7 +4276,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="7" t="n">
+      <c r="A78" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -4104,7 +4313,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="n">
+      <c r="A79" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4141,7 +4350,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="7" t="n">
+      <c r="A80" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4181,7 +4390,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="n">
+      <c r="A81" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4218,7 +4427,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="n">
+      <c r="A82" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4255,7 +4464,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="n">
+      <c r="A83" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -4295,7 +4504,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="n">
+      <c r="A84" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -4332,7 +4541,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="n">
+      <c r="A85" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -4372,7 +4581,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="7" t="n">
+      <c r="A86" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -4409,7 +4618,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="n">
+      <c r="A87" s="8" t="n">
         <v>46303</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -4446,7 +4655,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="n">
+      <c r="A88" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -4483,7 +4692,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="n">
+      <c r="A89" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -4520,7 +4729,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="n">
+      <c r="A90" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -4557,7 +4766,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="n">
+      <c r="A91" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -4594,7 +4803,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="n">
+      <c r="A92" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -4631,7 +4840,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="n">
+      <c r="A93" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -4668,7 +4877,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="n">
+      <c r="A94" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -4708,7 +4917,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="n">
+      <c r="A95" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -4748,7 +4957,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="7" t="n">
+      <c r="A96" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -4785,7 +4994,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="n">
+      <c r="A97" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -4822,7 +5031,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="7" t="n">
+      <c r="A98" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -4862,7 +5071,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="n">
+      <c r="A99" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -4899,7 +5108,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="7" t="n">
+      <c r="A100" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -4936,7 +5145,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="n">
+      <c r="A101" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -4976,7 +5185,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="n">
+      <c r="A102" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -5013,7 +5222,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="7" t="n">
+      <c r="A103" s="8" t="n">
         <v>46304</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -5050,7 +5259,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="n">
+      <c r="A104" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -5087,7 +5296,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="n">
+      <c r="A105" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -5127,7 +5336,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="7" t="n">
+      <c r="A106" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -5167,7 +5376,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -5204,7 +5413,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="n">
+      <c r="A108" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -5241,7 +5450,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="n">
+      <c r="A109" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -5278,7 +5487,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="7" t="n">
+      <c r="A110" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -5315,7 +5524,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="n">
+      <c r="A111" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -5352,7 +5561,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="n">
+      <c r="A112" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -5392,7 +5601,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="n">
+      <c r="A113" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -5429,7 +5638,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="7" t="n">
+      <c r="A114" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -5466,7 +5675,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="7" t="n">
+      <c r="A115" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -5503,7 +5712,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="7" t="n">
+      <c r="A116" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -5540,7 +5749,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="n">
+      <c r="A117" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -5577,7 +5786,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="7" t="n">
+      <c r="A118" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -5617,7 +5826,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="7" t="n">
+      <c r="A119" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -5654,7 +5863,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="7" t="n">
+      <c r="A120" s="8" t="n">
         <v>46307</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -5691,7 +5900,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="7" t="n">
+      <c r="A121" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -5728,7 +5937,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="n">
+      <c r="A122" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -5765,7 +5974,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="7" t="n">
+      <c r="A123" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -5802,7 +6011,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="7" t="n">
+      <c r="A124" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -5839,7 +6048,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="7" t="n">
+      <c r="A125" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -5876,7 +6085,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="7" t="n">
+      <c r="A126" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -5913,7 +6122,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="n">
+      <c r="A127" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -5950,7 +6159,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="7" t="n">
+      <c r="A128" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -5990,7 +6199,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="n">
+      <c r="A129" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -6027,7 +6236,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="7" t="n">
+      <c r="A130" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -6064,7 +6273,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="7" t="n">
+      <c r="A131" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -6101,7 +6310,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="n">
+      <c r="A132" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -6138,7 +6347,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="7" t="n">
+      <c r="A133" s="8" t="n">
         <v>46308</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -6175,7 +6384,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="7" t="n">
+      <c r="A134" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -6212,7 +6421,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="7" t="n">
+      <c r="A135" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -6249,7 +6458,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="7" t="n">
+      <c r="A136" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -6286,7 +6495,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="7" t="n">
+      <c r="A137" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -6323,7 +6532,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="7" t="n">
+      <c r="A138" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -6360,7 +6569,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="7" t="n">
+      <c r="A139" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -6397,7 +6606,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="7" t="n">
+      <c r="A140" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -6434,7 +6643,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="7" t="n">
+      <c r="A141" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -6471,7 +6680,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="7" t="n">
+      <c r="A142" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -6511,7 +6720,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="7" t="n">
+      <c r="A143" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -6548,7 +6757,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="7" t="n">
+      <c r="A144" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -6585,7 +6794,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="7" t="n">
+      <c r="A145" s="8" t="n">
         <v>46309</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -6625,7 +6834,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="7" t="n">
+      <c r="A146" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -6665,7 +6874,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="7" t="n">
+      <c r="A147" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -6702,7 +6911,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="7" t="n">
+      <c r="A148" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -6739,7 +6948,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="7" t="n">
+      <c r="A149" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -6776,7 +6985,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="7" t="n">
+      <c r="A150" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -6813,7 +7022,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="7" t="n">
+      <c r="A151" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -6850,7 +7059,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="7" t="n">
+      <c r="A152" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -6887,7 +7096,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="7" t="n">
+      <c r="A153" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -6924,7 +7133,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="n">
+      <c r="A154" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -6961,7 +7170,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="7" t="n">
+      <c r="A155" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -6998,7 +7207,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="7" t="n">
+      <c r="A156" s="8" t="n">
         <v>46310</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -7035,7 +7244,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="7" t="n">
+      <c r="A157" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -7072,7 +7281,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="7" t="n">
+      <c r="A158" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -7109,7 +7318,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="7" t="n">
+      <c r="A159" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -7146,7 +7355,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="7" t="n">
+      <c r="A160" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -7183,7 +7392,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="7" t="n">
+      <c r="A161" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -7220,7 +7429,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="7" t="n">
+      <c r="A162" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -7257,7 +7466,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="7" t="n">
+      <c r="A163" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -7294,7 +7503,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="7" t="n">
+      <c r="A164" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -7331,7 +7540,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="7" t="n">
+      <c r="A165" s="8" t="n">
         <v>46311</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -7368,7 +7577,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="7" t="n">
+      <c r="A166" s="8" t="n">
         <v>46314</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -7405,7 +7614,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="7" t="n">
+      <c r="A167" s="8" t="n">
         <v>46314</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -7442,7 +7651,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="7" t="n">
+      <c r="A168" s="8" t="n">
         <v>46314</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -7479,7 +7688,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="7" t="n">
+      <c r="A169" s="8" t="n">
         <v>46314</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -7516,7 +7725,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="7" t="n">
+      <c r="A170" s="8" t="n">
         <v>46315</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -7556,7 +7765,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="7" t="n">
+      <c r="A171" s="8" t="n">
         <v>46315</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -7593,7 +7802,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="7" t="n">
+      <c r="A172" s="8" t="n">
         <v>46315</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -7630,7 +7839,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="7" t="n">
+      <c r="A173" s="8" t="n">
         <v>46315</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -7667,7 +7876,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="7" t="n">
+      <c r="A174" s="8" t="n">
         <v>46315</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -7707,7 +7916,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="7" t="n">
+      <c r="A175" s="8" t="n">
         <v>46315</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -7744,7 +7953,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="7" t="n">
+      <c r="A176" s="8" t="n">
         <v>46316</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -7784,7 +7993,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="7" t="n">
+      <c r="A177" s="8" t="n">
         <v>46316</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -7821,7 +8030,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="7" t="n">
+      <c r="A178" s="8" t="n">
         <v>46316</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -7861,7 +8070,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="7" t="n">
+      <c r="A179" s="8" t="n">
         <v>46316</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -7898,7 +8107,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="7" t="n">
+      <c r="A180" s="8" t="n">
         <v>46316</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -7938,7 +8147,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="7" t="n">
+      <c r="A181" s="8" t="n">
         <v>46317</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -7975,7 +8184,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="7" t="n">
+      <c r="A182" s="8" t="n">
         <v>46317</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -8012,7 +8221,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="7" t="n">
+      <c r="A183" s="8" t="n">
         <v>46317</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -8049,7 +8258,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="7" t="n">
+      <c r="A184" s="8" t="n">
         <v>46317</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -8086,7 +8295,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="7" t="n">
+      <c r="A185" s="8" t="n">
         <v>46317</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -8123,7 +8332,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="7" t="n">
+      <c r="A186" s="8" t="n">
         <v>46317</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -8160,7 +8369,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="7" t="n">
+      <c r="A187" s="8" t="n">
         <v>46318</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -8197,7 +8406,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="7" t="n">
+      <c r="A188" s="8" t="n">
         <v>46318</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -8234,7 +8443,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="7" t="n">
+      <c r="A189" s="8" t="n">
         <v>46318</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -8271,7 +8480,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="7" t="n">
+      <c r="A190" s="8" t="n">
         <v>46318</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -8308,7 +8517,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="7" t="n">
+      <c r="A191" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -8345,7 +8554,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="7" t="n">
+      <c r="A192" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -8382,7 +8591,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="7" t="n">
+      <c r="A193" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -8419,7 +8628,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="7" t="n">
+      <c r="A194" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -8459,7 +8668,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="7" t="n">
+      <c r="A195" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -8496,7 +8705,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="7" t="n">
+      <c r="A196" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -8533,7 +8742,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="7" t="n">
+      <c r="A197" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -8573,7 +8782,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="7" t="n">
+      <c r="A198" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -8613,7 +8822,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="7" t="n">
+      <c r="A199" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -8650,7 +8859,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="7" t="n">
+      <c r="A200" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -8687,7 +8896,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="7" t="n">
+      <c r="A201" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -8727,7 +8936,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="7" t="n">
+      <c r="A202" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -8764,7 +8973,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="7" t="n">
+      <c r="A203" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -8804,7 +9013,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="7" t="n">
+      <c r="A204" s="8" t="n">
         <v>46321</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -8841,7 +9050,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="7" t="n">
+      <c r="A205" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -8878,7 +9087,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="7" t="n">
+      <c r="A206" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -8915,7 +9124,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="7" t="n">
+      <c r="A207" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -8952,7 +9161,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="7" t="n">
+      <c r="A208" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -8992,7 +9201,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="7" t="n">
+      <c r="A209" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -9029,7 +9238,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="7" t="n">
+      <c r="A210" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -9066,7 +9275,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="7" t="n">
+      <c r="A211" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -9103,7 +9312,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="7" t="n">
+      <c r="A212" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -9140,7 +9349,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="7" t="n">
+      <c r="A213" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -9177,7 +9386,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="7" t="n">
+      <c r="A214" s="8" t="n">
         <v>46322</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -9214,7 +9423,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="7" t="n">
+      <c r="A215" s="8" t="n">
         <v>46323</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -9251,7 +9460,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="7" t="n">
+      <c r="A216" s="8" t="n">
         <v>46323</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -9288,7 +9497,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="7" t="n">
+      <c r="A217" s="8" t="n">
         <v>46323</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -9325,7 +9534,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="7" t="n">
+      <c r="A218" s="8" t="n">
         <v>46323</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -9362,7 +9571,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="7" t="n">
+      <c r="A219" s="8" t="n">
         <v>46324</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -9399,7 +9608,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="7" t="n">
+      <c r="A220" s="8" t="n">
         <v>46324</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -9436,7 +9645,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="7" t="n">
+      <c r="A221" s="8" t="n">
         <v>46324</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -9473,7 +9682,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="7" t="n">
+      <c r="A222" s="8" t="n">
         <v>46324</v>
       </c>
       <c r="B222" t="inlineStr">
